--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE4042F-42EA-0142-A76E-C64ACF532F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B965E68F-15CD-F546-9A0B-BB1B1CEBB7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,10 @@
     <sheet name="Installed Capacity" sheetId="3" r:id="rId3"/>
     <sheet name="Capacity Factor Calculation" sheetId="4" r:id="rId4"/>
     <sheet name="Solar Capacity Factor" sheetId="8" r:id="rId5"/>
-    <sheet name="BECF-pre-ret" sheetId="5" r:id="rId6"/>
-    <sheet name="BECF-pre-nonret" sheetId="6" r:id="rId7"/>
-    <sheet name="BECF-new" sheetId="7" r:id="rId8"/>
+    <sheet name="Capacity Factor-Reports" sheetId="9" r:id="rId6"/>
+    <sheet name="BECF-pre-ret" sheetId="5" r:id="rId7"/>
+    <sheet name="BECF-pre-nonret" sheetId="6" r:id="rId8"/>
+    <sheet name="BECF-new" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="173">
   <si>
     <t>BAU Expected Capacity Factors</t>
   </si>
@@ -544,6 +545,75 @@
   <si>
     <t>Conversion from GWh to MWh</t>
   </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Capacity factor</t>
+  </si>
+  <si>
+    <t>Ember</t>
+  </si>
+  <si>
+    <t>Indonesia’s expansion of clean power can spur growth and equality</t>
+  </si>
+  <si>
+    <t>https://ember-energy.org/app/uploads/2024/10/EN-Report-Indonesias-expansion-of-clean-power-can-spur-growth-and-equality.pdf</t>
+  </si>
+  <si>
+    <t>Climate Policy Initiative</t>
+  </si>
+  <si>
+    <t>Indonesia Power Sector Finance Dashboard</t>
+  </si>
+  <si>
+    <t>https://www.climatepolicyinitiative.org/wp-content/uploads/2024/10/Indonesia-Power-Sector-Finance-Flows.pdf</t>
+  </si>
+  <si>
+    <t>ERIA</t>
+  </si>
+  <si>
+    <t>Forecast of Biomass Demand Potential in Indonesia: Seeking a Business Model for Wood Pellets</t>
+  </si>
+  <si>
+    <t>https://www.eria.org/uploads/media/Research-Project-Report/2022-01-Biomass-Demand-Potential-Indonesia/Forecast-of-Biomass-Demand-Potential-in-Indonesia.pdf</t>
+  </si>
+  <si>
+    <t>IESR</t>
+  </si>
+  <si>
+    <t>https://iesr.or.id/wp-content/uploads/2022/01/Indonesia-Energy-Transition-Outlook-2022-IESR-Digital-Version-.pdf</t>
+  </si>
+  <si>
+    <t>Indonesia Energy Transition Outlook 2022</t>
+  </si>
+  <si>
+    <t>IRENA</t>
+  </si>
+  <si>
+    <t>RENEWABLE ENERGY PROSPECTS: INDONESIA</t>
+  </si>
+  <si>
+    <t>https://www.irena.org/-/media/Files/IRENA/Agency/Publication/2017/Mar/IRENA_REmap_Indonesia_report_2017.pdf</t>
+  </si>
+  <si>
+    <t>IAEA</t>
+  </si>
+  <si>
+    <t>PROVEN TECHNOLOGY PROVEN TECHNOLOGY PERSPECTIVE PERSPECTIVE FROM INDONESIA</t>
+  </si>
+  <si>
+    <t>https://nucleus.iaea.org/sites/INPRO/df1/Session%202/19-Suprawoto.pdf</t>
+  </si>
+  <si>
+    <t>Sidik Permana, Nuri Trianti, and Adi Rahmansyah</t>
+  </si>
+  <si>
+    <t>Nuclear energy contribution potential to secure electricity demand with low carbon emission and low risk of power plant in Indonesia</t>
+  </si>
+  <si>
+    <t>https://iopscience.iop.org/article/10.1088/1755-1315/753/1/012048/pdf</t>
+  </si>
 </sst>
 </file>
 
@@ -555,7 +625,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +759,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF242424"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -911,10 +989,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1066,6 +1145,14 @@
     <xf numFmtId="11" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1125,7 +1212,8 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1139,6 +1227,105 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2EC8457B-567F-E150-95F3-D9E0D9E5731F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10756900" y="3644900"/>
+          <a:ext cx="9029700" cy="2171700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEBC14CB-7C92-4313-2EBB-A24438582A74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12700" y="3657600"/>
+          <a:ext cx="9855200" cy="7162800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1339,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1035"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="8.6640625" customWidth="1"/>
@@ -1359,16 +1546,16 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="77"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+      <c r="I3" s="81"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1406,186 +1593,347 @@
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2"/>
+      <c r="B11" s="75">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="76" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="75">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="76" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="75">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="65" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="76" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2"/>
+      <c r="B25" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="2"/>
+      <c r="B26" s="75">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="2"/>
+      <c r="B27" s="77" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="2"/>
+      <c r="B28" s="76" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+    </row>
+    <row r="30" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2"/>
+      <c r="B30" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2"/>
+      <c r="B31" s="75">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2"/>
+      <c r="B32" s="65" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2"/>
+      <c r="B33" s="76" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
+      <c r="B34" s="65"/>
+    </row>
+    <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="2"/>
+      <c r="B35" s="74" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2"/>
+      <c r="B36" s="78">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="2"/>
+      <c r="B37" s="65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="2"/>
+      <c r="B38" s="76" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="2"/>
+      <c r="B39" s="65"/>
+    </row>
+    <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2"/>
+      <c r="B40" s="74" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="78">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2"/>
+      <c r="B42" s="65" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2"/>
+      <c r="B43" s="76" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="2"/>
+      <c r="B44" s="65"/>
+    </row>
+    <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="78" t="s">
+      <c r="B46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B47" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="79"/>
-      <c r="I12" s="79"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="79"/>
-      <c r="C13" s="79"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="79"/>
-      <c r="G13" s="79"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="79"/>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="79"/>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
-      <c r="F14" s="79"/>
-      <c r="G14" s="79"/>
-      <c r="H14" s="79"/>
-      <c r="I14" s="79"/>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="79"/>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
-      <c r="H15" s="79"/>
-      <c r="I15" s="79"/>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-      <c r="F16" s="79"/>
-      <c r="G16" s="79"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="79"/>
-    </row>
-    <row r="17" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-    </row>
-    <row r="18" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-    </row>
-    <row r="19" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="79"/>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
-      <c r="F19" s="79"/>
-      <c r="G19" s="79"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="79"/>
-    </row>
-    <row r="20" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="79"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="79"/>
-      <c r="G20" s="79"/>
-      <c r="H20" s="79"/>
-      <c r="I20" s="79"/>
-    </row>
-    <row r="21" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="79"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
-    </row>
-    <row r="22" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="79"/>
-    </row>
-    <row r="23" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="79"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="79"/>
-      <c r="I23" s="79"/>
-    </row>
-    <row r="24" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="79"/>
-      <c r="C24" s="79"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
-      <c r="F24" s="79"/>
-      <c r="G24" s="79"/>
-      <c r="H24" s="79"/>
-      <c r="I24" s="79"/>
-    </row>
-    <row r="25" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C47" s="83"/>
+      <c r="D47" s="83"/>
+      <c r="E47" s="83"/>
+      <c r="F47" s="83"/>
+      <c r="G47" s="83"/>
+      <c r="H47" s="83"/>
+      <c r="I47" s="83"/>
+    </row>
+    <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B48" s="83"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="83"/>
+      <c r="G48" s="83"/>
+      <c r="H48" s="83"/>
+      <c r="I48" s="83"/>
+    </row>
+    <row r="49" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="83"/>
+      <c r="G49" s="83"/>
+      <c r="H49" s="83"/>
+      <c r="I49" s="83"/>
+    </row>
+    <row r="50" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="83"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="83"/>
+      <c r="E50" s="83"/>
+      <c r="F50" s="83"/>
+      <c r="G50" s="83"/>
+      <c r="H50" s="83"/>
+      <c r="I50" s="83"/>
+    </row>
+    <row r="51" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="83"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
+    </row>
+    <row r="52" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+    </row>
+    <row r="53" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="83"/>
+      <c r="C53" s="83"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="83"/>
+      <c r="F53" s="83"/>
+      <c r="G53" s="83"/>
+      <c r="H53" s="83"/>
+      <c r="I53" s="83"/>
+    </row>
+    <row r="54" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="83"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
+      <c r="I54" s="83"/>
+    </row>
+    <row r="55" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="83"/>
+      <c r="G55" s="83"/>
+      <c r="H55" s="83"/>
+      <c r="I55" s="83"/>
+    </row>
+    <row r="56" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="83"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="83"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+    </row>
+    <row r="57" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="83"/>
+      <c r="G57" s="83"/>
+      <c r="H57" s="83"/>
+      <c r="I57" s="83"/>
+    </row>
+    <row r="58" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="83"/>
+      <c r="G58" s="83"/>
+      <c r="H58" s="83"/>
+      <c r="I58" s="83"/>
+    </row>
+    <row r="59" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="83"/>
+      <c r="C59" s="83"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="83"/>
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="83"/>
+    </row>
+    <row r="60" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2522,13 +2870,55 @@
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1013" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1014" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1015" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1016" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1017" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1018" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1019" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1020" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1021" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1022" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1023" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1024" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1025" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1026" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1027" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1028" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1029" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1030" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1031" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1032" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1033" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1034" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1035" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B12:I24"/>
+    <mergeCell ref="B47:I59"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B13" r:id="rId2" xr:uid="{B849A754-6091-FB40-B100-15350FE94C95}"/>
+    <hyperlink ref="B18" r:id="rId3" xr:uid="{B912C859-CB9B-EB44-82E7-1D3A68216806}"/>
+    <hyperlink ref="B23" r:id="rId4" xr:uid="{975F4FE7-D8E5-0540-8E2E-7C21F6D41974}"/>
+    <hyperlink ref="B28" r:id="rId5" xr:uid="{E32369E6-517E-DC43-B8DF-80DC041DCD36}"/>
+    <hyperlink ref="B33" r:id="rId6" xr:uid="{31D3C805-F505-AB40-AC7F-7C2BE018D12B}"/>
+    <hyperlink ref="B38" r:id="rId7" xr:uid="{B56265E6-1266-1644-8311-402A1FC2CD58}"/>
+    <hyperlink ref="B43" r:id="rId8" xr:uid="{ED1268E7-0774-8647-BC1C-DC9C87DB471F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -2549,11 +2939,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2564,14 +2954,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="93" t="s">
+      <c r="B3" s="85"/>
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="81"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -2642,14 +3032,14 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="95" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="81"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="12" t="s">
         <v>25</v>
       </c>
@@ -2731,12 +3121,12 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="84"/>
-      <c r="B5" s="85"/>
-      <c r="C5" s="95" t="s">
+      <c r="A5" s="88"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="81"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="12">
         <v>3</v>
       </c>
@@ -2815,14 +3205,14 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="95" t="s">
+      <c r="B6" s="85"/>
+      <c r="C6" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="81"/>
+      <c r="D6" s="85"/>
       <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
@@ -2901,14 +3291,14 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="95" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="12" t="s">
         <v>28</v>
       </c>
@@ -2987,12 +3377,12 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="84"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="95" t="s">
+      <c r="A8" s="88"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="81"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -3071,14 +3461,14 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="95" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="81"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="12" t="s">
         <v>32</v>
       </c>
@@ -3157,12 +3547,12 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="95" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="81"/>
+      <c r="D10" s="85"/>
       <c r="E10" s="12" t="s">
         <v>28</v>
       </c>
@@ -3241,12 +3631,12 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="87"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="95" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="81"/>
+      <c r="D11" s="85"/>
       <c r="E11" s="12" t="s">
         <v>28</v>
       </c>
@@ -3325,12 +3715,12 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="84"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="95" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="81"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="12" t="s">
         <v>28</v>
       </c>
@@ -3375,14 +3765,14 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="95" t="s">
+      <c r="B13" s="87"/>
+      <c r="C13" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="81"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="12" t="s">
         <v>37</v>
       </c>
@@ -3460,12 +3850,12 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="84"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="95" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="81"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="12">
         <v>3</v>
       </c>
@@ -3704,14 +4094,14 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="95" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="81"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
@@ -3751,12 +4141,12 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="84"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="95" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="81"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="12">
         <v>1</v>
       </c>
@@ -3799,14 +4189,14 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="95" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="81"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="12" t="s">
         <v>37</v>
       </c>
@@ -3859,12 +4249,12 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="87"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="95" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="81"/>
+      <c r="D20" s="85"/>
       <c r="E20" s="12" t="s">
         <v>37</v>
       </c>
@@ -3923,12 +4313,12 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="84"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="95" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="81"/>
+      <c r="D21" s="85"/>
       <c r="E21" s="12">
         <v>2</v>
       </c>
@@ -3987,14 +4377,14 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="95" t="s">
+      <c r="B22" s="85"/>
+      <c r="C22" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="81"/>
+      <c r="D22" s="85"/>
       <c r="E22" s="12">
         <v>2</v>
       </c>
@@ -4019,14 +4409,14 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="89" t="s">
+      <c r="A23" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="83"/>
-      <c r="C23" s="95" t="s">
+      <c r="B23" s="87"/>
+      <c r="C23" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="81"/>
+      <c r="D23" s="85"/>
       <c r="E23" s="12" t="s">
         <v>28</v>
       </c>
@@ -4051,12 +4441,12 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="87"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="96" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="81"/>
+      <c r="D24" s="85"/>
       <c r="E24" s="12">
         <v>3</v>
       </c>
@@ -4114,12 +4504,12 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="96" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="81"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="12">
         <v>3</v>
       </c>
@@ -4147,12 +4537,12 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="87"/>
-      <c r="B26" s="88"/>
-      <c r="C26" s="96" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="81"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="12">
         <v>3</v>
       </c>
@@ -4180,12 +4570,12 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="84"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="95" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="81"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="12">
         <v>3</v>
       </c>
@@ -4356,12 +4746,12 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="97" t="s">
+      <c r="F35" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="79"/>
-      <c r="H35" s="79"/>
-      <c r="I35" s="79"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27" t="s">
@@ -5061,12 +5451,12 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="98" t="s">
+      <c r="A53" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="76"/>
-      <c r="C53" s="76"/>
-      <c r="D53" s="77"/>
+      <c r="B53" s="80"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="81"/>
       <c r="E53" s="26" t="s">
         <v>10</v>
       </c>
@@ -5076,11 +5466,11 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="97" t="s">
+      <c r="F54" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
+      <c r="G54" s="83"/>
+      <c r="H54" s="83"/>
     </row>
     <row r="55" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27" t="s">
@@ -5868,12 +6258,12 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="99" t="s">
+      <c r="A70" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="76"/>
-      <c r="C70" s="76"/>
-      <c r="D70" s="77"/>
+      <c r="B70" s="80"/>
+      <c r="C70" s="80"/>
+      <c r="D70" s="81"/>
       <c r="E70" s="26" t="s">
         <v>10</v>
       </c>
@@ -7403,11 +7793,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="81"/>
       <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
@@ -7418,14 +7808,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="93" t="s">
+      <c r="B3" s="85"/>
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="81"/>
+      <c r="D3" s="85"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -7461,14 +7851,14 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="90" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="81"/>
+      <c r="D4" s="85"/>
       <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
@@ -7513,12 +7903,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="87"/>
-      <c r="B5" s="88"/>
-      <c r="C5" s="95" t="s">
+      <c r="A5" s="91"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="81"/>
+      <c r="D5" s="85"/>
       <c r="E5" s="12" t="s">
         <v>28</v>
       </c>
@@ -7563,12 +7953,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84"/>
-      <c r="B6" s="85"/>
-      <c r="C6" s="95" t="s">
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="81"/>
+      <c r="D6" s="85"/>
       <c r="E6" s="12">
         <v>1</v>
       </c>
@@ -7613,14 +8003,14 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="80" t="s">
+      <c r="A7" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="100" t="s">
+      <c r="B7" s="85"/>
+      <c r="C7" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="85"/>
       <c r="E7" s="12">
         <v>1</v>
       </c>
@@ -7665,14 +8055,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="82" t="s">
+      <c r="A8" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="83"/>
-      <c r="C8" s="100" t="s">
+      <c r="B8" s="87"/>
+      <c r="C8" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="81"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -7717,12 +8107,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="87"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="100" t="s">
+      <c r="A9" s="91"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="81"/>
+      <c r="D9" s="85"/>
       <c r="E9" s="12">
         <v>1</v>
       </c>
@@ -7767,12 +8157,12 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="84"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="95" t="s">
+      <c r="A10" s="88"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="81"/>
+      <c r="D10" s="85"/>
       <c r="E10" s="12">
         <v>1</v>
       </c>
@@ -7828,14 +8218,14 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="100" t="s">
+      <c r="B11" s="87"/>
+      <c r="C11" s="104" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="81"/>
+      <c r="D11" s="85"/>
       <c r="E11" s="12">
         <v>1</v>
       </c>
@@ -7880,12 +8270,12 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="87"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="100" t="s">
+      <c r="A12" s="91"/>
+      <c r="B12" s="92"/>
+      <c r="C12" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="81"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="12">
         <v>1</v>
       </c>
@@ -7930,12 +8320,12 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="87"/>
-      <c r="B13" s="88"/>
-      <c r="C13" s="100" t="s">
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
+      <c r="C13" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="81"/>
+      <c r="D13" s="85"/>
       <c r="E13" s="12">
         <v>1</v>
       </c>
@@ -7980,12 +8370,12 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="84"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="100" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="81"/>
+      <c r="D14" s="85"/>
       <c r="E14" s="12">
         <v>1</v>
       </c>
@@ -8122,25 +8512,25 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="100" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="81"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="84"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="100" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="81"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="12">
         <v>2</v>
       </c>
@@ -8149,14 +8539,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="83"/>
-      <c r="C19" s="100" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="81"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="12">
         <v>1</v>
       </c>
@@ -8174,12 +8564,12 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="84"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="95" t="s">
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="81"/>
+      <c r="D20" s="85"/>
       <c r="E20" s="12">
         <v>1</v>
       </c>
@@ -8200,14 +8590,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="89" t="s">
+      <c r="A21" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="83"/>
-      <c r="C21" s="95" t="s">
+      <c r="B21" s="87"/>
+      <c r="C21" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="81"/>
+      <c r="D21" s="85"/>
       <c r="E21" s="12" t="s">
         <v>28</v>
       </c>
@@ -8228,8 +8618,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="84"/>
-      <c r="B22" s="85"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8254,14 +8644,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="95" t="s">
+      <c r="B23" s="85"/>
+      <c r="C23" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="81"/>
+      <c r="D23" s="85"/>
       <c r="E23" s="12">
         <v>1</v>
       </c>
@@ -8282,14 +8672,14 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="89" t="s">
+      <c r="A24" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="95" t="s">
+      <c r="B24" s="87"/>
+      <c r="C24" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="81"/>
+      <c r="D24" s="85"/>
       <c r="E24" s="12">
         <v>1</v>
       </c>
@@ -8310,12 +8700,12 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="87"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="100" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="81"/>
+      <c r="D25" s="85"/>
       <c r="E25" s="12">
         <v>2</v>
       </c>
@@ -8336,12 +8726,12 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="87"/>
-      <c r="B26" s="88"/>
-      <c r="C26" s="96" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="81"/>
+      <c r="D26" s="85"/>
       <c r="E26" s="12">
         <v>2</v>
       </c>
@@ -8362,12 +8752,12 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="87"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="96" t="s">
+      <c r="A27" s="91"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="100" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="81"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="12">
         <v>2</v>
       </c>
@@ -8388,12 +8778,12 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="84"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="95" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="81"/>
+      <c r="D28" s="85"/>
       <c r="E28" s="12">
         <v>2</v>
       </c>
@@ -18419,6 +18809,157 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CDDCDD-446B-FA4F-B242-594ECC6C0CA3}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="65" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="54" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8">
+        <f>B7</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="54" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="B15">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17">
+        <v>0.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
@@ -18539,132 +19080,132 @@
         <v>126</v>
       </c>
       <c r="B2" s="64">
-        <f>'Capacity Factor Calculation'!Q2</f>
-        <v>0.67782537363300799</v>
+        <f>'Capacity Factor-Reports'!B2</f>
+        <v>0.65</v>
       </c>
       <c r="C2" s="64">
-        <f>'Capacity Factor Calculation'!Q2</f>
-        <v>0.67782537363300799</v>
+        <f>B2</f>
+        <v>0.65</v>
       </c>
       <c r="D2" s="64">
-        <f>'Capacity Factor Calculation'!R2</f>
-        <v>0.67966570922029579</v>
+        <f t="shared" ref="D2:AG10" si="0">C2</f>
+        <v>0.65</v>
       </c>
       <c r="E2" s="64">
-        <f>'Capacity Factor Calculation'!S2</f>
-        <v>0.68132093869389931</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="F2" s="64">
-        <f>'Capacity Factor Calculation'!T2</f>
-        <v>0.68281765251993087</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="G2" s="64">
-        <f>'Capacity Factor Calculation'!U2</f>
-        <v>0.68417758093293024</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="H2" s="64">
-        <f>'Capacity Factor Calculation'!V2</f>
-        <v>0.68541865585845485</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="I2" s="64">
-        <f>'Capacity Factor Calculation'!W2</f>
-        <v>0.68655580606689082</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="J2" s="64">
-        <f>'Capacity Factor Calculation'!X2</f>
-        <v>0.68760156060162037</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="K2" s="64">
-        <f>'Capacity Factor Calculation'!Y2</f>
-        <v>0.68856651233111088</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="L2" s="64">
-        <f>'Capacity Factor Calculation'!Z2</f>
-        <v>0.68945967804537156</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="M2" s="64">
-        <f>'Capacity Factor Calculation'!AA2</f>
-        <v>0.69028878106819402</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="N2" s="64">
-        <f>'Capacity Factor Calculation'!AB2</f>
-        <v>0.69106047516332147</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="O2" s="64">
-        <f>'Capacity Factor Calculation'!AC2</f>
-        <v>0.69178052348571284</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="P2" s="64">
-        <f>'Capacity Factor Calculation'!AD2</f>
-        <v>0.69245394276711425</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="Q2" s="64">
-        <f>'Capacity Factor Calculation'!AE2</f>
-        <v>0.69308512036859438</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="R2" s="64">
-        <f>'Capacity Factor Calculation'!AF2</f>
-        <v>0.69367790997578316</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="S2" s="64">
-        <f>'Capacity Factor Calculation'!AG2</f>
-        <v>0.69423571034896026</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="T2" s="64">
-        <f>'Capacity Factor Calculation'!AH2</f>
-        <v>0.69476153052829603</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="U2" s="64">
-        <f>'Capacity Factor Calculation'!AI2</f>
-        <v>0.69525804413644221</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="V2" s="64">
-        <f>'Capacity Factor Calculation'!AJ2</f>
-        <v>0.69572763484762945</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="W2" s="64">
-        <f>'Capacity Factor Calculation'!AK2</f>
-        <v>0.69617243465548662</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="X2" s="64">
-        <f>'Capacity Factor Calculation'!AL2</f>
-        <v>0.69659435623594479</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="Y2" s="64">
-        <f>'Capacity Factor Calculation'!AM2</f>
-        <v>0.69699512044159861</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="Z2" s="64">
-        <f>'Capacity Factor Calculation'!AN2</f>
-        <v>0.69737627976111316</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AA2" s="64">
-        <f>'Capacity Factor Calculation'!AO2</f>
-        <v>0.69773923841800067</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AB2" s="64">
-        <f>'Capacity Factor Calculation'!AP2</f>
-        <v>0.69808526965733764</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AC2" s="64">
-        <f>'Capacity Factor Calculation'!AQ2</f>
-        <v>0.69841553066899087</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AD2" s="64">
-        <f>'Capacity Factor Calculation'!AR2</f>
-        <v>0.69873107551593039</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AE2" s="64">
-        <f>'Capacity Factor Calculation'!AS2</f>
-        <v>0.69903286637198059</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AF2" s="64">
-        <f>'Capacity Factor Calculation'!AT2</f>
-        <v>0.69932178332143213</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
       <c r="AG2" s="64">
-        <f>'Capacity Factor Calculation'!AU2</f>
-        <v>0.69959863293072588</v>
+        <f t="shared" si="0"/>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18672,132 +19213,132 @@
         <v>127</v>
       </c>
       <c r="B3" s="64">
-        <f>'Capacity Factor Calculation'!Q3</f>
-        <v>0.46334270205422579</v>
+        <f>'Capacity Factor-Reports'!B3</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="C3" s="64">
-        <f>'Capacity Factor Calculation'!Q3</f>
-        <v>0.46334270205422579</v>
+        <f t="shared" ref="C3:R17" si="1">B3</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D3" s="64">
-        <f>'Capacity Factor Calculation'!R3</f>
-        <v>0.47230130396568493</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E3" s="64">
-        <f>'Capacity Factor Calculation'!S3</f>
-        <v>0.48090540931570031</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F3" s="64">
-        <f>'Capacity Factor Calculation'!T3</f>
-        <v>0.48917565129265556</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G3" s="64">
-        <f>'Capacity Factor Calculation'!U3</f>
-        <v>0.49713109230926311</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H3" s="64">
-        <f>'Capacity Factor Calculation'!V3</f>
-        <v>0.50478937068699459</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I3" s="64">
-        <f>'Capacity Factor Calculation'!W3</f>
-        <v>0.51216683120445228</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J3" s="64">
-        <f>'Capacity Factor Calculation'!X3</f>
-        <v>0.51927864154324566</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K3" s="64">
-        <f>'Capacity Factor Calculation'!Y3</f>
-        <v>0.52613889637721789</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L3" s="64">
-        <f>'Capacity Factor Calculation'!Z3</f>
-        <v>0.53276071060829144</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M3" s="64">
-        <f>'Capacity Factor Calculation'!AA3</f>
-        <v>0.5391563030466322</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N3" s="64">
-        <f>'Capacity Factor Calculation'!AB3</f>
-        <v>0.54533707165847944</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O3" s="64">
-        <f>'Capacity Factor Calculation'!AC3</f>
-        <v>0.55131366135668725</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P3" s="64">
-        <f>'Capacity Factor Calculation'!AD3</f>
-        <v>0.5570960251821393</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q3" s="64">
-        <f>'Capacity Factor Calculation'!AE3</f>
-        <v>0.56269347961571159</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R3" s="64">
-        <f>'Capacity Factor Calculation'!AF3</f>
-        <v>0.56811475466746209</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S3" s="64">
-        <f>'Capacity Factor Calculation'!AG3</f>
-        <v>0.57336803930944047</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T3" s="64">
-        <f>'Capacity Factor Calculation'!AH3</f>
-        <v>0.57846102274938105</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="U3" s="64">
-        <f>'Capacity Factor Calculation'!AI3</f>
-        <v>0.58340093198288456</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V3" s="64">
-        <f>'Capacity Factor Calculation'!AJ3</f>
-        <v>0.58819456600973596</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W3" s="64">
-        <f>'Capacity Factor Calculation'!AK3</f>
-        <v>0.59284832705499801</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X3" s="64">
-        <f>'Capacity Factor Calculation'!AL3</f>
-        <v>0.59736824909645314</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y3" s="64">
-        <f>'Capacity Factor Calculation'!AM3</f>
-        <v>0.60176002396564587</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z3" s="64">
-        <f>'Capacity Factor Calculation'!AN3</f>
-        <v>0.60602902525989633</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA3" s="64">
-        <f>'Capacity Factor Calculation'!AO3</f>
-        <v>0.61018033027659013</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB3" s="64">
-        <f>'Capacity Factor Calculation'!AP3</f>
-        <v>0.61421874015795352</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AC3" s="64">
-        <f>'Capacity Factor Calculation'!AQ3</f>
-        <v>0.61814879841432158</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AD3" s="64">
-        <f>'Capacity Factor Calculation'!AR3</f>
-        <v>0.62197480797622773</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AE3" s="64">
-        <f>'Capacity Factor Calculation'!AS3</f>
-        <v>0.62570084690981886</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AF3" s="64">
-        <f>'Capacity Factor Calculation'!AT3</f>
-        <v>0.62933078291622802</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AG3" s="64">
-        <f>'Capacity Factor Calculation'!AU3</f>
-        <v>0.6328682867233516</v>
+        <f t="shared" si="0"/>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18805,132 +19346,132 @@
         <v>128</v>
       </c>
       <c r="B4" s="64">
-        <f>'Capacity Factor Calculation'!Q4</f>
-        <v>0.46334270205422579</v>
+        <f>'Capacity Factor-Reports'!B4</f>
+        <v>0.45</v>
       </c>
       <c r="C4" s="64">
-        <f>'Capacity Factor Calculation'!Q4</f>
-        <v>0.46334270205422579</v>
+        <f t="shared" si="1"/>
+        <v>0.45</v>
       </c>
       <c r="D4" s="64">
-        <f>'Capacity Factor Calculation'!R4</f>
-        <v>0.47230130396568493</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="E4" s="64">
-        <f>'Capacity Factor Calculation'!S4</f>
-        <v>0.48090540931570031</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="F4" s="64">
-        <f>'Capacity Factor Calculation'!T4</f>
-        <v>0.48917565129265556</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="G4" s="64">
-        <f>'Capacity Factor Calculation'!U4</f>
-        <v>0.49713109230926311</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="H4" s="64">
-        <f>'Capacity Factor Calculation'!V4</f>
-        <v>0.50478937068699459</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="I4" s="64">
-        <f>'Capacity Factor Calculation'!W4</f>
-        <v>0.51216683120445228</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="J4" s="64">
-        <f>'Capacity Factor Calculation'!X4</f>
-        <v>0.51927864154324566</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="K4" s="64">
-        <f>'Capacity Factor Calculation'!Y4</f>
-        <v>0.52613889637721789</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="L4" s="64">
-        <f>'Capacity Factor Calculation'!Z4</f>
-        <v>0.53276071060829144</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="M4" s="64">
-        <f>'Capacity Factor Calculation'!AA4</f>
-        <v>0.5391563030466322</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="N4" s="64">
-        <f>'Capacity Factor Calculation'!AB4</f>
-        <v>0.54533707165847944</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="O4" s="64">
-        <f>'Capacity Factor Calculation'!AC4</f>
-        <v>0.55131366135668725</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="P4" s="64">
-        <f>'Capacity Factor Calculation'!AD4</f>
-        <v>0.5570960251821393</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="Q4" s="64">
-        <f>'Capacity Factor Calculation'!AE4</f>
-        <v>0.56269347961571159</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="R4" s="64">
-        <f>'Capacity Factor Calculation'!AF4</f>
-        <v>0.56811475466746209</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="S4" s="64">
-        <f>'Capacity Factor Calculation'!AG4</f>
-        <v>0.57336803930944047</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="T4" s="64">
-        <f>'Capacity Factor Calculation'!AH4</f>
-        <v>0.57846102274938105</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="U4" s="64">
-        <f>'Capacity Factor Calculation'!AI4</f>
-        <v>0.58340093198288456</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="V4" s="64">
-        <f>'Capacity Factor Calculation'!AJ4</f>
-        <v>0.58819456600973596</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="W4" s="64">
-        <f>'Capacity Factor Calculation'!AK4</f>
-        <v>0.59284832705499801</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="X4" s="64">
-        <f>'Capacity Factor Calculation'!AL4</f>
-        <v>0.59736824909645314</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="Y4" s="64">
-        <f>'Capacity Factor Calculation'!AM4</f>
-        <v>0.60176002396564587</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="Z4" s="64">
-        <f>'Capacity Factor Calculation'!AN4</f>
-        <v>0.60602902525989633</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="64">
-        <f>'Capacity Factor Calculation'!AO4</f>
-        <v>0.61018033027659013</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AB4" s="64">
-        <f>'Capacity Factor Calculation'!AP4</f>
-        <v>0.61421874015795352</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AC4" s="64">
-        <f>'Capacity Factor Calculation'!AQ4</f>
-        <v>0.61814879841432158</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AD4" s="64">
-        <f>'Capacity Factor Calculation'!AR4</f>
-        <v>0.62197480797622773</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AE4" s="64">
-        <f>'Capacity Factor Calculation'!AS4</f>
-        <v>0.62570084690981886</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AF4" s="64">
-        <f>'Capacity Factor Calculation'!AT4</f>
-        <v>0.62933078291622802</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
       <c r="AG4" s="64">
-        <f>'Capacity Factor Calculation'!AU4</f>
-        <v>0.6328682867233516</v>
+        <f t="shared" si="0"/>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18938,132 +19479,132 @@
         <v>15</v>
       </c>
       <c r="B5" s="64">
-        <f>'Capacity Factor Calculation'!Q5</f>
-        <v>0.42471073854961994</v>
+        <f>'Capacity Factor-Reports'!B5</f>
+        <v>0.37</v>
       </c>
       <c r="C5" s="64">
-        <f>'Capacity Factor Calculation'!Q5</f>
-        <v>0.42471073854961994</v>
+        <f t="shared" si="1"/>
+        <v>0.37</v>
       </c>
       <c r="D5" s="64">
-        <f>'Capacity Factor Calculation'!R5</f>
-        <v>0.42670006553791556</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="E5" s="64">
-        <f>'Capacity Factor Calculation'!S5</f>
-        <v>0.42857964718299035</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="F5" s="64">
-        <f>'Capacity Factor Calculation'!T5</f>
-        <v>0.43035832120303452</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="G5" s="64">
-        <f>'Capacity Factor Calculation'!U5</f>
-        <v>0.43204400119526082</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="H5" s="64">
-        <f>'Capacity Factor Calculation'!V5</f>
-        <v>0.43364379434774014</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="I5" s="64">
-        <f>'Capacity Factor Calculation'!W5</f>
-        <v>0.4351641016057391</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="J5" s="64">
-        <f>'Capacity Factor Calculation'!X5</f>
-        <v>0.43661070326964907</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="K5" s="64">
-        <f>'Capacity Factor Calculation'!Y5</f>
-        <v>0.43798883243793135</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="L5" s="64">
-        <f>'Capacity Factor Calculation'!Z5</f>
-        <v>0.43930323826234552</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="M5" s="64">
-        <f>'Capacity Factor Calculation'!AA5</f>
-        <v>0.44055824062687848</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="N5" s="64">
-        <f>'Capacity Factor Calculation'!AB5</f>
-        <v>0.44175777757692092</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="O5" s="64">
-        <f>'Capacity Factor Calculation'!AC5</f>
-        <v>0.44290544659600523</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="P5" s="64">
-        <f>'Capacity Factor Calculation'!AD5</f>
-        <v>0.44400454064144224</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="Q5" s="64">
-        <f>'Capacity Factor Calculation'!AE5</f>
-        <v>0.44505807969910294</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="R5" s="64">
-        <f>'Capacity Factor Calculation'!AF5</f>
-        <v>0.44606883849430101</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="S5" s="64">
-        <f>'Capacity Factor Calculation'!AG5</f>
-        <v>0.44703937089414475</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="T5" s="64">
-        <f>'Capacity Factor Calculation'!AH5</f>
-        <v>0.44797203145316167</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="U5" s="64">
-        <f>'Capacity Factor Calculation'!AI5</f>
-        <v>0.44886899448501155</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="V5" s="64">
-        <f>'Capacity Factor Calculation'!AJ5</f>
-        <v>0.44973227098541613</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="W5" s="64">
-        <f>'Capacity Factor Calculation'!AK5</f>
-        <v>0.45056372368348974</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="X5" s="64">
-        <f>'Capacity Factor Calculation'!AL5</f>
-        <v>0.45136508045869939</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="Y5" s="64">
-        <f>'Capacity Factor Calculation'!AM5</f>
-        <v>0.45213794632677035</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="Z5" s="64">
-        <f>'Capacity Factor Calculation'!AN5</f>
-        <v>0.45288381416944878</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AA5" s="64">
-        <f>'Capacity Factor Calculation'!AO5</f>
-        <v>0.4536040743591746</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AB5" s="64">
-        <f>'Capacity Factor Calculation'!AP5</f>
-        <v>0.45430002340916098</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AC5" s="64">
-        <f>'Capacity Factor Calculation'!AQ5</f>
-        <v>0.45497287176205242</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AD5" s="64">
-        <f>'Capacity Factor Calculation'!AR5</f>
-        <v>0.45562375081570877</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AE5" s="64">
-        <f>'Capacity Factor Calculation'!AS5</f>
-        <v>0.45625371927184288</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AF5" s="64">
-        <f>'Capacity Factor Calculation'!AT5</f>
-        <v>0.45686376888239838</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
       <c r="AG5" s="64">
-        <f>'Capacity Factor Calculation'!AU5</f>
-        <v>0.45745482965938111</v>
+        <f t="shared" si="0"/>
+        <v>0.37</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19071,132 +19612,132 @@
         <v>129</v>
       </c>
       <c r="B6" s="64">
-        <f>'Capacity Factor Calculation'!Q6</f>
-        <v>0.19089506879858689</v>
+        <f>'Capacity Factor-Reports'!B6</f>
+        <v>0.35</v>
       </c>
       <c r="C6" s="64">
-        <f>'Capacity Factor Calculation'!Q6</f>
-        <v>0.19089506879858689</v>
+        <f t="shared" si="1"/>
+        <v>0.35</v>
       </c>
       <c r="D6" s="64">
-        <f>'Capacity Factor Calculation'!R6</f>
-        <v>0.19048075744739912</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="E6" s="64">
-        <f>'Capacity Factor Calculation'!S6</f>
-        <v>0.190160325233211</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="F6" s="64">
-        <f>'Capacity Factor Calculation'!T6</f>
-        <v>0.18990511109979744</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="G6" s="64">
-        <f>'Capacity Factor Calculation'!U6</f>
-        <v>0.18969704322974223</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="H6" s="64">
-        <f>'Capacity Factor Calculation'!V6</f>
-        <v>0.18952416212690099</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="I6" s="64">
-        <f>'Capacity Factor Calculation'!W6</f>
-        <v>0.18937823792084044</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="J6" s="64">
-        <f>'Capacity Factor Calculation'!X6</f>
-        <v>0.1892534216415441</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="K6" s="64">
-        <f>'Capacity Factor Calculation'!Y6</f>
-        <v>0.18914544229798283</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="L6" s="64">
-        <f>'Capacity Factor Calculation'!Z6</f>
-        <v>0.18905110835329414</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="M6" s="64">
-        <f>'Capacity Factor Calculation'!AA6</f>
-        <v>0.18896798696430725</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="N6" s="64">
-        <f>'Capacity Factor Calculation'!AB6</f>
-        <v>0.18889419118197412</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="O6" s="64">
-        <f>'Capacity Factor Calculation'!AC6</f>
-        <v>0.1888282349709906</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="P6" s="64">
-        <f>'Capacity Factor Calculation'!AD6</f>
-        <v>0.18876893210417986</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="Q6" s="64">
-        <f>'Capacity Factor Calculation'!AE6</f>
-        <v>0.18871532418489448</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="R6" s="64">
-        <f>'Capacity Factor Calculation'!AF6</f>
-        <v>0.18866662845570523</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="S6" s="64">
-        <f>'Capacity Factor Calculation'!AG6</f>
-        <v>0.18862219932571028</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="T6" s="64">
-        <f>'Capacity Factor Calculation'!AH6</f>
-        <v>0.18858149958608286</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="U6" s="64">
-        <f>'Capacity Factor Calculation'!AI6</f>
-        <v>0.18854407858214964</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="V6" s="64">
-        <f>'Capacity Factor Calculation'!AJ6</f>
-        <v>0.18850955545652448</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="W6" s="64">
-        <f>'Capacity Factor Calculation'!AK6</f>
-        <v>0.18847760614009484</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="X6" s="64">
-        <f>'Capacity Factor Calculation'!AL6</f>
-        <v>0.18844795314801843</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="Y6" s="64">
-        <f>'Capacity Factor Calculation'!AM6</f>
-        <v>0.18842035749960068</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="Z6" s="64">
-        <f>'Capacity Factor Calculation'!AN6</f>
-        <v>0.18839461226361512</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AA6" s="64">
-        <f>'Capacity Factor Calculation'!AO6</f>
-        <v>0.18837053735993203</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AB6" s="64">
-        <f>'Capacity Factor Calculation'!AP6</f>
-        <v>0.1883479753411558</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AC6" s="64">
-        <f>'Capacity Factor Calculation'!AQ6</f>
-        <v>0.1883267879453068</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AD6" s="64">
-        <f>'Capacity Factor Calculation'!AR6</f>
-        <v>0.18830685325995919</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AE6" s="64">
-        <f>'Capacity Factor Calculation'!AS6</f>
-        <v>0.18828806337494855</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AF6" s="64">
-        <f>'Capacity Factor Calculation'!AT6</f>
-        <v>0.18827032242820382</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
       <c r="AG6" s="64">
-        <f>'Capacity Factor Calculation'!AU6</f>
-        <v>0.18825354496995095</v>
+        <f t="shared" si="0"/>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19204,132 +19745,132 @@
         <v>23</v>
       </c>
       <c r="B7" s="64">
-        <f>'Capacity Factor Calculation'!Q7</f>
-        <v>8.1335616438358793E-2</v>
+        <f>'Capacity Factor-Reports'!B7</f>
+        <v>0.2</v>
       </c>
       <c r="C7" s="64">
-        <f>'Capacity Factor Calculation'!Q7</f>
-        <v>8.1335616438358793E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.2</v>
       </c>
       <c r="D7" s="64">
-        <f>'Capacity Factor Calculation'!R7</f>
-        <v>7.9500978473582562E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="E7" s="64">
-        <f>'Capacity Factor Calculation'!S7</f>
-        <v>7.8021431727795298E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="F7" s="64">
-        <f>'Capacity Factor Calculation'!T7</f>
-        <v>7.6802981466561074E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="G7" s="64">
-        <f>'Capacity Factor Calculation'!U7</f>
-        <v>7.5782117734173524E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="H7" s="64">
-        <f>'Capacity Factor Calculation'!V7</f>
-        <v>7.4914383561644107E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="I7" s="64">
-        <f>'Capacity Factor Calculation'!W7</f>
-        <v>7.4167728575981043E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="J7" s="64">
-        <f>'Capacity Factor Calculation'!X7</f>
-        <v>7.3518463371054985E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="K7" s="64">
-        <f>'Capacity Factor Calculation'!Y7</f>
-        <v>7.2948700027956614E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="L7" s="64">
-        <f>'Capacity Factor Calculation'!Z7</f>
-        <v>7.244467860906334E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="M7" s="64">
-        <f>'Capacity Factor Calculation'!AA7</f>
-        <v>7.1995641344957062E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="N7" s="64">
-        <f>'Capacity Factor Calculation'!AB7</f>
-        <v>7.1593056211620418E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="O7" s="64">
-        <f>'Capacity Factor Calculation'!AC7</f>
-        <v>7.123006961599021E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="P7" s="64">
-        <f>'Capacity Factor Calculation'!AD7</f>
-        <v>7.0901113013699196E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="64">
-        <f>'Capacity Factor Calculation'!AE7</f>
-        <v>7.0601615211613344E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="R7" s="64">
-        <f>'Capacity Factor Calculation'!AF7</f>
-        <v>7.0327788649707318E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="S7" s="64">
-        <f>'Capacity Factor Calculation'!AG7</f>
-        <v>7.0076468380559698E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="T7" s="64">
-        <f>'Capacity Factor Calculation'!AH7</f>
-        <v>6.9844989185292153E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="U7" s="64">
-        <f>'Capacity Factor Calculation'!AI7</f>
-        <v>6.9631090688400274E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="V7" s="64">
-        <f>'Capacity Factor Calculation'!AJ7</f>
-        <v>6.943284330103619E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="W7" s="64">
-        <f>'Capacity Factor Calculation'!AK7</f>
-        <v>6.9248589846897801E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="X7" s="64">
-        <f>'Capacity Factor Calculation'!AL7</f>
-        <v>6.907689912826967E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Y7" s="64">
-        <f>'Capacity Factor Calculation'!AM7</f>
-        <v>6.8916528676803049E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Z7" s="64">
-        <f>'Capacity Factor Calculation'!AN7</f>
-        <v>6.8766394637132161E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AA7" s="64">
-        <f>'Capacity Factor Calculation'!AO7</f>
-        <v>6.8625547239091131E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AB7" s="64">
-        <f>'Capacity Factor Calculation'!AP7</f>
-        <v>6.8493150684931864E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AC7" s="64">
-        <f>'Capacity Factor Calculation'!AQ7</f>
-        <v>6.8368466551403231E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AD7" s="64">
-        <f>'Capacity Factor Calculation'!AR7</f>
-        <v>6.8250840010339139E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AE7" s="64">
-        <f>'Capacity Factor Calculation'!AS7</f>
-        <v>6.8139688324745831E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AF7" s="64">
-        <f>'Capacity Factor Calculation'!AT7</f>
-        <v>6.8034491193737875E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AG7" s="64">
-        <f>'Capacity Factor Calculation'!AU7</f>
-        <v>6.7934782608696162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19337,132 +19878,132 @@
         <v>130</v>
       </c>
       <c r="B8" s="64">
-        <f>'Capacity Factor Calculation'!Q8</f>
-        <v>8.1335616438358793E-2</v>
+        <f>'Capacity Factor-Reports'!B8</f>
+        <v>0.2</v>
       </c>
       <c r="C8" s="64">
-        <f>'Capacity Factor Calculation'!Q8</f>
-        <v>8.1335616438358793E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.2</v>
       </c>
       <c r="D8" s="64">
-        <f>'Capacity Factor Calculation'!R8</f>
-        <v>7.9500978473582562E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="E8" s="64">
-        <f>'Capacity Factor Calculation'!S8</f>
-        <v>7.8021431727795298E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="F8" s="64">
-        <f>'Capacity Factor Calculation'!T8</f>
-        <v>7.6802981466561074E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="G8" s="64">
-        <f>'Capacity Factor Calculation'!U8</f>
-        <v>7.5782117734173524E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="H8" s="64">
-        <f>'Capacity Factor Calculation'!V8</f>
-        <v>7.4914383561644107E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="I8" s="64">
-        <f>'Capacity Factor Calculation'!W8</f>
-        <v>7.4167728575981043E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="J8" s="64">
-        <f>'Capacity Factor Calculation'!X8</f>
-        <v>7.3518463371054985E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="K8" s="64">
-        <f>'Capacity Factor Calculation'!Y8</f>
-        <v>7.2948700027956614E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="L8" s="64">
-        <f>'Capacity Factor Calculation'!Z8</f>
-        <v>7.244467860906334E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="M8" s="64">
-        <f>'Capacity Factor Calculation'!AA8</f>
-        <v>7.1995641344957062E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="N8" s="64">
-        <f>'Capacity Factor Calculation'!AB8</f>
-        <v>7.1593056211620418E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="O8" s="64">
-        <f>'Capacity Factor Calculation'!AC8</f>
-        <v>7.123006961599021E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="P8" s="64">
-        <f>'Capacity Factor Calculation'!AD8</f>
-        <v>7.0901113013699196E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="64">
-        <f>'Capacity Factor Calculation'!AE8</f>
-        <v>7.0601615211613344E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="R8" s="64">
-        <f>'Capacity Factor Calculation'!AF8</f>
-        <v>7.0327788649707318E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="S8" s="64">
-        <f>'Capacity Factor Calculation'!AG8</f>
-        <v>7.0076468380559698E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="T8" s="64">
-        <f>'Capacity Factor Calculation'!AH8</f>
-        <v>6.9844989185292153E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="U8" s="64">
-        <f>'Capacity Factor Calculation'!AI8</f>
-        <v>6.9631090688400274E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="V8" s="64">
-        <f>'Capacity Factor Calculation'!AJ8</f>
-        <v>6.943284330103619E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="W8" s="64">
-        <f>'Capacity Factor Calculation'!AK8</f>
-        <v>6.9248589846897801E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="X8" s="64">
-        <f>'Capacity Factor Calculation'!AL8</f>
-        <v>6.907689912826967E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Y8" s="64">
-        <f>'Capacity Factor Calculation'!AM8</f>
-        <v>6.8916528676803049E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="Z8" s="64">
-        <f>'Capacity Factor Calculation'!AN8</f>
-        <v>6.8766394637132161E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AA8" s="64">
-        <f>'Capacity Factor Calculation'!AO8</f>
-        <v>6.8625547239091131E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AB8" s="64">
-        <f>'Capacity Factor Calculation'!AP8</f>
-        <v>6.8493150684931864E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AC8" s="64">
-        <f>'Capacity Factor Calculation'!AQ8</f>
-        <v>6.8368466551403231E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AD8" s="64">
-        <f>'Capacity Factor Calculation'!AR8</f>
-        <v>6.8250840010339139E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AE8" s="64">
-        <f>'Capacity Factor Calculation'!AS8</f>
-        <v>6.8139688324745831E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AF8" s="64">
-        <f>'Capacity Factor Calculation'!AT8</f>
-        <v>6.8034491193737875E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
       <c r="AG8" s="64">
-        <f>'Capacity Factor Calculation'!AU8</f>
-        <v>6.7934782608696162E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19470,132 +20011,132 @@
         <v>21</v>
       </c>
       <c r="B9" s="64">
-        <f>'Capacity Factor Calculation'!Q9</f>
-        <v>0.4468599033816501</v>
+        <f>'Capacity Factor-Reports'!B9</f>
+        <v>0.5</v>
       </c>
       <c r="C9" s="64">
-        <f>'Capacity Factor Calculation'!Q9</f>
-        <v>0.4468599033816501</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="D9" s="64">
-        <f>'Capacity Factor Calculation'!R9</f>
-        <v>0.4408734340241256</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="E9" s="64">
-        <f>'Capacity Factor Calculation'!S9</f>
-        <v>0.43612554453367519</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="F9" s="64">
-        <f>'Capacity Factor Calculation'!T9</f>
-        <v>0.4322678843226842</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="G9" s="64">
-        <f>'Capacity Factor Calculation'!U9</f>
-        <v>0.42907153729072023</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="H9" s="64">
-        <f>'Capacity Factor Calculation'!V9</f>
-        <v>0.42637987663222426</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="I9" s="64">
-        <f>'Capacity Factor Calculation'!W9</f>
-        <v>0.42408211753350822</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="J9" s="64">
-        <f>'Capacity Factor Calculation'!X9</f>
-        <v>0.42209768922098073</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="K9" s="64">
-        <f>'Capacity Factor Calculation'!Y9</f>
-        <v>0.42036659218239292</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="L9" s="64">
-        <f>'Capacity Factor Calculation'!Z9</f>
-        <v>0.41884322678843561</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="M9" s="64">
-        <f>'Capacity Factor Calculation'!AA9</f>
-        <v>0.41749231785417162</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="N9" s="64">
-        <f>'Capacity Factor Calculation'!AB9</f>
-        <v>0.41628614916286444</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="O9" s="64">
-        <f>'Capacity Factor Calculation'!AC9</f>
-        <v>0.41520264169440213</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="P9" s="64">
-        <f>'Capacity Factor Calculation'!AD9</f>
-        <v>0.41422398978740388</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="Q9" s="64">
-        <f>'Capacity Factor Calculation'!AE9</f>
-        <v>0.41333567497951312</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="R9" s="64">
-        <f>'Capacity Factor Calculation'!AF9</f>
-        <v>0.41252574088996574</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="S9" s="64">
-        <f>'Capacity Factor Calculation'!AG9</f>
-        <v>0.41178425193474621</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="T9" s="64">
-        <f>'Capacity Factor Calculation'!AH9</f>
-        <v>0.41110288370562564</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="U9" s="64">
-        <f>'Capacity Factor Calculation'!AI9</f>
-        <v>0.4104746091047482</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="V9" s="64">
-        <f>'Capacity Factor Calculation'!AJ9</f>
-        <v>0.40989345509893654</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="W9" s="64">
-        <f>'Capacity Factor Calculation'!AK9</f>
-        <v>0.40935431222607521</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="X9" s="64">
-        <f>'Capacity Factor Calculation'!AL9</f>
-        <v>0.40885278397225067</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="Y9" s="64">
-        <f>'Capacity Factor Calculation'!AM9</f>
-        <v>0.40838506661194235</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="Z9" s="64">
-        <f>'Capacity Factor Calculation'!AN9</f>
-        <v>0.40794785255774113</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AA9" s="64">
-        <f>'Capacity Factor Calculation'!AO9</f>
-        <v>0.40753825202275262</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AB9" s="64">
-        <f>'Capacity Factor Calculation'!AP9</f>
-        <v>0.40715372907153891</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AC9" s="64">
-        <f>'Capacity Factor Calculation'!AQ9</f>
-        <v>0.4067920490679221</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AD9" s="64">
-        <f>'Capacity Factor Calculation'!AR9</f>
-        <v>0.40645123521836007</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AE9" s="64">
-        <f>'Capacity Factor Calculation'!AS9</f>
-        <v>0.40612953242578281</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AF9" s="64">
-        <f>'Capacity Factor Calculation'!AT9</f>
-        <v>0.40582537705825522</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="AG9" s="64">
-        <f>'Capacity Factor Calculation'!AU9</f>
-        <v>0.40553737153325126</v>
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19603,132 +20144,132 @@
         <v>16</v>
       </c>
       <c r="B10" s="64">
-        <f>'Capacity Factor Calculation'!Q10</f>
-        <v>0.70817828411633454</v>
+        <f>'Capacity Factor-Reports'!B10</f>
+        <v>0.82</v>
       </c>
       <c r="C10" s="64">
-        <f>'Capacity Factor Calculation'!Q10</f>
-        <v>0.70817828411633454</v>
+        <f t="shared" si="1"/>
+        <v>0.82</v>
       </c>
       <c r="D10" s="64">
-        <f>'Capacity Factor Calculation'!R10</f>
-        <v>0.695153888370318</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="E10" s="64">
-        <f>'Capacity Factor Calculation'!S10</f>
-        <v>0.6835736832052709</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="F10" s="64">
-        <f>'Capacity Factor Calculation'!T10</f>
-        <v>0.67321008111225944</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="G10" s="64">
-        <f>'Capacity Factor Calculation'!U10</f>
-        <v>0.6638809281485365</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="H10" s="64">
-        <f>'Capacity Factor Calculation'!V10</f>
-        <v>0.65543870542125116</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="I10" s="64">
-        <f>'Capacity Factor Calculation'!W10</f>
-        <v>0.64776267068336491</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="J10" s="64">
-        <f>'Capacity Factor Calculation'!X10</f>
-        <v>0.64075304666001498</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="K10" s="64">
-        <f>'Capacity Factor Calculation'!Y10</f>
-        <v>0.63432666005974137</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="L10" s="64">
-        <f>'Capacity Factor Calculation'!Z10</f>
-        <v>0.62841362567858994</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="M10" s="64">
-        <f>'Capacity Factor Calculation'!AA10</f>
-        <v>0.62295479462506265</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="N10" s="64">
-        <f>'Capacity Factor Calculation'!AB10</f>
-        <v>0.61789976883109354</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="O10" s="64">
-        <f>'Capacity Factor Calculation'!AC10</f>
-        <v>0.61320534046440445</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="P10" s="64">
-        <f>'Capacity Factor Calculation'!AD10</f>
-        <v>0.60883425381020517</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="Q10" s="64">
-        <f>'Capacity Factor Calculation'!AE10</f>
-        <v>0.60475421447181665</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="R10" s="64">
-        <f>'Capacity Factor Calculation'!AF10</f>
-        <v>0.60093709011074936</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="S10" s="64">
-        <f>'Capacity Factor Calculation'!AG10</f>
-        <v>0.59735826087517918</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="T10" s="64">
-        <f>'Capacity Factor Calculation'!AH10</f>
-        <v>0.59399608780012902</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="U10" s="64">
-        <f>'Capacity Factor Calculation'!AI10</f>
-        <v>0.59083147491766075</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="V10" s="64">
-        <f>'Capacity Factor Calculation'!AJ10</f>
-        <v>0.58784750635473082</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="W10" s="64">
-        <f>'Capacity Factor Calculation'!AK10</f>
-        <v>0.58502914385261118</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="X10" s="64">
-        <f>'Capacity Factor Calculation'!AL10</f>
-        <v>0.58236297328838782</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="Y10" s="64">
-        <f>'Capacity Factor Calculation'!AM10</f>
-        <v>0.57983699118050303</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="Z10" s="64">
-        <f>'Capacity Factor Calculation'!AN10</f>
-        <v>0.57744042400840934</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AA10" s="64">
-        <f>'Capacity Factor Calculation'!AO10</f>
-        <v>0.57516357460936229</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AB10" s="64">
-        <f>'Capacity Factor Calculation'!AP10</f>
-        <v>0.57299769103349163</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AC10" s="64">
-        <f>'Capacity Factor Calculation'!AQ10</f>
-        <v>0.57093485411730271</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AD10" s="64">
-        <f>'Capacity Factor Calculation'!AR10</f>
-        <v>0.56896788073121796</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AE10" s="64">
-        <f>'Capacity Factor Calculation'!AS10</f>
-        <v>0.56709024020956622</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AF10" s="64">
-        <f>'Capacity Factor Calculation'!AT10</f>
-        <v>0.56529598191401242</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
       <c r="AG10" s="64">
-        <f>'Capacity Factor Calculation'!AU10</f>
-        <v>0.56357967223773575</v>
+        <f t="shared" si="0"/>
+        <v>0.82</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19736,132 +20277,132 @@
         <v>131</v>
       </c>
       <c r="B11" s="64">
-        <f>'Capacity Factor Calculation'!Q11</f>
-        <v>8.3496071984080808E-2</v>
+        <f>'Capacity Factor-Reports'!B11</f>
+        <v>0.7</v>
       </c>
       <c r="C11" s="64">
-        <f>'Capacity Factor Calculation'!Q11</f>
-        <v>8.3496071984080808E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.7</v>
       </c>
       <c r="D11" s="64">
-        <f>'Capacity Factor Calculation'!R11</f>
-        <v>3.1828746187346255E-2</v>
+        <f t="shared" ref="D11:AG17" si="2">C11</f>
+        <v>0.7</v>
       </c>
       <c r="E11" s="64">
-        <f>'Capacity Factor Calculation'!S11</f>
-        <v>3.179041369494881E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="F11" s="64">
-        <f>'Capacity Factor Calculation'!T11</f>
-        <v>3.1752173421859459E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="G11" s="64">
-        <f>'Capacity Factor Calculation'!U11</f>
-        <v>3.1714025035689826E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="H11" s="64">
-        <f>'Capacity Factor Calculation'!V11</f>
-        <v>3.1675968205646998E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="I11" s="64">
-        <f>'Capacity Factor Calculation'!W11</f>
-        <v>3.1638002602523967E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="J11" s="64">
-        <f>'Capacity Factor Calculation'!X11</f>
-        <v>3.1600127898690142E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="K11" s="64">
-        <f>'Capacity Factor Calculation'!Y11</f>
-        <v>3.1562343768081903E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="L11" s="64">
-        <f>'Capacity Factor Calculation'!Z11</f>
-        <v>3.1524649886193266E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="M11" s="64">
-        <f>'Capacity Factor Calculation'!AA11</f>
-        <v>3.1487045930066598E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="N11" s="64">
-        <f>'Capacity Factor Calculation'!AB11</f>
-        <v>3.1449531578283355E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="O11" s="64">
-        <f>'Capacity Factor Calculation'!AC11</f>
-        <v>3.1412106510954975E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="P11" s="64">
-        <f>'Capacity Factor Calculation'!AD11</f>
-        <v>3.1374770409713745E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Q11" s="64">
-        <f>'Capacity Factor Calculation'!AE11</f>
-        <v>3.1337522957703798E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="R11" s="64">
-        <f>'Capacity Factor Calculation'!AF11</f>
-        <v>3.1300363839572132E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="S11" s="64">
-        <f>'Capacity Factor Calculation'!AG11</f>
-        <v>3.1263292741459725E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="T11" s="64">
-        <f>'Capacity Factor Calculation'!AH11</f>
-        <v>3.1226309350992701E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="U11" s="64">
-        <f>'Capacity Factor Calculation'!AI11</f>
-        <v>3.1189413357273529E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="V11" s="64">
-        <f>'Capacity Factor Calculation'!AJ11</f>
-        <v>3.115260445087234E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="W11" s="64">
-        <f>'Capacity Factor Calculation'!AK11</f>
-        <v>3.1115882323818268E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="X11" s="64">
-        <f>'Capacity Factor Calculation'!AL11</f>
-        <v>3.1079246669590853E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Y11" s="64">
-        <f>'Capacity Factor Calculation'!AM11</f>
-        <v>3.104269718311152E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Z11" s="64">
-        <f>'Capacity Factor Calculation'!AN11</f>
-        <v>3.1006233560735116E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AA11" s="64">
-        <f>'Capacity Factor Calculation'!AO11</f>
-        <v>3.0969855500241492E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AB11" s="64">
-        <f>'Capacity Factor Calculation'!AP11</f>
-        <v>3.0933562700827144E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AC11" s="64">
-        <f>'Capacity Factor Calculation'!AQ11</f>
-        <v>3.0897354863096953E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AD11" s="64">
-        <f>'Capacity Factor Calculation'!AR11</f>
-        <v>3.0861231689055919E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AE11" s="64">
-        <f>'Capacity Factor Calculation'!AS11</f>
-        <v>3.0825192882101008E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AF11" s="64">
-        <f>'Capacity Factor Calculation'!AT11</f>
-        <v>3.078923814701302E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AG11" s="64">
-        <f>'Capacity Factor Calculation'!AU11</f>
-        <v>3.075336718994854E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19869,132 +20410,132 @@
         <v>132</v>
       </c>
       <c r="B12" s="64">
-        <f>B3</f>
-        <v>0.46334270205422579</v>
+        <f>'Capacity Factor-Reports'!B12</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="C12" s="64">
-        <f t="shared" ref="C12:AG12" si="0">C3</f>
-        <v>0.46334270205422579</v>
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.47230130396568493</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.48090540931570031</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.48917565129265556</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.49713109230926311</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.50478937068699459</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.51216683120445228</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.51927864154324566</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.52613889637721789</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.53276071060829144</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.5391563030466322</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.54533707165847944</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.55131366135668725</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.5570960251821393</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.56269347961571159</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.56811475466746209</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.57336803930944047</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.57846102274938105</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="U12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.58340093198288456</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.58819456600973596</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.59284832705499801</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.59736824909645314</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.60176002396564587</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.60602902525989633</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.61018033027659013</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.61421874015795352</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AC12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.61814879841432158</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AD12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.62197480797622773</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AE12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.62570084690981886</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AF12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.62933078291622802</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AG12" s="64">
-        <f t="shared" si="0"/>
-        <v>0.6328682867233516</v>
+        <f t="shared" si="2"/>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20002,132 +20543,132 @@
         <v>65</v>
       </c>
       <c r="B13" s="64">
-        <f>'Capacity Factor Calculation'!Q13</f>
-        <v>0.67782537363300799</v>
+        <f>'Capacity Factor-Reports'!B13</f>
+        <v>0.65</v>
       </c>
       <c r="C13" s="64">
-        <f>'Capacity Factor Calculation'!Q13</f>
-        <v>0.67782537363300799</v>
+        <f t="shared" si="1"/>
+        <v>0.65</v>
       </c>
       <c r="D13" s="64">
-        <f>'Capacity Factor Calculation'!R13</f>
-        <v>0.67966570922029579</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="E13" s="64">
-        <f>'Capacity Factor Calculation'!S13</f>
-        <v>0.68132093869389931</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="F13" s="64">
-        <f>'Capacity Factor Calculation'!T13</f>
-        <v>0.68281765251993087</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="G13" s="64">
-        <f>'Capacity Factor Calculation'!U13</f>
-        <v>0.68417758093293024</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="H13" s="64">
-        <f>'Capacity Factor Calculation'!V13</f>
-        <v>0.68541865585845485</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="I13" s="64">
-        <f>'Capacity Factor Calculation'!W13</f>
-        <v>0.68655580606689082</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="J13" s="64">
-        <f>'Capacity Factor Calculation'!X13</f>
-        <v>0.68760156060162037</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="K13" s="64">
-        <f>'Capacity Factor Calculation'!Y13</f>
-        <v>0.68856651233111088</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="L13" s="64">
-        <f>'Capacity Factor Calculation'!Z13</f>
-        <v>0.68945967804537156</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="M13" s="64">
-        <f>'Capacity Factor Calculation'!AA13</f>
-        <v>0.69028878106819402</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="N13" s="64">
-        <f>'Capacity Factor Calculation'!AB13</f>
-        <v>0.69106047516332147</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="O13" s="64">
-        <f>'Capacity Factor Calculation'!AC13</f>
-        <v>0.69178052348571284</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="P13" s="64">
-        <f>'Capacity Factor Calculation'!AD13</f>
-        <v>0.69245394276711425</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="Q13" s="64">
-        <f>'Capacity Factor Calculation'!AE13</f>
-        <v>0.69308512036859438</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="R13" s="64">
-        <f>'Capacity Factor Calculation'!AF13</f>
-        <v>0.69367790997578316</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="S13" s="64">
-        <f>'Capacity Factor Calculation'!AG13</f>
-        <v>0.69423571034896026</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="T13" s="64">
-        <f>'Capacity Factor Calculation'!AH13</f>
-        <v>0.69476153052829603</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="U13" s="64">
-        <f>'Capacity Factor Calculation'!AI13</f>
-        <v>0.69525804413644221</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="V13" s="64">
-        <f>'Capacity Factor Calculation'!AJ13</f>
-        <v>0.69572763484762945</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="W13" s="64">
-        <f>'Capacity Factor Calculation'!AK13</f>
-        <v>0.69617243465548662</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="X13" s="64">
-        <f>'Capacity Factor Calculation'!AL13</f>
-        <v>0.69659435623594479</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="Y13" s="64">
-        <f>'Capacity Factor Calculation'!AM13</f>
-        <v>0.69699512044159861</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="Z13" s="64">
-        <f>'Capacity Factor Calculation'!AN13</f>
-        <v>0.69737627976111316</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AA13" s="64">
-        <f>'Capacity Factor Calculation'!AO13</f>
-        <v>0.69773923841800067</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AB13" s="64">
-        <f>'Capacity Factor Calculation'!AP13</f>
-        <v>0.69808526965733764</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AC13" s="64">
-        <f>'Capacity Factor Calculation'!AQ13</f>
-        <v>0.69841553066899087</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AD13" s="64">
-        <f>'Capacity Factor Calculation'!AR13</f>
-        <v>0.69873107551593039</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AE13" s="64">
-        <f>'Capacity Factor Calculation'!AS13</f>
-        <v>0.69903286637198059</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AF13" s="64">
-        <f>'Capacity Factor Calculation'!AT13</f>
-        <v>0.69932178332143213</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
       <c r="AG13" s="64">
-        <f>'Capacity Factor Calculation'!AU13</f>
-        <v>0.69959863293072588</v>
+        <f t="shared" si="2"/>
+        <v>0.65</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20135,132 +20676,132 @@
         <v>133</v>
       </c>
       <c r="B14" s="64">
-        <f>'Capacity Factor Calculation'!Q14</f>
-        <v>0.19089506879858689</v>
+        <f>'Capacity Factor-Reports'!B14</f>
+        <v>0.37</v>
       </c>
       <c r="C14" s="64">
-        <f>'Capacity Factor Calculation'!Q14</f>
-        <v>0.19089506879858689</v>
+        <f t="shared" si="1"/>
+        <v>0.37</v>
       </c>
       <c r="D14" s="64">
-        <f>'Capacity Factor Calculation'!R14</f>
-        <v>0.19048075744739912</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="E14" s="64">
-        <f>'Capacity Factor Calculation'!S14</f>
-        <v>0.190160325233211</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="F14" s="64">
-        <f>'Capacity Factor Calculation'!T14</f>
-        <v>0.18990511109979744</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="G14" s="64">
-        <f>'Capacity Factor Calculation'!U14</f>
-        <v>0.18969704322974223</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="H14" s="64">
-        <f>'Capacity Factor Calculation'!V14</f>
-        <v>0.18952416212690099</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="I14" s="64">
-        <f>'Capacity Factor Calculation'!W14</f>
-        <v>0.18937823792084044</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="J14" s="64">
-        <f>'Capacity Factor Calculation'!X14</f>
-        <v>0.1892534216415441</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="K14" s="64">
-        <f>'Capacity Factor Calculation'!Y14</f>
-        <v>0.18914544229798283</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="L14" s="64">
-        <f>'Capacity Factor Calculation'!Z14</f>
-        <v>0.18905110835329414</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="M14" s="64">
-        <f>'Capacity Factor Calculation'!AA14</f>
-        <v>0.18896798696430725</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="N14" s="64">
-        <f>'Capacity Factor Calculation'!AB14</f>
-        <v>0.18889419118197412</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="O14" s="64">
-        <f>'Capacity Factor Calculation'!AC14</f>
-        <v>0.1888282349709906</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="P14" s="64">
-        <f>'Capacity Factor Calculation'!AD14</f>
-        <v>0.18876893210417986</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="Q14" s="64">
-        <f>'Capacity Factor Calculation'!AE14</f>
-        <v>0.18871532418489448</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="R14" s="64">
-        <f>'Capacity Factor Calculation'!AF14</f>
-        <v>0.18866662845570523</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="S14" s="64">
-        <f>'Capacity Factor Calculation'!AG14</f>
-        <v>0.18862219932571028</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="T14" s="64">
-        <f>'Capacity Factor Calculation'!AH14</f>
-        <v>0.18858149958608286</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="U14" s="64">
-        <f>'Capacity Factor Calculation'!AI14</f>
-        <v>0.18854407858214964</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="V14" s="64">
-        <f>'Capacity Factor Calculation'!AJ14</f>
-        <v>0.18850955545652448</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="W14" s="64">
-        <f>'Capacity Factor Calculation'!AK14</f>
-        <v>0.18847760614009484</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="X14" s="64">
-        <f>'Capacity Factor Calculation'!AL14</f>
-        <v>0.18844795314801843</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="Y14" s="64">
-        <f>'Capacity Factor Calculation'!AM14</f>
-        <v>0.18842035749960068</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="Z14" s="64">
-        <f>'Capacity Factor Calculation'!AN14</f>
-        <v>0.18839461226361512</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AA14" s="64">
-        <f>'Capacity Factor Calculation'!AO14</f>
-        <v>0.18837053735993203</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AB14" s="64">
-        <f>'Capacity Factor Calculation'!AP14</f>
-        <v>0.1883479753411558</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AC14" s="64">
-        <f>'Capacity Factor Calculation'!AQ14</f>
-        <v>0.1883267879453068</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AD14" s="64">
-        <f>'Capacity Factor Calculation'!AR14</f>
-        <v>0.18830685325995919</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AE14" s="64">
-        <f>'Capacity Factor Calculation'!AS14</f>
-        <v>0.18828806337494855</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AF14" s="64">
-        <f>'Capacity Factor Calculation'!AT14</f>
-        <v>0.18827032242820382</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
       <c r="AG14" s="64">
-        <f>'Capacity Factor Calculation'!AU14</f>
-        <v>0.18825354496995095</v>
+        <f t="shared" si="2"/>
+        <v>0.37</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20268,132 +20809,132 @@
         <v>134</v>
       </c>
       <c r="B15" s="64">
-        <f>'Capacity Factor Calculation'!Q15</f>
-        <v>8.3496071984080808E-2</v>
+        <f>'Capacity Factor-Reports'!B15</f>
+        <v>0.7</v>
       </c>
       <c r="C15" s="64">
-        <f>'Capacity Factor Calculation'!Q15</f>
-        <v>8.3496071984080808E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.7</v>
       </c>
       <c r="D15" s="64">
-        <f>'Capacity Factor Calculation'!R15</f>
-        <v>3.1828746187346255E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="E15" s="64">
-        <f>'Capacity Factor Calculation'!S15</f>
-        <v>3.179041369494881E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="F15" s="64">
-        <f>'Capacity Factor Calculation'!T15</f>
-        <v>3.1752173421859459E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="G15" s="64">
-        <f>'Capacity Factor Calculation'!U15</f>
-        <v>3.1714025035689826E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="H15" s="64">
-        <f>'Capacity Factor Calculation'!V15</f>
-        <v>3.1675968205646998E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="I15" s="64">
-        <f>'Capacity Factor Calculation'!W15</f>
-        <v>3.1638002602523967E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="J15" s="64">
-        <f>'Capacity Factor Calculation'!X15</f>
-        <v>3.1600127898690142E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="K15" s="64">
-        <f>'Capacity Factor Calculation'!Y15</f>
-        <v>3.1562343768081903E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="L15" s="64">
-        <f>'Capacity Factor Calculation'!Z15</f>
-        <v>3.1524649886193266E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="M15" s="64">
-        <f>'Capacity Factor Calculation'!AA15</f>
-        <v>3.1487045930066598E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="N15" s="64">
-        <f>'Capacity Factor Calculation'!AB15</f>
-        <v>3.1449531578283355E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="O15" s="64">
-        <f>'Capacity Factor Calculation'!AC15</f>
-        <v>3.1412106510954975E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="P15" s="64">
-        <f>'Capacity Factor Calculation'!AD15</f>
-        <v>3.1374770409713745E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Q15" s="64">
-        <f>'Capacity Factor Calculation'!AE15</f>
-        <v>3.1337522957703798E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="R15" s="64">
-        <f>'Capacity Factor Calculation'!AF15</f>
-        <v>3.1300363839572132E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="S15" s="64">
-        <f>'Capacity Factor Calculation'!AG15</f>
-        <v>3.1263292741459725E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="T15" s="64">
-        <f>'Capacity Factor Calculation'!AH15</f>
-        <v>3.1226309350992701E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="U15" s="64">
-        <f>'Capacity Factor Calculation'!AI15</f>
-        <v>3.1189413357273529E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="V15" s="64">
-        <f>'Capacity Factor Calculation'!AJ15</f>
-        <v>3.115260445087234E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="W15" s="64">
-        <f>'Capacity Factor Calculation'!AK15</f>
-        <v>3.1115882323818268E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="X15" s="64">
-        <f>'Capacity Factor Calculation'!AL15</f>
-        <v>3.1079246669590853E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Y15" s="64">
-        <f>'Capacity Factor Calculation'!AM15</f>
-        <v>3.104269718311152E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Z15" s="64">
-        <f>'Capacity Factor Calculation'!AN15</f>
-        <v>3.1006233560735116E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AA15" s="64">
-        <f>'Capacity Factor Calculation'!AO15</f>
-        <v>3.0969855500241492E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AB15" s="64">
-        <f>'Capacity Factor Calculation'!AP15</f>
-        <v>3.0933562700827144E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AC15" s="64">
-        <f>'Capacity Factor Calculation'!AQ15</f>
-        <v>3.0897354863096953E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AD15" s="64">
-        <f>'Capacity Factor Calculation'!AR15</f>
-        <v>3.0861231689055919E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AE15" s="64">
-        <f>'Capacity Factor Calculation'!AS15</f>
-        <v>3.0825192882101008E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AF15" s="64">
-        <f>'Capacity Factor Calculation'!AT15</f>
-        <v>3.078923814701302E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AG15" s="64">
-        <f>'Capacity Factor Calculation'!AU15</f>
-        <v>3.075336718994854E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20401,132 +20942,132 @@
         <v>135</v>
       </c>
       <c r="B16" s="64">
-        <f>'Capacity Factor Calculation'!Q16</f>
-        <v>8.3496071984080808E-2</v>
+        <f>'Capacity Factor-Reports'!B16</f>
+        <v>0.7</v>
       </c>
       <c r="C16" s="64">
-        <f>'Capacity Factor Calculation'!Q16</f>
-        <v>8.3496071984080808E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.7</v>
       </c>
       <c r="D16" s="64">
-        <f>'Capacity Factor Calculation'!R16</f>
-        <v>3.1828746187346255E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="E16" s="64">
-        <f>'Capacity Factor Calculation'!S16</f>
-        <v>3.179041369494881E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="F16" s="64">
-        <f>'Capacity Factor Calculation'!T16</f>
-        <v>3.1752173421859459E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="G16" s="64">
-        <f>'Capacity Factor Calculation'!U16</f>
-        <v>3.1714025035689826E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="H16" s="64">
-        <f>'Capacity Factor Calculation'!V16</f>
-        <v>3.1675968205646998E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="I16" s="64">
-        <f>'Capacity Factor Calculation'!W16</f>
-        <v>3.1638002602523967E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="J16" s="64">
-        <f>'Capacity Factor Calculation'!X16</f>
-        <v>3.1600127898690142E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="K16" s="64">
-        <f>'Capacity Factor Calculation'!Y16</f>
-        <v>3.1562343768081903E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="L16" s="64">
-        <f>'Capacity Factor Calculation'!Z16</f>
-        <v>3.1524649886193266E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="M16" s="64">
-        <f>'Capacity Factor Calculation'!AA16</f>
-        <v>3.1487045930066598E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="N16" s="64">
-        <f>'Capacity Factor Calculation'!AB16</f>
-        <v>3.1449531578283355E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="O16" s="64">
-        <f>'Capacity Factor Calculation'!AC16</f>
-        <v>3.1412106510954975E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="P16" s="64">
-        <f>'Capacity Factor Calculation'!AD16</f>
-        <v>3.1374770409713745E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Q16" s="64">
-        <f>'Capacity Factor Calculation'!AE16</f>
-        <v>3.1337522957703798E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="R16" s="64">
-        <f>'Capacity Factor Calculation'!AF16</f>
-        <v>3.1300363839572132E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="S16" s="64">
-        <f>'Capacity Factor Calculation'!AG16</f>
-        <v>3.1263292741459725E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="T16" s="64">
-        <f>'Capacity Factor Calculation'!AH16</f>
-        <v>3.1226309350992701E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="U16" s="64">
-        <f>'Capacity Factor Calculation'!AI16</f>
-        <v>3.1189413357273529E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="V16" s="64">
-        <f>'Capacity Factor Calculation'!AJ16</f>
-        <v>3.115260445087234E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="W16" s="64">
-        <f>'Capacity Factor Calculation'!AK16</f>
-        <v>3.1115882323818268E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="X16" s="64">
-        <f>'Capacity Factor Calculation'!AL16</f>
-        <v>3.1079246669590853E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Y16" s="64">
-        <f>'Capacity Factor Calculation'!AM16</f>
-        <v>3.104269718311152E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="Z16" s="64">
-        <f>'Capacity Factor Calculation'!AN16</f>
-        <v>3.1006233560735116E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AA16" s="64">
-        <f>'Capacity Factor Calculation'!AO16</f>
-        <v>3.0969855500241492E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AB16" s="64">
-        <f>'Capacity Factor Calculation'!AP16</f>
-        <v>3.0933562700827144E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AC16" s="64">
-        <f>'Capacity Factor Calculation'!AQ16</f>
-        <v>3.0897354863096953E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AD16" s="64">
-        <f>'Capacity Factor Calculation'!AR16</f>
-        <v>3.0861231689055919E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AE16" s="64">
-        <f>'Capacity Factor Calculation'!AS16</f>
-        <v>3.0825192882101008E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AF16" s="64">
-        <f>'Capacity Factor Calculation'!AT16</f>
-        <v>3.078923814701302E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
       <c r="AG16" s="64">
-        <f>'Capacity Factor Calculation'!AU16</f>
-        <v>3.075336718994854E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20534,132 +21075,132 @@
         <v>66</v>
       </c>
       <c r="B17" s="64">
-        <f>'Capacity Factor Calculation'!Q17</f>
-        <v>0.4468599033816501</v>
+        <f>'Capacity Factor-Reports'!B17</f>
+        <v>0.5</v>
       </c>
       <c r="C17" s="64">
-        <f>'Capacity Factor Calculation'!Q17</f>
-        <v>0.4468599033816501</v>
+        <f t="shared" si="1"/>
+        <v>0.5</v>
       </c>
       <c r="D17" s="64">
-        <f>'Capacity Factor Calculation'!R17</f>
-        <v>0.4408734340241256</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="E17" s="64">
-        <f>'Capacity Factor Calculation'!S17</f>
-        <v>0.43612554453367519</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="F17" s="64">
-        <f>'Capacity Factor Calculation'!T17</f>
-        <v>0.4322678843226842</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="G17" s="64">
-        <f>'Capacity Factor Calculation'!U17</f>
-        <v>0.42907153729072023</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="H17" s="64">
-        <f>'Capacity Factor Calculation'!V17</f>
-        <v>0.42637987663222426</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="I17" s="64">
-        <f>'Capacity Factor Calculation'!W17</f>
-        <v>0.42408211753350822</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="J17" s="64">
-        <f>'Capacity Factor Calculation'!X17</f>
-        <v>0.42209768922098073</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="K17" s="64">
-        <f>'Capacity Factor Calculation'!Y17</f>
-        <v>0.42036659218239292</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="L17" s="64">
-        <f>'Capacity Factor Calculation'!Z17</f>
-        <v>0.41884322678843561</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="M17" s="64">
-        <f>'Capacity Factor Calculation'!AA17</f>
-        <v>0.41749231785417162</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="N17" s="64">
-        <f>'Capacity Factor Calculation'!AB17</f>
-        <v>0.41628614916286444</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="O17" s="64">
-        <f>'Capacity Factor Calculation'!AC17</f>
-        <v>0.41520264169440213</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="P17" s="64">
-        <f>'Capacity Factor Calculation'!AD17</f>
-        <v>0.41422398978740388</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="Q17" s="64">
-        <f>'Capacity Factor Calculation'!AE17</f>
-        <v>0.41333567497951312</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="R17" s="64">
-        <f>'Capacity Factor Calculation'!AF17</f>
-        <v>0.41252574088996574</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="S17" s="64">
-        <f>'Capacity Factor Calculation'!AG17</f>
-        <v>0.41178425193474621</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="T17" s="64">
-        <f>'Capacity Factor Calculation'!AH17</f>
-        <v>0.41110288370562564</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="U17" s="64">
-        <f>'Capacity Factor Calculation'!AI17</f>
-        <v>0.4104746091047482</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="V17" s="64">
-        <f>'Capacity Factor Calculation'!AJ17</f>
-        <v>0.40989345509893654</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="W17" s="64">
-        <f>'Capacity Factor Calculation'!AK17</f>
-        <v>0.40935431222607521</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="X17" s="64">
-        <f>'Capacity Factor Calculation'!AL17</f>
-        <v>0.40885278397225067</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="Y17" s="64">
-        <f>'Capacity Factor Calculation'!AM17</f>
-        <v>0.40838506661194235</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="Z17" s="64">
-        <f>'Capacity Factor Calculation'!AN17</f>
-        <v>0.40794785255774113</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AA17" s="64">
-        <f>'Capacity Factor Calculation'!AO17</f>
-        <v>0.40753825202275262</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AB17" s="64">
-        <f>'Capacity Factor Calculation'!AP17</f>
-        <v>0.40715372907153891</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AC17" s="64">
-        <f>'Capacity Factor Calculation'!AQ17</f>
-        <v>0.4067920490679221</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AD17" s="64">
-        <f>'Capacity Factor Calculation'!AR17</f>
-        <v>0.40645123521836007</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AE17" s="64">
-        <f>'Capacity Factor Calculation'!AS17</f>
-        <v>0.40612953242578281</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AF17" s="64">
-        <f>'Capacity Factor Calculation'!AT17</f>
-        <v>0.40582537705825522</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
       <c r="AG17" s="64">
-        <f>'Capacity Factor Calculation'!AU17</f>
-        <v>0.40553737153325126</v>
+        <f t="shared" si="2"/>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -21655,7 +22196,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
@@ -24870,7 +25411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
@@ -24989,132 +25530,132 @@
         <v>126</v>
       </c>
       <c r="B2" s="63">
-        <f>'BECF-pre-ret'!B2*1.1</f>
-        <v>0.74560791099630885</v>
+        <f>'BECF-pre-ret'!B2</f>
+        <v>0.65</v>
       </c>
       <c r="C2" s="63">
         <f t="shared" ref="C2:AG2" si="0">$B2</f>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="D2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="E2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="F2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="G2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="H2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="I2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="J2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="K2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="L2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="M2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="N2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="O2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="P2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Q2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="R2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="S2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="T2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="U2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="V2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="W2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="X2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Y2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Z2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AA2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AB2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AC2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AD2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AE2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AF2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AG2" s="63">
         <f t="shared" si="0"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25122,132 +25663,132 @@
         <v>127</v>
       </c>
       <c r="B3" s="63">
-        <f>'BECF-pre-ret'!B3*1.1</f>
-        <v>0.50967697225964836</v>
+        <f>'BECF-pre-ret'!B3</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="C3" s="63">
         <f t="shared" ref="C3:AG3" si="1">$B3</f>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="U3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AC3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AD3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AE3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AF3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AG3" s="63">
         <f t="shared" si="1"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25255,132 +25796,132 @@
         <v>128</v>
       </c>
       <c r="B4" s="63">
-        <f>'BECF-pre-ret'!B4*1.1</f>
-        <v>0.50967697225964836</v>
+        <f>'BECF-pre-ret'!B4</f>
+        <v>0.45</v>
       </c>
       <c r="C4" s="63">
         <f>$B$4</f>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="D4" s="63">
         <f t="shared" ref="D4:AG4" si="2">$B$4</f>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="E4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="F4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="G4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="H4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="J4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="K4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="L4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="M4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="N4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="O4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="P4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="Q4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="R4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="S4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="T4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="U4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="V4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="W4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="X4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="Y4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="Z4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AA4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AB4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AC4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AD4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AE4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AF4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
       <c r="AG4" s="63">
         <f t="shared" si="2"/>
-        <v>0.50967697225964836</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25388,132 +25929,132 @@
         <v>15</v>
       </c>
       <c r="B5" s="63">
-        <f>'BECF-pre-ret'!B5*1.1</f>
-        <v>0.46718181240458195</v>
+        <f>'BECF-pre-ret'!B5</f>
+        <v>0.37</v>
       </c>
       <c r="C5" s="63">
         <f t="shared" ref="C5:AG5" si="3">$B5</f>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="D5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="E5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="F5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="G5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="H5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="I5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="J5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="K5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="L5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="M5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="N5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="O5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="P5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="Q5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="R5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="S5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="T5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="U5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="V5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="W5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="X5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="Y5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="Z5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AA5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AB5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AC5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AD5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AE5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AF5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
       <c r="AG5" s="63">
         <f t="shared" si="3"/>
-        <v>0.46718181240458195</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25522,131 +26063,131 @@
       </c>
       <c r="B6" s="63">
         <f>'BECF-pre-ret'!B6</f>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="C6" s="63">
         <f t="shared" ref="C6:C7" si="4">$B6</f>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="D6" s="63">
         <f t="shared" ref="D6:D7" si="5">B6</f>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="E6" s="63">
         <f t="shared" ref="E6:AG6" si="6">D6</f>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="F6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="G6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="I6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="J6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="K6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="L6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="M6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="N6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="O6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="P6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="Q6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="R6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="S6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="T6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="U6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="V6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="W6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="X6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="Y6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="Z6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AA6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AB6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AC6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AD6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AE6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AF6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
       <c r="AG6" s="63">
         <f t="shared" si="6"/>
-        <v>0.19089506879858689</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25655,131 +26196,131 @@
       </c>
       <c r="B7" s="63">
         <f>'BECF-pre-ret'!B7</f>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="C7" s="63">
         <f t="shared" si="4"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="63">
         <f t="shared" si="5"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="E7" s="63">
         <f t="shared" ref="E7:AG7" si="7">D7</f>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="I7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="K7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="L7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="N7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="O7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="R7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="S7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="T7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="U7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="V7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="W7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="X7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Y7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Z7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AA7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AB7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AC7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AD7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AE7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AF7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" s="63">
         <f t="shared" si="7"/>
-        <v>8.1335616438358793E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25787,132 +26328,132 @@
         <v>130</v>
       </c>
       <c r="B8" s="63">
-        <f>'BECF-pre-ret'!B8*1.1</f>
-        <v>8.9469178082194678E-2</v>
+        <f>'BECF-pre-ret'!B8</f>
+        <v>0.2</v>
       </c>
       <c r="C8" s="63">
         <f>$B8</f>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D8" s="63">
         <f t="shared" ref="D8:AG8" si="8">$B8</f>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="E8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="F8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="I8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="K8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="L8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="N8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="O8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="P8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="R8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="S8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="T8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="U8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="V8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="W8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="X8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Y8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AA8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AB8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AC8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AD8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AE8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AF8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" s="63">
         <f t="shared" si="8"/>
-        <v>8.9469178082194678E-2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25920,132 +26461,132 @@
         <v>21</v>
       </c>
       <c r="B9" s="63">
-        <f>'BECF-pre-ret'!B9*1.1</f>
-        <v>0.49154589371981516</v>
+        <f>'BECF-pre-ret'!B9</f>
+        <v>0.5</v>
       </c>
       <c r="C9" s="63">
         <f t="shared" ref="C9:AG9" si="9">$B9</f>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="E9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="F9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="J9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="K9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="M9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="N9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="O9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="P9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="R9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="S9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="T9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="U9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="V9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="W9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="X9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Y9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Z9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AA9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AB9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AC9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AD9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AE9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AF9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AG9" s="63">
         <f t="shared" si="9"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26053,132 +26594,132 @@
         <v>16</v>
       </c>
       <c r="B10" s="63">
-        <f>'BECF-pre-ret'!B10*1.1</f>
-        <v>0.77899611252796808</v>
+        <f>'BECF-pre-ret'!B10</f>
+        <v>0.82</v>
       </c>
       <c r="C10" s="63">
         <f t="shared" ref="C10:AG10" si="10">$B10</f>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="D10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="E10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="F10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="G10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="H10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="I10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="J10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="K10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="L10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="M10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="N10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="O10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="P10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="Q10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="R10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="S10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="T10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="U10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="V10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="W10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="X10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="Y10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="Z10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AA10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AB10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AC10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AD10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AE10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AF10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
       <c r="AG10" s="63">
         <f t="shared" si="10"/>
-        <v>0.77899611252796808</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26186,132 +26727,132 @@
         <v>131</v>
       </c>
       <c r="B11" s="63">
-        <f>'BECF-pre-ret'!B11*1.1</f>
-        <v>9.1845679182488899E-2</v>
+        <f>'BECF-pre-ret'!B11</f>
+        <v>0.7</v>
       </c>
       <c r="C11" s="63">
         <f t="shared" ref="C11:AG11" si="11">$B11</f>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="D11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="E11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="F11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="G11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="H11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="I11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="J11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="K11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="L11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="M11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="N11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="O11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="P11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Q11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="R11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="S11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="T11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="V11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="W11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="X11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Y11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Z11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AA11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AB11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AC11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AD11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AE11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AF11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AG11" s="63">
         <f t="shared" si="11"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26319,132 +26860,132 @@
         <v>132</v>
       </c>
       <c r="B12" s="63">
-        <f>'BECF-pre-ret'!B12*1.1</f>
-        <v>0.50967697225964836</v>
+        <f>'BECF-pre-ret'!B12</f>
+        <v>0.28999999999999998</v>
       </c>
       <c r="C12" s="63">
         <f t="shared" ref="C12:AG12" si="12">$B12</f>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="D12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="F12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="K12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="L12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="M12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="O12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="P12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Q12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="R12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="S12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="T12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="U12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="W12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="X12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Y12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="Z12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AA12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AB12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AC12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AD12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AE12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AF12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AG12" s="63">
         <f t="shared" si="12"/>
-        <v>0.50967697225964836</v>
+        <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26452,132 +26993,132 @@
         <v>65</v>
       </c>
       <c r="B13" s="63">
-        <f>'BECF-pre-ret'!B13*1.1</f>
-        <v>0.74560791099630885</v>
+        <f>'BECF-pre-ret'!B13</f>
+        <v>0.65</v>
       </c>
       <c r="C13" s="63">
         <f t="shared" ref="C13:AG13" si="13">$B13</f>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="D13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="E13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="F13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="G13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="H13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="I13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="J13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="K13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="L13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="M13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="N13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="O13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="P13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Q13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="R13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="S13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="T13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="U13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="V13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="W13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="X13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Y13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="Z13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AA13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AB13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AC13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AD13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AE13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AF13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
       <c r="AG13" s="63">
         <f t="shared" si="13"/>
-        <v>0.74560791099630885</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26586,131 +27127,131 @@
       </c>
       <c r="B14" s="63">
         <f>'BECF-pre-ret'!B14</f>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="C14" s="63">
         <f t="shared" ref="C14:AG14" si="14">$B14</f>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="D14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="E14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="F14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="G14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="H14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="I14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="J14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="K14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="L14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="M14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="N14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="O14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="P14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="Q14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="R14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="S14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="T14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="U14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="V14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="W14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="X14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="Y14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="Z14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AA14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AB14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AC14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AD14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AE14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AF14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
       <c r="AG14" s="63">
         <f t="shared" si="14"/>
-        <v>0.19089506879858689</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26718,132 +27259,132 @@
         <v>134</v>
       </c>
       <c r="B15" s="63">
-        <f>'BECF-pre-ret'!B15*1.1</f>
-        <v>9.1845679182488899E-2</v>
+        <f>'BECF-pre-ret'!B15</f>
+        <v>0.7</v>
       </c>
       <c r="C15" s="63">
         <f t="shared" ref="C15:AG15" si="15">$B15</f>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="D15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="E15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="F15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="G15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="I15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="J15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="K15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="L15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="M15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="N15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="O15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="P15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Q15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="R15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="S15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="T15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="V15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="W15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="X15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Y15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Z15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AA15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AB15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AC15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AD15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AE15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AF15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AG15" s="63">
         <f t="shared" si="15"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26851,132 +27392,132 @@
         <v>135</v>
       </c>
       <c r="B16" s="63">
-        <f>'BECF-pre-ret'!B16*1.1</f>
-        <v>9.1845679182488899E-2</v>
+        <f>'BECF-pre-ret'!B16</f>
+        <v>0.7</v>
       </c>
       <c r="C16" s="63">
         <f t="shared" ref="C16:AG16" si="16">$B16</f>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="D16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="E16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="F16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="G16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="I16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="J16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="K16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="L16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="M16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="N16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="O16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="P16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Q16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="R16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="S16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="T16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="U16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="V16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="W16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="X16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Y16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="Z16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AA16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AB16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AC16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AD16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AE16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AF16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
       <c r="AG16" s="63">
         <f t="shared" si="16"/>
-        <v>9.1845679182488899E-2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26984,132 +27525,132 @@
         <v>66</v>
       </c>
       <c r="B17" s="63">
-        <f>'BECF-pre-ret'!B17*1.1</f>
-        <v>0.49154589371981516</v>
+        <f>'BECF-pre-ret'!B17</f>
+        <v>0.5</v>
       </c>
       <c r="C17" s="63">
         <f t="shared" ref="C17:AG17" si="17">$B17</f>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="D17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="E17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="J17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="K17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="M17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="N17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="O17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="P17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="R17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="S17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="T17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="U17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="V17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="W17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="X17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Y17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="Z17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AA17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AB17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AC17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AE17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AF17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
       <c r="AG17" s="63">
         <f t="shared" si="17"/>
-        <v>0.49154589371981516</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B965E68F-15CD-F546-9A0B-BB1B1CEBB7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CF2DE1-7121-A547-B6F3-826EB0AC2016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1163,23 +1163,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1196,19 +1202,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
@@ -2939,7 +2939,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="97" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="80"/>
@@ -2954,11 +2954,11 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="98" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="85"/>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="99" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="85"/>
@@ -3032,11 +3032,11 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="99" t="s">
+      <c r="B4" s="91"/>
+      <c r="C4" s="84" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="85"/>
@@ -3121,9 +3121,9 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="88"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="99" t="s">
+      <c r="A5" s="94"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="84" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="85"/>
@@ -3205,11 +3205,11 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="101" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="85"/>
-      <c r="C6" s="99" t="s">
+      <c r="C6" s="84" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="85"/>
@@ -3291,11 +3291,11 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="99" t="s">
+      <c r="B7" s="91"/>
+      <c r="C7" s="84" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="85"/>
@@ -3377,9 +3377,9 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="88"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="99" t="s">
+      <c r="A8" s="94"/>
+      <c r="B8" s="95"/>
+      <c r="C8" s="84" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="85"/>
@@ -3461,11 +3461,11 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="99" t="s">
+      <c r="B9" s="91"/>
+      <c r="C9" s="84" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="85"/>
@@ -3547,9 +3547,9 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="91"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="99" t="s">
+      <c r="A10" s="92"/>
+      <c r="B10" s="93"/>
+      <c r="C10" s="84" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="85"/>
@@ -3631,9 +3631,9 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="99" t="s">
+      <c r="A11" s="92"/>
+      <c r="B11" s="93"/>
+      <c r="C11" s="84" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="85"/>
@@ -3715,9 +3715,9 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="99" t="s">
+      <c r="A12" s="94"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="84" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="85"/>
@@ -3765,11 +3765,11 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="99" t="s">
+      <c r="B13" s="91"/>
+      <c r="C13" s="84" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="85"/>
@@ -3850,9 +3850,9 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="99" t="s">
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="84" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="85"/>
@@ -4094,11 +4094,11 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="91"/>
+      <c r="C17" s="84" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="85"/>
@@ -4141,9 +4141,9 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="99" t="s">
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="84" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="85"/>
@@ -4189,11 +4189,11 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="93" t="s">
+      <c r="A19" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="99" t="s">
+      <c r="B19" s="91"/>
+      <c r="C19" s="84" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="85"/>
@@ -4249,9 +4249,9 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="99" t="s">
+      <c r="A20" s="92"/>
+      <c r="B20" s="93"/>
+      <c r="C20" s="84" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="85"/>
@@ -4313,9 +4313,9 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="99" t="s">
+      <c r="A21" s="94"/>
+      <c r="B21" s="95"/>
+      <c r="C21" s="84" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="85"/>
@@ -4377,11 +4377,11 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="96" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="85"/>
-      <c r="C22" s="99" t="s">
+      <c r="C22" s="84" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="85"/>
@@ -4409,11 +4409,11 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="99" t="s">
+      <c r="B23" s="91"/>
+      <c r="C23" s="84" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="85"/>
@@ -4441,9 +4441,9 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="100" t="s">
+      <c r="A24" s="92"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D24" s="85"/>
@@ -4504,9 +4504,9 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="100" t="s">
+      <c r="A25" s="92"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="89" t="s">
         <v>52</v>
       </c>
       <c r="D25" s="85"/>
@@ -4537,9 +4537,9 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="100" t="s">
+      <c r="A26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="89" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="85"/>
@@ -4570,9 +4570,9 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="99" t="s">
+      <c r="A27" s="94"/>
+      <c r="B27" s="95"/>
+      <c r="C27" s="84" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="85"/>
@@ -4746,7 +4746,7 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="101" t="s">
+      <c r="F35" s="86" t="s">
         <v>55</v>
       </c>
       <c r="G35" s="83"/>
@@ -5451,7 +5451,7 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="102" t="s">
+      <c r="A53" s="87" t="s">
         <v>67</v>
       </c>
       <c r="B53" s="80"/>
@@ -5466,7 +5466,7 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="101" t="s">
+      <c r="F54" s="86" t="s">
         <v>55</v>
       </c>
       <c r="G54" s="83"/>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="103" t="s">
+      <c r="A70" s="88" t="s">
         <v>71</v>
       </c>
       <c r="B70" s="80"/>
@@ -7734,23 +7734,11 @@
     <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="A9:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A17:B18"/>
     <mergeCell ref="A19:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B27"/>
@@ -7767,11 +7755,23 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="A9:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A70:D70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7793,7 +7793,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="97" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="80"/>
@@ -7808,11 +7808,11 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="98" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="85"/>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="99" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="85"/>
@@ -7851,11 +7851,11 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="91"/>
+      <c r="C4" s="96" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="85"/>
@@ -7903,9 +7903,9 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="91"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="99" t="s">
+      <c r="A5" s="92"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="84" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="85"/>
@@ -7953,9 +7953,9 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="88"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="99" t="s">
+      <c r="A6" s="94"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="84" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="85"/>
@@ -8003,7 +8003,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="101" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="85"/>
@@ -8055,10 +8055,10 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="87"/>
+      <c r="B8" s="91"/>
       <c r="C8" s="104" t="s">
         <v>80</v>
       </c>
@@ -8107,8 +8107,8 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="104" t="s">
         <v>29</v>
       </c>
@@ -8157,9 +8157,9 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="99" t="s">
+      <c r="A10" s="94"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="84" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="85"/>
@@ -8218,10 +8218,10 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="87"/>
+      <c r="B11" s="91"/>
       <c r="C11" s="104" t="s">
         <v>81</v>
       </c>
@@ -8270,8 +8270,8 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="91"/>
-      <c r="B12" s="92"/>
+      <c r="A12" s="92"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="104" t="s">
         <v>34</v>
       </c>
@@ -8320,8 +8320,8 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="104" t="s">
         <v>82</v>
       </c>
@@ -8370,8 +8370,8 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
+      <c r="A14" s="94"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="104" t="s">
         <v>35</v>
       </c>
@@ -8512,10 +8512,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="87"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="104" t="s">
         <v>36</v>
       </c>
@@ -8525,8 +8525,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
+      <c r="A18" s="94"/>
+      <c r="B18" s="95"/>
       <c r="C18" s="104" t="s">
         <v>38</v>
       </c>
@@ -8539,10 +8539,10 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="87"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="104" t="s">
         <v>84</v>
       </c>
@@ -8564,9 +8564,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="99" t="s">
+      <c r="A20" s="94"/>
+      <c r="B20" s="95"/>
+      <c r="C20" s="84" t="s">
         <v>85</v>
       </c>
       <c r="D20" s="85"/>
@@ -8590,11 +8590,11 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="93" t="s">
+      <c r="A21" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="99" t="s">
+      <c r="B21" s="91"/>
+      <c r="C21" s="84" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="85"/>
@@ -8618,8 +8618,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8644,11 +8644,11 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="96" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="85"/>
-      <c r="C23" s="99" t="s">
+      <c r="C23" s="84" t="s">
         <v>49</v>
       </c>
       <c r="D23" s="85"/>
@@ -8672,11 +8672,11 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="99" t="s">
+      <c r="B24" s="91"/>
+      <c r="C24" s="84" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="85"/>
@@ -8700,8 +8700,8 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="93"/>
       <c r="C25" s="104" t="s">
         <v>53</v>
       </c>
@@ -8726,9 +8726,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="100" t="s">
+      <c r="A26" s="92"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="89" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="85"/>
@@ -8752,9 +8752,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="100" t="s">
+      <c r="A27" s="92"/>
+      <c r="B27" s="93"/>
+      <c r="C27" s="89" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="85"/>
@@ -8778,9 +8778,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="99" t="s">
+      <c r="A28" s="94"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="84" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="85"/>
@@ -10828,22 +10828,13 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A24:B28"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
@@ -10855,13 +10846,22 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A11:B14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A24:B28"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18869,7 +18869,7 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="B8">
         <f>B7</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -19746,131 +19746,131 @@
       </c>
       <c r="B7" s="64">
         <f>'Capacity Factor-Reports'!B7</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C7" s="64">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="L7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="N7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="P7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Q7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="R7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Y7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AA7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AB7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AC7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AD7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AE7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AF7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19879,131 +19879,131 @@
       </c>
       <c r="B8" s="64">
         <f>'Capacity Factor-Reports'!B8</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C8" s="64">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="L8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="N8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="P8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Q8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="R8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="U8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Y8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AA8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AB8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AC8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AD8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AE8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AF8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" s="64">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26196,131 +26196,131 @@
       </c>
       <c r="B7" s="63">
         <f>'BECF-pre-ret'!B7</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C7" s="63">
         <f t="shared" si="4"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D7" s="63">
         <f t="shared" si="5"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E7" s="63">
         <f t="shared" ref="E7:AG7" si="7">D7</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="L7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="N7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="P7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Q7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="R7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Y7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AA7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AB7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AC7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AD7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AE7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AF7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" s="63">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26329,131 +26329,131 @@
       </c>
       <c r="B8" s="63">
         <f>'BECF-pre-ret'!B8</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C8" s="63">
         <f>$B8</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D8" s="63">
         <f t="shared" ref="D8:AG8" si="8">$B8</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="I8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="K8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="L8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="N8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="P8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Q8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="R8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="S8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="U8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="X8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Y8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AA8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AB8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AC8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AD8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AE8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AF8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" s="63">
         <f t="shared" si="8"/>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">

--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CF2DE1-7121-A547-B6F3-826EB0AC2016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A43400-EFB8-DB4F-9A18-366DE4E70F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -834,7 +834,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -988,12 +988,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1163,29 +1200,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1202,15 +1233,39 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2939,7 +2994,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="95" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="80"/>
@@ -2954,11 +3009,11 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="85"/>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="85"/>
@@ -3032,11 +3087,11 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="84" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="99" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="85"/>
@@ -3121,9 +3176,9 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="94"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="84" t="s">
+      <c r="A5" s="88"/>
+      <c r="B5" s="89"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="85"/>
@@ -3205,11 +3260,11 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="101" t="s">
+      <c r="A6" s="84" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="85"/>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="99" t="s">
         <v>27</v>
       </c>
       <c r="D6" s="85"/>
@@ -3291,11 +3346,11 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="91"/>
-      <c r="C7" s="84" t="s">
+      <c r="B7" s="87"/>
+      <c r="C7" s="99" t="s">
         <v>29</v>
       </c>
       <c r="D7" s="85"/>
@@ -3377,9 +3432,9 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="94"/>
-      <c r="B8" s="95"/>
-      <c r="C8" s="84" t="s">
+      <c r="A8" s="88"/>
+      <c r="B8" s="89"/>
+      <c r="C8" s="99" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="85"/>
@@ -3461,11 +3516,11 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="103" t="s">
+      <c r="A9" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="91"/>
-      <c r="C9" s="84" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="99" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="85"/>
@@ -3547,9 +3602,9 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="84" t="s">
+      <c r="A10" s="91"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="99" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="85"/>
@@ -3631,9 +3686,9 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="92"/>
-      <c r="B11" s="93"/>
-      <c r="C11" s="84" t="s">
+      <c r="A11" s="91"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="99" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="85"/>
@@ -3715,9 +3770,9 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="94"/>
-      <c r="B12" s="95"/>
-      <c r="C12" s="84" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="99" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="85"/>
@@ -3765,11 +3820,11 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="84" t="s">
+      <c r="B13" s="87"/>
+      <c r="C13" s="99" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="85"/>
@@ -3850,9 +3905,9 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
-      <c r="C14" s="84" t="s">
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="99" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="85"/>
@@ -4094,11 +4149,11 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="103" t="s">
+      <c r="A17" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="91"/>
-      <c r="C17" s="84" t="s">
+      <c r="B17" s="87"/>
+      <c r="C17" s="99" t="s">
         <v>39</v>
       </c>
       <c r="D17" s="85"/>
@@ -4141,9 +4196,9 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
-      <c r="C18" s="84" t="s">
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="99" t="s">
         <v>40</v>
       </c>
       <c r="D18" s="85"/>
@@ -4189,11 +4244,11 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="91"/>
-      <c r="C19" s="84" t="s">
+      <c r="B19" s="87"/>
+      <c r="C19" s="99" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="85"/>
@@ -4249,9 +4304,9 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="92"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="84" t="s">
+      <c r="A20" s="91"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="99" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="85"/>
@@ -4313,9 +4368,9 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="94"/>
-      <c r="B21" s="95"/>
-      <c r="C21" s="84" t="s">
+      <c r="A21" s="88"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="99" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="85"/>
@@ -4377,11 +4432,11 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="94" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="85"/>
-      <c r="C22" s="84" t="s">
+      <c r="C22" s="99" t="s">
         <v>49</v>
       </c>
       <c r="D22" s="85"/>
@@ -4409,11 +4464,11 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="90" t="s">
+      <c r="A23" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="91"/>
-      <c r="C23" s="84" t="s">
+      <c r="B23" s="87"/>
+      <c r="C23" s="99" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="85"/>
@@ -4441,9 +4496,9 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="92"/>
-      <c r="B24" s="93"/>
-      <c r="C24" s="89" t="s">
+      <c r="A24" s="91"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="100" t="s">
         <v>51</v>
       </c>
       <c r="D24" s="85"/>
@@ -4504,9 +4559,9 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="92"/>
-      <c r="B25" s="93"/>
-      <c r="C25" s="89" t="s">
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="100" t="s">
         <v>52</v>
       </c>
       <c r="D25" s="85"/>
@@ -4537,9 +4592,9 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="92"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="89" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>53</v>
       </c>
       <c r="D26" s="85"/>
@@ -4570,9 +4625,9 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="94"/>
-      <c r="B27" s="95"/>
-      <c r="C27" s="84" t="s">
+      <c r="A27" s="88"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="99" t="s">
         <v>38</v>
       </c>
       <c r="D27" s="85"/>
@@ -4746,7 +4801,7 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="86" t="s">
+      <c r="F35" s="101" t="s">
         <v>55</v>
       </c>
       <c r="G35" s="83"/>
@@ -5451,7 +5506,7 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="87" t="s">
+      <c r="A53" s="102" t="s">
         <v>67</v>
       </c>
       <c r="B53" s="80"/>
@@ -5466,7 +5521,7 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="86" t="s">
+      <c r="F54" s="101" t="s">
         <v>55</v>
       </c>
       <c r="G54" s="83"/>
@@ -6258,7 +6313,7 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="88" t="s">
+      <c r="A70" s="103" t="s">
         <v>71</v>
       </c>
       <c r="B70" s="80"/>
@@ -7734,11 +7789,23 @@
     <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="A9:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="A19:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B27"/>
@@ -7755,23 +7822,11 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="A9:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A17:B18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7793,7 +7848,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="95" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="80"/>
@@ -7808,11 +7863,11 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="96" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="85"/>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="97" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="85"/>
@@ -7851,11 +7906,11 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="98" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="91"/>
-      <c r="C4" s="96" t="s">
+      <c r="B4" s="87"/>
+      <c r="C4" s="94" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="85"/>
@@ -7903,9 +7958,9 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="92"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="84" t="s">
+      <c r="A5" s="91"/>
+      <c r="B5" s="92"/>
+      <c r="C5" s="99" t="s">
         <v>26</v>
       </c>
       <c r="D5" s="85"/>
@@ -7953,9 +8008,9 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="94"/>
-      <c r="B6" s="95"/>
-      <c r="C6" s="84" t="s">
+      <c r="A6" s="88"/>
+      <c r="B6" s="89"/>
+      <c r="C6" s="99" t="s">
         <v>79</v>
       </c>
       <c r="D6" s="85"/>
@@ -8003,7 +8058,7 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="101" t="s">
+      <c r="A7" s="84" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="85"/>
@@ -8055,10 +8110,10 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="102" t="s">
+      <c r="A8" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="91"/>
+      <c r="B8" s="87"/>
       <c r="C8" s="104" t="s">
         <v>80</v>
       </c>
@@ -8107,8 +8162,8 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="92"/>
-      <c r="B9" s="93"/>
+      <c r="A9" s="91"/>
+      <c r="B9" s="92"/>
       <c r="C9" s="104" t="s">
         <v>29</v>
       </c>
@@ -8157,9 +8212,9 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="94"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="84" t="s">
+      <c r="A10" s="88"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="99" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="85"/>
@@ -8218,10 +8273,10 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="103" t="s">
+      <c r="A11" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="91"/>
+      <c r="B11" s="87"/>
       <c r="C11" s="104" t="s">
         <v>81</v>
       </c>
@@ -8270,8 +8325,8 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="92"/>
-      <c r="B12" s="93"/>
+      <c r="A12" s="91"/>
+      <c r="B12" s="92"/>
       <c r="C12" s="104" t="s">
         <v>34</v>
       </c>
@@ -8320,8 +8375,8 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="92"/>
-      <c r="B13" s="93"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="92"/>
       <c r="C13" s="104" t="s">
         <v>82</v>
       </c>
@@ -8370,8 +8425,8 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="94"/>
-      <c r="B14" s="95"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="89"/>
       <c r="C14" s="104" t="s">
         <v>35</v>
       </c>
@@ -8512,10 +8567,10 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="103" t="s">
+      <c r="A17" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="91"/>
+      <c r="B17" s="87"/>
       <c r="C17" s="104" t="s">
         <v>36</v>
       </c>
@@ -8525,8 +8580,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="94"/>
-      <c r="B18" s="95"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="89"/>
       <c r="C18" s="104" t="s">
         <v>38</v>
       </c>
@@ -8539,10 +8594,10 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="91"/>
+      <c r="B19" s="87"/>
       <c r="C19" s="104" t="s">
         <v>84</v>
       </c>
@@ -8564,9 +8619,9 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="94"/>
-      <c r="B20" s="95"/>
-      <c r="C20" s="84" t="s">
+      <c r="A20" s="88"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="99" t="s">
         <v>85</v>
       </c>
       <c r="D20" s="85"/>
@@ -8590,11 +8645,11 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="91"/>
-      <c r="C21" s="84" t="s">
+      <c r="B21" s="87"/>
+      <c r="C21" s="99" t="s">
         <v>47</v>
       </c>
       <c r="D21" s="85"/>
@@ -8618,8 +8673,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="94"/>
-      <c r="B22" s="95"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="89"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8644,11 +8699,11 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="96" t="s">
+      <c r="A23" s="94" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="85"/>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="99" t="s">
         <v>49</v>
       </c>
       <c r="D23" s="85"/>
@@ -8672,11 +8727,11 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="90" t="s">
+      <c r="A24" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="84" t="s">
+      <c r="B24" s="87"/>
+      <c r="C24" s="99" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="85"/>
@@ -8700,8 +8755,8 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="92"/>
-      <c r="B25" s="93"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="104" t="s">
         <v>53</v>
       </c>
@@ -8726,9 +8781,9 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="92"/>
-      <c r="B26" s="93"/>
-      <c r="C26" s="89" t="s">
+      <c r="A26" s="91"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="100" t="s">
         <v>51</v>
       </c>
       <c r="D26" s="85"/>
@@ -8752,9 +8807,9 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="92"/>
-      <c r="B27" s="93"/>
-      <c r="C27" s="89" t="s">
+      <c r="A27" s="91"/>
+      <c r="B27" s="92"/>
+      <c r="C27" s="100" t="s">
         <v>52</v>
       </c>
       <c r="D27" s="85"/>
@@ -8778,9 +8833,9 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="94"/>
-      <c r="B28" s="95"/>
-      <c r="C28" s="84" t="s">
+      <c r="A28" s="88"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="99" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="85"/>
@@ -10828,13 +10883,22 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A24:B28"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
@@ -10846,22 +10910,13 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A11:B14"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A24:B28"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18964,7 +19019,7 @@
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BC1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
@@ -18974,7 +19029,7 @@
     <col min="6" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="53" t="s">
         <v>93</v>
       </c>
@@ -19074,8 +19129,70 @@
       <c r="AG1" s="57" t="s">
         <v>125</v>
       </c>
+      <c r="AH1" s="107">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="108">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="108">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="108">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="108">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="108">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="108">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="108">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="108">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="108">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="108">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="108">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="108">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="108">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="108">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="108">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="108">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="108">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="108">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="108">
+        <v>2070</v>
+      </c>
+      <c r="BB1" s="105"/>
+      <c r="BC1" s="105"/>
     </row>
-    <row r="2" spans="1:33" s="52" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:55" s="52" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
         <v>126</v>
       </c>
@@ -19203,12 +19320,92 @@
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
-      <c r="AG2" s="64">
+      <c r="AG2" s="106">
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
+      <c r="AH2" s="109">
+        <f>AG2</f>
+        <v>0.65</v>
+      </c>
+      <c r="AI2" s="109">
+        <f t="shared" ref="AI2:BA16" si="1">AH2</f>
+        <v>0.65</v>
+      </c>
+      <c r="AJ2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AK2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AL2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AM2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AN2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AO2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AP2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AQ2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AR2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AS2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AT2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AU2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AV2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AW2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AX2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AY2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AZ2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="BA2" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="54" t="s">
         <v>127</v>
       </c>
@@ -19217,67 +19414,67 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="C3" s="64">
-        <f t="shared" ref="C3:R17" si="1">B3</f>
+        <f t="shared" ref="C3:R17" si="2">B3</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="D3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="E3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="F3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="G3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="I3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="J3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="K3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="L3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="M3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="N3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="O3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="P3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="R3" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S3" s="64">
@@ -19336,12 +19533,92 @@
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AG3" s="64">
+      <c r="AG3" s="106">
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
+      <c r="AH3" s="109">
+        <f t="shared" ref="AH3:AW17" si="3">AG3</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AI3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AJ3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AK3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AM3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AP3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AQ3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AR3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AT3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AU3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AV3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AW3" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AX3" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AY3" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AZ3" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="BA3" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>128</v>
       </c>
@@ -19350,7 +19627,7 @@
         <v>0.45</v>
       </c>
       <c r="C4" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="D4" s="64">
@@ -19469,12 +19746,92 @@
         <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
-      <c r="AG4" s="64">
+      <c r="AG4" s="106">
         <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
+      <c r="AH4" s="109">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="AI4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AJ4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AK4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AL4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AM4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AN4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AO4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AP4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AQ4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AR4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AS4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AT4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AU4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AV4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AW4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AX4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AY4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AZ4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="BA4" s="109">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
         <v>15</v>
       </c>
@@ -19483,7 +19840,7 @@
         <v>0.37</v>
       </c>
       <c r="C5" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
       <c r="D5" s="64">
@@ -19602,12 +19959,92 @@
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
-      <c r="AG5" s="64">
+      <c r="AG5" s="106">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
+      <c r="AH5" s="109">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="AI5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AJ5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AK5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AL5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AM5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AN5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AO5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AP5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AQ5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AR5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AS5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AT5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AU5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AV5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AW5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AX5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AY5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AZ5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="BA5" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="54" t="s">
         <v>129</v>
       </c>
@@ -19616,7 +20053,7 @@
         <v>0.35</v>
       </c>
       <c r="C6" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.35</v>
       </c>
       <c r="D6" s="64">
@@ -19735,12 +20172,92 @@
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
-      <c r="AG6" s="64">
+      <c r="AG6" s="106">
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
+      <c r="AH6" s="109">
+        <f t="shared" si="3"/>
+        <v>0.35</v>
+      </c>
+      <c r="AI6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AJ6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AK6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AL6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AM6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AN6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AO6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AP6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AQ6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AR6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AS6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AT6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AU6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AV6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AW6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AX6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AY6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AZ6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="BA6" s="109">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="54" t="s">
         <v>23</v>
       </c>
@@ -19749,7 +20266,7 @@
         <v>0.18</v>
       </c>
       <c r="C7" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
       <c r="D7" s="64">
@@ -19868,12 +20385,92 @@
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AG7" s="64">
+      <c r="AG7" s="106">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
+      <c r="AH7" s="109">
+        <f t="shared" si="3"/>
+        <v>0.18</v>
+      </c>
+      <c r="AI7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AJ7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AK7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AL7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AM7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AN7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AO7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AP7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AQ7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AR7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AT7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AX7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AY7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AZ7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="BA7" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="54" t="s">
         <v>130</v>
       </c>
@@ -19882,7 +20479,7 @@
         <v>0.18</v>
       </c>
       <c r="C8" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.18</v>
       </c>
       <c r="D8" s="64">
@@ -20001,12 +20598,92 @@
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AG8" s="64">
+      <c r="AG8" s="106">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
+      <c r="AH8" s="109">
+        <f t="shared" si="3"/>
+        <v>0.18</v>
+      </c>
+      <c r="AI8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AJ8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AK8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AL8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AM8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AN8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AO8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AP8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AQ8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AR8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AT8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AX8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AY8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AZ8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="BA8" s="109">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="54" t="s">
         <v>21</v>
       </c>
@@ -20015,7 +20692,7 @@
         <v>0.5</v>
       </c>
       <c r="C9" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="D9" s="64">
@@ -20134,12 +20811,92 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="AG9" s="64">
+      <c r="AG9" s="106">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
+      <c r="AH9" s="109">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AK9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA9" s="109">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="54" t="s">
         <v>16</v>
       </c>
@@ -20148,7 +20905,7 @@
         <v>0.82</v>
       </c>
       <c r="C10" s="64">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.82</v>
       </c>
       <c r="D10" s="64">
@@ -20267,12 +21024,92 @@
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
-      <c r="AG10" s="64">
+      <c r="AG10" s="106">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
+      <c r="AH10" s="109">
+        <f t="shared" si="3"/>
+        <v>0.82</v>
+      </c>
+      <c r="AI10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AJ10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AK10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AL10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AM10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AN10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AO10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AP10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AQ10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AR10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AS10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AT10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AU10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AV10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AW10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AX10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AY10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AZ10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="BA10" s="109">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="54" t="s">
         <v>131</v>
       </c>
@@ -20281,131 +21118,211 @@
         <v>0.7</v>
       </c>
       <c r="C11" s="64">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="D11" s="64">
-        <f t="shared" ref="D11:AG17" si="2">C11</f>
-        <v>0.7</v>
-      </c>
-      <c r="E11" s="64">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
+      <c r="D11" s="64">
+        <f t="shared" ref="D11:AG17" si="4">C11</f>
+        <v>0.7</v>
+      </c>
+      <c r="E11" s="64">
+        <f t="shared" si="4"/>
+        <v>0.7</v>
+      </c>
       <c r="F11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="G11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="H11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="I11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="J11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="K11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="L11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="M11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="N11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="O11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="P11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Q11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="R11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="S11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="T11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="U11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="V11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="W11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="X11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Y11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Z11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AA11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AB11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AC11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AD11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AE11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AF11" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG11" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG11" s="106">
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
+      <c r="AH11" s="109">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AN11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA11" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="54" t="s">
         <v>132</v>
       </c>
@@ -20414,131 +21331,211 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="C12" s="64">
-        <f t="shared" si="1"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="D12" s="64">
         <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
+      <c r="D12" s="64">
+        <f t="shared" si="4"/>
+        <v>0.28999999999999998</v>
+      </c>
       <c r="E12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="F12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="G12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="I12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="K12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="L12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="M12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="N12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="O12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="P12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="R12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="T12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="U12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="W12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="X12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Y12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Z12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AA12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AB12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AC12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AD12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AE12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AF12" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AG12" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG12" s="106">
+        <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
+      <c r="AH12" s="109">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AI12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AJ12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AK12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AM12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AP12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AQ12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AR12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AT12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AU12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AV12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AW12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AX12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AY12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AZ12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="BA12" s="109">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="54" t="s">
         <v>65</v>
       </c>
@@ -20547,131 +21544,211 @@
         <v>0.65</v>
       </c>
       <c r="C13" s="64">
-        <f t="shared" si="1"/>
-        <v>0.65</v>
-      </c>
-      <c r="D13" s="64">
         <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
+      <c r="D13" s="64">
+        <f t="shared" si="4"/>
+        <v>0.65</v>
+      </c>
       <c r="E13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="F13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="G13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="H13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="I13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="J13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="K13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="L13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="M13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="N13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="O13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="P13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="Q13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="R13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="S13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="T13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="U13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="V13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="W13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="X13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="Y13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="Z13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AA13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AB13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AC13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AD13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AE13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
       <c r="AF13" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
-      <c r="AG13" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG13" s="106">
+        <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
+      <c r="AH13" s="109">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+      <c r="AI13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AJ13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AK13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AL13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AM13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AN13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AO13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AP13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AQ13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AR13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AS13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AT13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AU13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AV13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AW13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AX13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AY13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AZ13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="BA13" s="109">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="54" t="s">
         <v>133</v>
       </c>
@@ -20680,131 +21757,211 @@
         <v>0.37</v>
       </c>
       <c r="C14" s="64">
-        <f t="shared" si="1"/>
-        <v>0.37</v>
-      </c>
-      <c r="D14" s="64">
         <f t="shared" si="2"/>
         <v>0.37</v>
       </c>
+      <c r="D14" s="64">
+        <f t="shared" si="4"/>
+        <v>0.37</v>
+      </c>
       <c r="E14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="F14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="G14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="H14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="I14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="J14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="K14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="L14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="M14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="N14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="O14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="P14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="Q14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="R14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="S14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="T14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="U14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="V14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="W14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="X14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="Y14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="Z14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AA14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AB14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AC14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AD14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AE14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="AF14" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
-      <c r="AG14" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG14" s="106">
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
+      <c r="AH14" s="109">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="AI14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AJ14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AK14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AL14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AM14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AN14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AO14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AP14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AQ14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AR14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AS14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AT14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AU14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AV14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AW14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AX14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AY14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AZ14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="BA14" s="109">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="54" t="s">
         <v>134</v>
       </c>
@@ -20813,131 +21970,211 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="64">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="D15" s="64">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
+      <c r="D15" s="64">
+        <f t="shared" si="4"/>
+        <v>0.7</v>
+      </c>
       <c r="E15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="F15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="G15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="H15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="I15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="J15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="K15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="L15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="M15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="N15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="O15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="P15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Q15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="R15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="S15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="T15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="U15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="V15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="W15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="X15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Y15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Z15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AA15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AB15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AC15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AD15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AE15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AF15" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG15" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG15" s="106">
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
+      <c r="AH15" s="109">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AN15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA15" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="54" t="s">
         <v>135</v>
       </c>
@@ -20946,131 +22183,211 @@
         <v>0.7</v>
       </c>
       <c r="C16" s="64">
-        <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="D16" s="64">
         <f t="shared" si="2"/>
         <v>0.7</v>
       </c>
+      <c r="D16" s="64">
+        <f t="shared" si="4"/>
+        <v>0.7</v>
+      </c>
       <c r="E16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="F16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="G16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="H16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="I16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="J16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="K16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="L16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="M16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="N16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="O16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="P16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Q16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="R16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="S16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="T16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="U16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="V16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="W16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="X16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Y16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="Z16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AA16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AB16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AC16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AD16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AE16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="AF16" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG16" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG16" s="106">
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
+      <c r="AH16" s="109">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI16" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ16" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK16" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL16" s="109">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM16" s="109">
+        <f t="shared" ref="AI16:BA17" si="5">AL16</f>
+        <v>0.7</v>
+      </c>
+      <c r="AN16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA16" s="109">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="54" t="s">
         <v>66</v>
       </c>
@@ -21079,145 +22396,225 @@
         <v>0.5</v>
       </c>
       <c r="C17" s="64">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="D17" s="64">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
+      <c r="D17" s="64">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
       <c r="E17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="F17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="G17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="H17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="I17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="J17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="K17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="L17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="M17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="N17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="O17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="P17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="Q17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="R17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="S17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="T17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="U17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="V17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="W17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="X17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="Y17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="Z17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AA17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AB17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AC17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AD17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AE17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="AF17" s="64">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="AG17" s="64">
-        <f t="shared" si="2"/>
+      <c r="AG17" s="106">
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
+      <c r="AH17" s="109">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AK17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA17" s="109">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -22201,7 +23598,7 @@
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
@@ -22209,7 +23606,7 @@
     <col min="5" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
         <v>93</v>
       </c>
@@ -22309,8 +23706,68 @@
       <c r="AG1" s="60">
         <v>2050</v>
       </c>
+      <c r="AH1" s="107">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="108">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="108">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="108">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="108">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="108">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="108">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="108">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="108">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="108">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="108">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="108">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="108">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="108">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="108">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="108">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="108">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="108">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="108">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="108">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>126</v>
       </c>
@@ -22318,7 +23775,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="58">
-        <f t="shared" ref="C2:AG2" si="0">$B2</f>
+        <f t="shared" ref="C2:BA2" si="0">$B2</f>
         <v>0</v>
       </c>
       <c r="D2" s="58">
@@ -22441,8 +23898,88 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AH2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AK2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AM2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AN2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AO2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AP2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AR2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AT2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AU2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AV2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AW2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AX2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AY2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AZ2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="BA2" s="58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>127</v>
       </c>
@@ -22450,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="58">
-        <f t="shared" ref="C3:AG3" si="1">$B3</f>
+        <f t="shared" ref="C3:BA3" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="D3" s="58">
@@ -22573,8 +24110,88 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="AH3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AL3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AM3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AN3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AP3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AR3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AS3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AU3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AW3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AX3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AY3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AZ3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="BA3" s="58">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>128</v>
       </c>
@@ -22582,7 +24199,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="58">
-        <f t="shared" ref="C4:AG4" si="2">$B4</f>
+        <f t="shared" ref="C4:BA4" si="2">$B4</f>
         <v>0</v>
       </c>
       <c r="D4" s="58">
@@ -22705,8 +24322,88 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="AH4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AL4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AM4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AN4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AP4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AR4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AS4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AT4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AU4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AV4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AW4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AX4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AY4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="BA4" s="58">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -22714,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="58">
-        <f t="shared" ref="C5:AG5" si="3">$B5</f>
+        <f t="shared" ref="C5:BA5" si="3">$B5</f>
         <v>0</v>
       </c>
       <c r="D5" s="58">
@@ -22837,8 +24534,88 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="AH5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AK5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AL5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AM5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AN5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AO5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AP5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AR5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AS5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AT5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="BA5" s="58">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>129</v>
       </c>
@@ -22846,7 +24623,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="58">
-        <f t="shared" ref="C6:AG6" si="4">$B6</f>
+        <f t="shared" ref="C6:BA6" si="4">$B6</f>
         <v>0</v>
       </c>
       <c r="D6" s="58">
@@ -22969,8 +24746,88 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
+      <c r="AH6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AI6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AK6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AL6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AM6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AN6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AP6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AR6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AS6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AT6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="BA6" s="58">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -22978,7 +24835,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="58">
-        <f t="shared" ref="C7:AG7" si="5">$B7</f>
+        <f t="shared" ref="C7:BA7" si="5">$B7</f>
         <v>0</v>
       </c>
       <c r="D7" s="58">
@@ -23101,8 +24958,88 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
+      <c r="AH7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AK7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AL7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AM7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AN7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AP7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AR7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AS7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AT7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AU7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AV7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AW7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AX7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AZ7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA7" s="58">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>130</v>
       </c>
@@ -23110,7 +25047,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="58">
-        <f t="shared" ref="C8:AG8" si="6">$B8</f>
+        <f t="shared" ref="C8:BA8" si="6">$B8</f>
         <v>0</v>
       </c>
       <c r="D8" s="58">
@@ -23233,8 +25170,88 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
+      <c r="AH8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AK8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AL8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AM8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AN8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AP8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AR8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AS8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AT8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AU8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AV8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AW8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AX8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AY8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AZ8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="BA8" s="58">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -23242,7 +25259,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="58">
-        <f t="shared" ref="C9:AG9" si="7">$B9</f>
+        <f t="shared" ref="C9:BA9" si="7">$B9</f>
         <v>0</v>
       </c>
       <c r="D9" s="58">
@@ -23365,8 +25382,88 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
+      <c r="AH9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AK9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AL9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AM9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AN9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AP9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AR9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AS9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AT9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AU9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AV9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AW9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AX9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AY9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="BA9" s="58">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -23374,7 +25471,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="58">
-        <f t="shared" ref="C10:AG10" si="8">$B10</f>
+        <f t="shared" ref="C10:BA10" si="8">$B10</f>
         <v>0</v>
       </c>
       <c r="D10" s="58">
@@ -23497,8 +25594,88 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
+      <c r="AH10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AK10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AL10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AM10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AN10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AP10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AR10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AS10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AT10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AU10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AV10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AW10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AX10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AY10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AZ10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="BA10" s="58">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>131</v>
       </c>
@@ -23506,7 +25683,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="58">
-        <f t="shared" ref="C11:AG11" si="9">$B11</f>
+        <f t="shared" ref="C11:BA11" si="9">$B11</f>
         <v>0</v>
       </c>
       <c r="D11" s="58">
@@ -23629,8 +25806,88 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
+      <c r="AH11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AK11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AL11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AM11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AN11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AP11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AR11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AS11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AT11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AU11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AV11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AW11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AY11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="AZ11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="BA11" s="58">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
@@ -23638,7 +25895,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="58">
-        <f t="shared" ref="C12:AG12" si="10">$B12</f>
+        <f t="shared" ref="C12:BA12" si="10">$B12</f>
         <v>0</v>
       </c>
       <c r="D12" s="58">
@@ -23761,8 +26018,88 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
+      <c r="AH12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AK12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AL12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AM12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AN12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AP12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AR12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AS12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AT12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AU12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AV12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AW12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AY12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AZ12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="BA12" s="58">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -23770,7 +26107,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="58">
-        <f t="shared" ref="C13:AG13" si="11">$B13</f>
+        <f t="shared" ref="C13:BA13" si="11">$B13</f>
         <v>0</v>
       </c>
       <c r="D13" s="58">
@@ -23893,8 +26230,88 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
+      <c r="AH13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AK13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AL13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AM13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AN13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AO13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AP13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AR13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AS13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AT13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AU13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AV13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AW13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AX13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AY13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AZ13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="BA13" s="58">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>133</v>
       </c>
@@ -23902,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="C14" s="58">
-        <f t="shared" ref="C14:AG14" si="12">$B14</f>
+        <f t="shared" ref="C14:BA14" si="12">$B14</f>
         <v>0</v>
       </c>
       <c r="D14" s="58">
@@ -24025,8 +26442,88 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
+      <c r="AH14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AK14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AL14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AM14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AO14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AP14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AR14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AS14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AT14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AU14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AV14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AW14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AX14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AY14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AZ14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="BA14" s="58">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>134</v>
       </c>
@@ -24034,7 +26531,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="58">
-        <f t="shared" ref="C15:AG15" si="13">$B15</f>
+        <f t="shared" ref="C15:BA15" si="13">$B15</f>
         <v>0</v>
       </c>
       <c r="D15" s="58">
@@ -24157,8 +26654,88 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
+      <c r="AH15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AK15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AN15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AO15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AP15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AR15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AS15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AT15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AU15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AV15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AW15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AX15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AY15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="BA15" s="58">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>135</v>
       </c>
@@ -24166,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="58">
-        <f t="shared" ref="C16:AG16" si="14">$B16</f>
+        <f t="shared" ref="C16:BA16" si="14">$B16</f>
         <v>0</v>
       </c>
       <c r="D16" s="58">
@@ -24289,8 +26866,88 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
+      <c r="AH16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AK16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AM16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AN16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AO16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AP16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AR16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AS16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AT16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AU16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AV16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AW16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AX16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AY16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AZ16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="BA16" s="58">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
@@ -24298,7 +26955,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="58">
-        <f t="shared" ref="C17:AG17" si="15">$B17</f>
+        <f t="shared" ref="C17:BA17" si="15">$B17</f>
         <v>0</v>
       </c>
       <c r="D17" s="58">
@@ -24421,22 +27078,102 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AH17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AK17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AM17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AN17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AO17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AP17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AR17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AS17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AT17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AU17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AV17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AW17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AX17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AY17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="AZ17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="BA17" s="58">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -25416,7 +28153,7 @@
   <sheetPr>
     <tabColor rgb="FF1E4E79"/>
   </sheetPr>
-  <dimension ref="A1:AG1000"/>
+  <dimension ref="A1:BA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.83203125" customWidth="1"/>
@@ -25424,7 +28161,7 @@
     <col min="5" max="33" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="29" t="s">
         <v>93</v>
       </c>
@@ -25524,8 +28261,68 @@
       <c r="AG1" s="62">
         <v>2050</v>
       </c>
+      <c r="AH1" s="107">
+        <v>2051</v>
+      </c>
+      <c r="AI1" s="108">
+        <v>2052</v>
+      </c>
+      <c r="AJ1" s="108">
+        <v>2053</v>
+      </c>
+      <c r="AK1" s="108">
+        <v>2054</v>
+      </c>
+      <c r="AL1" s="108">
+        <v>2055</v>
+      </c>
+      <c r="AM1" s="108">
+        <v>2056</v>
+      </c>
+      <c r="AN1" s="108">
+        <v>2057</v>
+      </c>
+      <c r="AO1" s="108">
+        <v>2058</v>
+      </c>
+      <c r="AP1" s="108">
+        <v>2059</v>
+      </c>
+      <c r="AQ1" s="108">
+        <v>2060</v>
+      </c>
+      <c r="AR1" s="108">
+        <v>2061</v>
+      </c>
+      <c r="AS1" s="108">
+        <v>2062</v>
+      </c>
+      <c r="AT1" s="108">
+        <v>2063</v>
+      </c>
+      <c r="AU1" s="108">
+        <v>2064</v>
+      </c>
+      <c r="AV1" s="108">
+        <v>2065</v>
+      </c>
+      <c r="AW1" s="108">
+        <v>2066</v>
+      </c>
+      <c r="AX1" s="108">
+        <v>2067</v>
+      </c>
+      <c r="AY1" s="108">
+        <v>2068</v>
+      </c>
+      <c r="AZ1" s="108">
+        <v>2069</v>
+      </c>
+      <c r="BA1" s="108">
+        <v>2070</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>126</v>
       </c>
@@ -25657,8 +28454,88 @@
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
+      <c r="AH2" s="110">
+        <f>AG2</f>
+        <v>0.65</v>
+      </c>
+      <c r="AI2" s="110">
+        <f t="shared" ref="AI2:BA16" si="1">AH2</f>
+        <v>0.65</v>
+      </c>
+      <c r="AJ2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AK2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AL2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AM2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AN2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AO2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AP2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AQ2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AR2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AS2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AT2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AU2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AV2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AW2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AX2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AY2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AZ2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="BA2" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>127</v>
       </c>
@@ -25667,131 +28544,211 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="C3" s="63">
-        <f t="shared" ref="C3:AG3" si="1">$B3</f>
+        <f t="shared" ref="C3:AG3" si="2">$B3</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="D3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="E3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="F3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="G3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="I3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="J3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="K3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="L3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="M3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="N3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="O3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="P3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="R3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="T3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="U3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="V3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="W3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="X3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Y3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Z3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AA3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AB3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AC3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AD3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AE3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AF3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AG3" s="63">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
+      <c r="AH3" s="110">
+        <f t="shared" ref="AH3:AW17" si="3">AG3</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AI3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AJ3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AK3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AM3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AP3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AQ3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AR3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AT3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AU3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AV3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AW3" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AX3" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AY3" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AZ3" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="BA3" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>128</v>
       </c>
@@ -25804,127 +28761,207 @@
         <v>0.45</v>
       </c>
       <c r="D4" s="63">
-        <f t="shared" ref="D4:AG4" si="2">$B$4</f>
+        <f t="shared" ref="D4:AG4" si="4">$B$4</f>
         <v>0.45</v>
       </c>
       <c r="E4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="F4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="G4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="H4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="I4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="J4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="K4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="L4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="M4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="N4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="O4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="P4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="Q4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="R4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="S4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="T4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="U4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="V4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="W4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="X4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="Y4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="Z4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AA4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AB4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AC4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AD4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AE4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AF4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
       <c r="AG4" s="63">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.45</v>
       </c>
+      <c r="AH4" s="110">
+        <f t="shared" si="3"/>
+        <v>0.45</v>
+      </c>
+      <c r="AI4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AJ4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AK4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AL4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AM4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AN4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AO4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AP4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AQ4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AR4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AS4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AT4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AU4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AV4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AW4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AX4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AY4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="AZ4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
+      <c r="BA4" s="110">
+        <f t="shared" si="1"/>
+        <v>0.45</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -25933,131 +28970,211 @@
         <v>0.37</v>
       </c>
       <c r="C5" s="63">
-        <f t="shared" ref="C5:AG5" si="3">$B5</f>
+        <f t="shared" ref="C5:AG5" si="5">$B5</f>
         <v>0.37</v>
       </c>
       <c r="D5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="E5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="F5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="G5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="H5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="I5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="J5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="K5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="L5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="M5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="N5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="O5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="P5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="Q5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="R5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="S5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="T5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="U5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="V5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="W5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="X5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="Y5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="Z5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AA5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AB5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AC5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AD5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AE5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AF5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AG5" s="63">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="AH5" s="110">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="E5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AI5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="F5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AJ5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="G5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AK5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="H5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AL5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="I5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AM5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="J5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AN5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="K5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AO5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="L5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AP5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="M5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AQ5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="N5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AR5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="O5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AS5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="P5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AT5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="Q5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AU5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="R5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AV5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="S5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AW5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="T5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AX5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="U5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AY5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="V5" s="63">
-        <f t="shared" si="3"/>
+      <c r="AZ5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="W5" s="63">
-        <f t="shared" si="3"/>
+      <c r="BA5" s="110">
+        <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="X5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="Y5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="Z5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AA5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AB5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AC5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AD5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AE5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AF5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
-      <c r="AG5" s="63">
-        <f t="shared" si="3"/>
-        <v>0.37</v>
-      </c>
     </row>
-    <row r="6" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>129</v>
       </c>
@@ -26066,131 +29183,211 @@
         <v>0.35</v>
       </c>
       <c r="C6" s="63">
-        <f t="shared" ref="C6:C7" si="4">$B6</f>
+        <f t="shared" ref="C6:C7" si="6">$B6</f>
         <v>0.35</v>
       </c>
       <c r="D6" s="63">
-        <f t="shared" ref="D6:D7" si="5">B6</f>
+        <f t="shared" ref="D6:D7" si="7">B6</f>
         <v>0.35</v>
       </c>
       <c r="E6" s="63">
-        <f t="shared" ref="E6:AG6" si="6">D6</f>
+        <f t="shared" ref="E6:AG6" si="8">D6</f>
         <v>0.35</v>
       </c>
       <c r="F6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="G6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="H6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="I6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="J6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="K6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="L6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="M6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="N6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="O6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="P6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="Q6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="R6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="S6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="T6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="U6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="V6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="W6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="X6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="Y6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="Z6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AA6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AB6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AC6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AD6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AE6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AF6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
       <c r="AG6" s="63">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
+      <c r="AH6" s="110">
+        <f t="shared" si="3"/>
+        <v>0.35</v>
+      </c>
+      <c r="AI6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AJ6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AK6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AL6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AM6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AN6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AO6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AP6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AQ6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AR6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AS6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AT6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AU6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AV6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AW6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AX6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AY6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="AZ6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
+      <c r="BA6" s="110">
+        <f t="shared" si="1"/>
+        <v>0.35</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -26199,131 +29396,211 @@
         <v>0.18</v>
       </c>
       <c r="C7" s="63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0.18</v>
       </c>
       <c r="D7" s="63">
-        <f t="shared" si="5"/>
-        <v>0.18</v>
-      </c>
-      <c r="E7" s="63">
-        <f t="shared" ref="E7:AG7" si="7">D7</f>
-        <v>0.18</v>
-      </c>
-      <c r="F7" s="63">
         <f t="shared" si="7"/>
         <v>0.18</v>
       </c>
+      <c r="E7" s="63">
+        <f t="shared" ref="E7:AG7" si="9">D7</f>
+        <v>0.18</v>
+      </c>
+      <c r="F7" s="63">
+        <f t="shared" si="9"/>
+        <v>0.18</v>
+      </c>
       <c r="G7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="H7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="I7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="J7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="K7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="L7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="M7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="N7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="O7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="P7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="Q7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="R7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="S7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="T7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="U7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="V7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="W7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="X7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="Y7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="Z7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AA7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AB7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AC7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AD7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AE7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AF7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
       <c r="AG7" s="63">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
+      <c r="AH7" s="110">
+        <f t="shared" si="3"/>
+        <v>0.18</v>
+      </c>
+      <c r="AI7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AJ7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AK7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AL7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AM7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AN7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AO7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AP7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AQ7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AR7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AT7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AX7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AY7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AZ7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="BA7" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>130</v>
       </c>
@@ -26336,127 +29613,207 @@
         <v>0.18</v>
       </c>
       <c r="D8" s="63">
-        <f t="shared" ref="D8:AG8" si="8">$B8</f>
+        <f t="shared" ref="D8:AG8" si="10">$B8</f>
         <v>0.18</v>
       </c>
       <c r="E8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="F8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="G8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="H8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="I8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="J8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="K8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="L8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="M8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="N8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="O8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="P8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="Q8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="R8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="S8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="T8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="U8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="V8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="W8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="X8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="Y8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="Z8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AA8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AB8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AC8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AD8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AE8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AF8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
       <c r="AG8" s="63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
+      <c r="AH8" s="110">
+        <f t="shared" si="3"/>
+        <v>0.18</v>
+      </c>
+      <c r="AI8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AJ8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AK8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AL8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AM8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AN8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AO8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AP8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AQ8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AR8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AS8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AT8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AU8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AV8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AW8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AX8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AY8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="AZ8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
+      <c r="BA8" s="110">
+        <f t="shared" si="1"/>
+        <v>0.18</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -26465,131 +29822,211 @@
         <v>0.5</v>
       </c>
       <c r="C9" s="63">
-        <f t="shared" ref="C9:AG9" si="9">$B9</f>
+        <f t="shared" ref="C9:AG9" si="11">$B9</f>
         <v>0.5</v>
       </c>
       <c r="D9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="E9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="F9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="G9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="H9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="I9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="J9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="K9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="L9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="M9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="N9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="O9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="P9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="Q9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="R9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="S9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="T9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="U9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="V9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="W9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="X9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="Y9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="Z9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AA9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AB9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AC9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AD9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AE9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AF9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="AG9" s="63">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
+      <c r="AH9" s="110">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AK9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA9" s="110">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -26598,131 +30035,211 @@
         <v>0.82</v>
       </c>
       <c r="C10" s="63">
-        <f t="shared" ref="C10:AG10" si="10">$B10</f>
+        <f t="shared" ref="C10:AG10" si="12">$B10</f>
         <v>0.82</v>
       </c>
       <c r="D10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="E10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="F10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="G10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="H10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="I10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="J10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="K10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="L10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="M10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="N10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="O10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="P10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="Q10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="R10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="S10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="T10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="U10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="V10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="W10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="X10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="Y10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="Z10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AA10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AB10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AC10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AD10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AE10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AF10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
       <c r="AG10" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
+      <c r="AH10" s="110">
+        <f t="shared" si="3"/>
+        <v>0.82</v>
+      </c>
+      <c r="AI10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AJ10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AK10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AL10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AM10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AN10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AO10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AP10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AQ10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AR10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AS10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AT10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AU10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AV10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AW10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AX10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AY10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="AZ10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
+      <c r="BA10" s="110">
+        <f t="shared" si="1"/>
+        <v>0.82</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>131</v>
       </c>
@@ -26731,131 +30248,211 @@
         <v>0.7</v>
       </c>
       <c r="C11" s="63">
-        <f t="shared" ref="C11:AG11" si="11">$B11</f>
+        <f t="shared" ref="C11:AG11" si="13">$B11</f>
         <v>0.7</v>
       </c>
       <c r="D11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="E11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="F11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="G11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="H11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="I11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="J11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="K11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="L11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="M11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="N11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="O11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="P11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="Q11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="R11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="S11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="T11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="U11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="V11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="W11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="X11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="Y11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="Z11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AA11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AB11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AC11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AD11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AE11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AF11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
       <c r="AG11" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
+      <c r="AH11" s="110">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AN11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA11" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
@@ -26864,131 +30461,211 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="C12" s="63">
-        <f t="shared" ref="C12:AG12" si="12">$B12</f>
+        <f t="shared" ref="C12:AG12" si="14">$B12</f>
         <v>0.28999999999999998</v>
       </c>
       <c r="D12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="E12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="F12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="G12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="H12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="I12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="J12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="K12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="L12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="M12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="N12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="O12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="P12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Q12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="R12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="S12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="T12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="U12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="V12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="W12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="X12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Y12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="Z12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AA12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AB12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AC12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AD12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AE12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AF12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
       <c r="AG12" s="63">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
+      <c r="AH12" s="110">
+        <f t="shared" si="3"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AI12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AJ12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AK12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AL12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AM12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AN12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AO12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AP12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AQ12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AR12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AS12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AT12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AU12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AV12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AW12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AX12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AY12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="AZ12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="BA12" s="110">
+        <f t="shared" si="1"/>
+        <v>0.28999999999999998</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -26997,131 +30674,211 @@
         <v>0.65</v>
       </c>
       <c r="C13" s="63">
-        <f t="shared" ref="C13:AG13" si="13">$B13</f>
+        <f t="shared" ref="C13:AG13" si="15">$B13</f>
         <v>0.65</v>
       </c>
       <c r="D13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="E13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="F13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="G13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="H13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="I13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="J13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="K13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="L13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="M13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="N13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="O13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="P13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="Q13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="R13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="S13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="T13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="U13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="V13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="W13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="X13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="Y13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="Z13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AA13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AB13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AC13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AD13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AE13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AF13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
       <c r="AG13" s="63">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
+      <c r="AH13" s="110">
+        <f t="shared" si="3"/>
+        <v>0.65</v>
+      </c>
+      <c r="AI13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AJ13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AK13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AL13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AM13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AN13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AO13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AP13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AQ13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AR13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AS13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AT13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AU13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AV13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AW13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AX13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AY13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="AZ13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="BA13" s="110">
+        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>133</v>
       </c>
@@ -27130,131 +30887,211 @@
         <v>0.37</v>
       </c>
       <c r="C14" s="63">
-        <f t="shared" ref="C14:AG14" si="14">$B14</f>
+        <f t="shared" ref="C14:AG14" si="16">$B14</f>
         <v>0.37</v>
       </c>
       <c r="D14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="E14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="F14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="G14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="H14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="I14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="J14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="K14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="L14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="M14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="N14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="O14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="P14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="Q14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="R14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="S14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="T14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="U14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="V14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="W14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="X14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="Y14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="Z14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AA14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AB14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AC14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AD14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AE14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AF14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
       <c r="AG14" s="63">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
+      <c r="AH14" s="110">
+        <f t="shared" si="3"/>
+        <v>0.37</v>
+      </c>
+      <c r="AI14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AJ14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AK14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AL14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AM14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AN14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AO14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AP14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AQ14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AR14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AS14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AT14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AU14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AV14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AW14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AX14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AY14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="AZ14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
+      <c r="BA14" s="110">
+        <f t="shared" si="1"/>
+        <v>0.37</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>134</v>
       </c>
@@ -27263,131 +31100,211 @@
         <v>0.7</v>
       </c>
       <c r="C15" s="63">
-        <f t="shared" ref="C15:AG15" si="15">$B15</f>
+        <f t="shared" ref="C15:AG15" si="17">$B15</f>
         <v>0.7</v>
       </c>
       <c r="D15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="E15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="F15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="G15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="H15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="I15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="J15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="K15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="L15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="M15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="N15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="O15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="P15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="Q15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="R15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="S15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="T15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="U15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="V15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="W15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="X15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="Y15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="Z15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AA15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AB15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AC15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AD15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AE15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AF15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
       <c r="AG15" s="63">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
+      <c r="AH15" s="110">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AN15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA15" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>135</v>
       </c>
@@ -27396,131 +31313,211 @@
         <v>0.7</v>
       </c>
       <c r="C16" s="63">
-        <f t="shared" ref="C16:AG16" si="16">$B16</f>
+        <f t="shared" ref="C16:AG16" si="18">$B16</f>
         <v>0.7</v>
       </c>
       <c r="D16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="E16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="F16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="G16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="H16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="I16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="J16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="K16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="L16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="M16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="N16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="O16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="P16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="Q16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="R16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="S16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="T16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="U16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="V16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="W16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="X16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="Y16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="Z16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AA16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AB16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AC16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AD16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AE16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AF16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
       <c r="AG16" s="63">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
+      <c r="AH16" s="110">
+        <f t="shared" si="3"/>
+        <v>0.7</v>
+      </c>
+      <c r="AI16" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AJ16" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AK16" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AL16" s="110">
+        <f t="shared" si="1"/>
+        <v>0.7</v>
+      </c>
+      <c r="AM16" s="110">
+        <f t="shared" ref="AI16:BA17" si="19">AL16</f>
+        <v>0.7</v>
+      </c>
+      <c r="AN16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AO16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AP16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AS16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AT16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AU16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AV16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AW16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AX16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AY16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="AZ16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
+      <c r="BA16" s="110">
+        <f t="shared" si="19"/>
+        <v>0.7</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>66</v>
       </c>
@@ -27529,145 +31526,225 @@
         <v>0.5</v>
       </c>
       <c r="C17" s="63">
-        <f t="shared" ref="C17:AG17" si="17">$B17</f>
+        <f t="shared" ref="C17:AG17" si="20">$B17</f>
         <v>0.5</v>
       </c>
       <c r="D17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="E17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="F17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="G17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="H17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="I17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="J17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="K17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="L17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="M17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="N17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="O17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="P17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="Q17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="R17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="S17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="T17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="U17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="V17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="W17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="X17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="Y17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="Z17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AA17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AB17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AC17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AD17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AE17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AF17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
       <c r="AG17" s="63">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
+      <c r="AH17" s="110">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="AI17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AJ17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AK17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AL17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AM17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AN17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AO17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AP17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AQ17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AR17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AS17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AT17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AU17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AV17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AW17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AX17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="AZ17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
+      <c r="BA17" s="110">
+        <f t="shared" si="19"/>
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>

--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A43400-EFB8-DB4F-9A18-366DE4E70F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CFDB6A-613F-F74A-AF36-251C24C31E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="176">
   <si>
     <t>BAU Expected Capacity Factors</t>
   </si>
@@ -614,6 +614,15 @@
   <si>
     <t>https://iopscience.iop.org/article/10.1088/1755-1315/753/1/012048/pdf</t>
   </si>
+  <si>
+    <t>Amid Global Crises, Nuclear Power Provides Energy Security with Increased Electricity Generation in 2021</t>
+  </si>
+  <si>
+    <t>https://www.iaea.org/newscenter/news/amid-global-crises-nuclear-power-provides-energy-security-with-increased-electricity-generation-in-2021</t>
+  </si>
+  <si>
+    <t> In 2021, the global median capacity factor was 85.6%, in line with recent years. Pressurized water reactors (PWR) and pressurized heavy water moderated, and cooled reactors (PHWR) have been the best performing reactors since 2011, with median capacity factors of 82% and 81%, respectively.</t>
+  </si>
 </sst>
 </file>
 
@@ -625,7 +634,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.000"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -770,6 +779,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1030,7 +1045,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1190,6 +1205,21 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="167" fontId="3" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1248,23 +1278,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="10" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="10" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1294,8 +1315,8 @@
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>8255000</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>101600</xdr:rowOff>
     </xdr:to>
@@ -1340,8 +1361,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>812800</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1581,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1035"/>
+  <dimension ref="A1:I1041"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="26" width="8.6640625" customWidth="1"/>
@@ -1601,16 +1622,16 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
-      <c r="I3" s="81"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="86"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1776,235 +1797,265 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="76" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="65"/>
     </row>
-    <row r="35" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="74" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="78">
         <v>2010</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="65" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="76" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="65"/>
     </row>
-    <row r="40" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="74" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="78">
         <v>2020</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="65" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="76" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
-      <c r="B44" s="65"/>
+      <c r="B44" s="76"/>
     </row>
-    <row r="45" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="74" t="s">
+        <v>167</v>
+      </c>
     </row>
-    <row r="46" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+    <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2"/>
+      <c r="B46" s="110">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="2"/>
+      <c r="B47" s="65" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="2"/>
+      <c r="B48" s="76" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2"/>
+      <c r="B49" s="76"/>
+    </row>
+    <row r="50" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2"/>
+      <c r="B50" s="65"/>
+    </row>
+    <row r="51" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="2"/>
+      <c r="B52" s="2"/>
     </row>
-    <row r="47" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="82" t="s">
+    <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="83"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
     </row>
-    <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="83"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
+    <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="88"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="88"/>
+      <c r="E54" s="88"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="88"/>
+      <c r="H54" s="88"/>
+      <c r="I54" s="88"/>
     </row>
-    <row r="49" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
+    <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B55" s="88"/>
+      <c r="C55" s="88"/>
+      <c r="D55" s="88"/>
+      <c r="E55" s="88"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="88"/>
+      <c r="I55" s="88"/>
     </row>
-    <row r="50" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
+    <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B56" s="88"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="88"/>
+      <c r="E56" s="88"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="88"/>
+      <c r="H56" s="88"/>
+      <c r="I56" s="88"/>
     </row>
-    <row r="51" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="83"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
+    <row r="57" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B57" s="88"/>
+      <c r="C57" s="88"/>
+      <c r="D57" s="88"/>
+      <c r="E57" s="88"/>
+      <c r="F57" s="88"/>
+      <c r="G57" s="88"/>
+      <c r="H57" s="88"/>
+      <c r="I57" s="88"/>
     </row>
-    <row r="52" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="83"/>
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
+    <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B58" s="88"/>
+      <c r="C58" s="88"/>
+      <c r="D58" s="88"/>
+      <c r="E58" s="88"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="88"/>
+      <c r="H58" s="88"/>
+      <c r="I58" s="88"/>
     </row>
-    <row r="53" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
+    <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B59" s="88"/>
+      <c r="C59" s="88"/>
+      <c r="D59" s="88"/>
+      <c r="E59" s="88"/>
+      <c r="F59" s="88"/>
+      <c r="G59" s="88"/>
+      <c r="H59" s="88"/>
+      <c r="I59" s="88"/>
     </row>
-    <row r="54" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
+    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="88"/>
+      <c r="C60" s="88"/>
+      <c r="D60" s="88"/>
+      <c r="E60" s="88"/>
+      <c r="F60" s="88"/>
+      <c r="G60" s="88"/>
+      <c r="H60" s="88"/>
+      <c r="I60" s="88"/>
     </row>
-    <row r="55" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="83"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
+    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="88"/>
+      <c r="C61" s="88"/>
+      <c r="D61" s="88"/>
+      <c r="E61" s="88"/>
+      <c r="F61" s="88"/>
+      <c r="G61" s="88"/>
+      <c r="H61" s="88"/>
+      <c r="I61" s="88"/>
     </row>
-    <row r="56" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="83"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
+    <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="88"/>
+      <c r="C62" s="88"/>
+      <c r="D62" s="88"/>
+      <c r="E62" s="88"/>
+      <c r="F62" s="88"/>
+      <c r="G62" s="88"/>
+      <c r="H62" s="88"/>
+      <c r="I62" s="88"/>
     </row>
-    <row r="57" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="83"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
+    <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B63" s="88"/>
+      <c r="C63" s="88"/>
+      <c r="D63" s="88"/>
+      <c r="E63" s="88"/>
+      <c r="F63" s="88"/>
+      <c r="G63" s="88"/>
+      <c r="H63" s="88"/>
+      <c r="I63" s="88"/>
     </row>
-    <row r="58" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
+    <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B64" s="88"/>
+      <c r="C64" s="88"/>
+      <c r="D64" s="88"/>
+      <c r="E64" s="88"/>
+      <c r="F64" s="88"/>
+      <c r="G64" s="88"/>
+      <c r="H64" s="88"/>
+      <c r="I64" s="88"/>
     </row>
-    <row r="59" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="83"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
+    <row r="65" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="88"/>
+      <c r="C65" s="88"/>
+      <c r="D65" s="88"/>
+      <c r="E65" s="88"/>
+      <c r="F65" s="88"/>
+      <c r="G65" s="88"/>
+      <c r="H65" s="88"/>
+      <c r="I65" s="88"/>
     </row>
-    <row r="60" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="111" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2960,10 +3011,16 @@
     <row r="1033" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1034" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1035" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1036" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1037" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1038" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1039" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1040" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1041" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B47:I59"/>
+    <mergeCell ref="B53:I65"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2994,11 +3051,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3009,14 +3066,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="97" t="s">
+      <c r="B3" s="90"/>
+      <c r="C3" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="85"/>
+      <c r="D3" s="90"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -3087,14 +3144,14 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="99" t="s">
+      <c r="B4" s="92"/>
+      <c r="C4" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="85"/>
+      <c r="D4" s="90"/>
       <c r="E4" s="12" t="s">
         <v>25</v>
       </c>
@@ -3176,12 +3233,12 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="88"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="99" t="s">
+      <c r="A5" s="93"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="85"/>
+      <c r="D5" s="90"/>
       <c r="E5" s="12">
         <v>3</v>
       </c>
@@ -3260,14 +3317,14 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="85"/>
-      <c r="C6" s="99" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="85"/>
+      <c r="D6" s="90"/>
       <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
@@ -3346,14 +3403,14 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="99" t="s">
+      <c r="B7" s="92"/>
+      <c r="C7" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="85"/>
+      <c r="D7" s="90"/>
       <c r="E7" s="12" t="s">
         <v>28</v>
       </c>
@@ -3432,12 +3489,12 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="88"/>
-      <c r="B8" s="89"/>
-      <c r="C8" s="99" t="s">
+      <c r="A8" s="93"/>
+      <c r="B8" s="94"/>
+      <c r="C8" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="85"/>
+      <c r="D8" s="90"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -3516,14 +3573,14 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="99" t="s">
+      <c r="B9" s="92"/>
+      <c r="C9" s="104" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="85"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="12" t="s">
         <v>32</v>
       </c>
@@ -3602,12 +3659,12 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="91"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="99" t="s">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="85"/>
+      <c r="D10" s="90"/>
       <c r="E10" s="12" t="s">
         <v>28</v>
       </c>
@@ -3686,12 +3743,12 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="91"/>
-      <c r="B11" s="92"/>
-      <c r="C11" s="99" t="s">
+      <c r="A11" s="96"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="85"/>
+      <c r="D11" s="90"/>
       <c r="E11" s="12" t="s">
         <v>28</v>
       </c>
@@ -3770,12 +3827,12 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="88"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="99" t="s">
+      <c r="A12" s="93"/>
+      <c r="B12" s="94"/>
+      <c r="C12" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="85"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="12" t="s">
         <v>28</v>
       </c>
@@ -3820,14 +3877,14 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="87"/>
-      <c r="C13" s="99" t="s">
+      <c r="B13" s="92"/>
+      <c r="C13" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="85"/>
+      <c r="D13" s="90"/>
       <c r="E13" s="12" t="s">
         <v>37</v>
       </c>
@@ -3905,12 +3962,12 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="99" t="s">
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="85"/>
+      <c r="D14" s="90"/>
       <c r="E14" s="12">
         <v>3</v>
       </c>
@@ -4149,14 +4206,14 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="92"/>
+      <c r="C17" s="104" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="85"/>
+      <c r="D17" s="90"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
@@ -4196,12 +4253,12 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="99" t="s">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="85"/>
+      <c r="D18" s="90"/>
       <c r="E18" s="12">
         <v>1</v>
       </c>
@@ -4244,14 +4301,14 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="93" t="s">
+      <c r="A19" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="99" t="s">
+      <c r="B19" s="92"/>
+      <c r="C19" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="85"/>
+      <c r="D19" s="90"/>
       <c r="E19" s="12" t="s">
         <v>37</v>
       </c>
@@ -4304,12 +4361,12 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="91"/>
-      <c r="B20" s="92"/>
-      <c r="C20" s="99" t="s">
+      <c r="A20" s="96"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="85"/>
+      <c r="D20" s="90"/>
       <c r="E20" s="12" t="s">
         <v>37</v>
       </c>
@@ -4368,12 +4425,12 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="88"/>
-      <c r="B21" s="89"/>
-      <c r="C21" s="99" t="s">
+      <c r="A21" s="93"/>
+      <c r="B21" s="94"/>
+      <c r="C21" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="85"/>
+      <c r="D21" s="90"/>
       <c r="E21" s="12">
         <v>2</v>
       </c>
@@ -4432,14 +4489,14 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="85"/>
-      <c r="C22" s="99" t="s">
+      <c r="B22" s="90"/>
+      <c r="C22" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="85"/>
+      <c r="D22" s="90"/>
       <c r="E22" s="12">
         <v>2</v>
       </c>
@@ -4464,14 +4521,14 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="99" t="s">
+      <c r="B23" s="92"/>
+      <c r="C23" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="85"/>
+      <c r="D23" s="90"/>
       <c r="E23" s="12" t="s">
         <v>28</v>
       </c>
@@ -4496,12 +4553,12 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="91"/>
-      <c r="B24" s="92"/>
-      <c r="C24" s="100" t="s">
+      <c r="A24" s="96"/>
+      <c r="B24" s="97"/>
+      <c r="C24" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="85"/>
+      <c r="D24" s="90"/>
       <c r="E24" s="12">
         <v>3</v>
       </c>
@@ -4559,12 +4616,12 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="100" t="s">
+      <c r="A25" s="96"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="85"/>
+      <c r="D25" s="90"/>
       <c r="E25" s="12">
         <v>3</v>
       </c>
@@ -4592,12 +4649,12 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="100" t="s">
+      <c r="A26" s="96"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="85"/>
+      <c r="D26" s="90"/>
       <c r="E26" s="12">
         <v>3</v>
       </c>
@@ -4625,12 +4682,12 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="88"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="99" t="s">
+      <c r="A27" s="93"/>
+      <c r="B27" s="94"/>
+      <c r="C27" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="85"/>
+      <c r="D27" s="90"/>
       <c r="E27" s="12">
         <v>3</v>
       </c>
@@ -4801,12 +4858,12 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="101" t="s">
+      <c r="F35" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27" t="s">
@@ -5506,12 +5563,12 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="102" t="s">
+      <c r="A53" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="81"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="86"/>
       <c r="E53" s="26" t="s">
         <v>10</v>
       </c>
@@ -5521,11 +5578,11 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="101" t="s">
+      <c r="F54" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
+      <c r="G54" s="88"/>
+      <c r="H54" s="88"/>
     </row>
     <row r="55" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27" t="s">
@@ -6313,12 +6370,12 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="103" t="s">
+      <c r="A70" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="80"/>
-      <c r="C70" s="80"/>
-      <c r="D70" s="81"/>
+      <c r="B70" s="85"/>
+      <c r="C70" s="85"/>
+      <c r="D70" s="86"/>
       <c r="E70" s="26" t="s">
         <v>10</v>
       </c>
@@ -7848,11 +7905,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="86"/>
       <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
@@ -7863,14 +7920,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="96" t="s">
+      <c r="A3" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="97" t="s">
+      <c r="B3" s="90"/>
+      <c r="C3" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="85"/>
+      <c r="D3" s="90"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -7906,14 +7963,14 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="92"/>
+      <c r="C4" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="85"/>
+      <c r="D4" s="90"/>
       <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
@@ -7958,12 +8015,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="91"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="99" t="s">
+      <c r="A5" s="96"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="85"/>
+      <c r="D5" s="90"/>
       <c r="E5" s="12" t="s">
         <v>28</v>
       </c>
@@ -8008,12 +8065,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="88"/>
-      <c r="B6" s="89"/>
-      <c r="C6" s="99" t="s">
+      <c r="A6" s="93"/>
+      <c r="B6" s="94"/>
+      <c r="C6" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="85"/>
+      <c r="D6" s="90"/>
       <c r="E6" s="12">
         <v>1</v>
       </c>
@@ -8058,14 +8115,14 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="104" t="s">
+      <c r="B7" s="90"/>
+      <c r="C7" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="85"/>
+      <c r="D7" s="90"/>
       <c r="E7" s="12">
         <v>1</v>
       </c>
@@ -8110,14 +8167,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="104" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="85"/>
+      <c r="D8" s="90"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -8162,12 +8219,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="91"/>
-      <c r="B9" s="92"/>
-      <c r="C9" s="104" t="s">
+      <c r="A9" s="96"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="109" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="85"/>
+      <c r="D9" s="90"/>
       <c r="E9" s="12">
         <v>1</v>
       </c>
@@ -8212,12 +8269,12 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="99" t="s">
+      <c r="A10" s="93"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="85"/>
+      <c r="D10" s="90"/>
       <c r="E10" s="12">
         <v>1</v>
       </c>
@@ -8273,14 +8330,14 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="90" t="s">
+      <c r="A11" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="87"/>
-      <c r="C11" s="104" t="s">
+      <c r="B11" s="92"/>
+      <c r="C11" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="85"/>
+      <c r="D11" s="90"/>
       <c r="E11" s="12">
         <v>1</v>
       </c>
@@ -8325,12 +8382,12 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="91"/>
-      <c r="B12" s="92"/>
-      <c r="C12" s="104" t="s">
+      <c r="A12" s="96"/>
+      <c r="B12" s="97"/>
+      <c r="C12" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="85"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="12">
         <v>1</v>
       </c>
@@ -8375,12 +8432,12 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="91"/>
-      <c r="B13" s="92"/>
-      <c r="C13" s="104" t="s">
+      <c r="A13" s="96"/>
+      <c r="B13" s="97"/>
+      <c r="C13" s="109" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="85"/>
+      <c r="D13" s="90"/>
       <c r="E13" s="12">
         <v>1</v>
       </c>
@@ -8425,12 +8482,12 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="89"/>
-      <c r="C14" s="104" t="s">
+      <c r="A14" s="93"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="109" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="85"/>
+      <c r="D14" s="90"/>
       <c r="E14" s="12">
         <v>1</v>
       </c>
@@ -8567,25 +8624,25 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="90" t="s">
+      <c r="A17" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="87"/>
-      <c r="C17" s="104" t="s">
+      <c r="B17" s="92"/>
+      <c r="C17" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="85"/>
+      <c r="D17" s="90"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="89"/>
-      <c r="C18" s="104" t="s">
+      <c r="A18" s="93"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="85"/>
+      <c r="D18" s="90"/>
       <c r="E18" s="12">
         <v>2</v>
       </c>
@@ -8594,14 +8651,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="90" t="s">
+      <c r="A19" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="104" t="s">
+      <c r="B19" s="92"/>
+      <c r="C19" s="109" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="85"/>
+      <c r="D19" s="90"/>
       <c r="E19" s="12">
         <v>1</v>
       </c>
@@ -8619,12 +8676,12 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="88"/>
-      <c r="B20" s="89"/>
-      <c r="C20" s="99" t="s">
+      <c r="A20" s="93"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="104" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="85"/>
+      <c r="D20" s="90"/>
       <c r="E20" s="12">
         <v>1</v>
       </c>
@@ -8645,14 +8702,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="93" t="s">
+      <c r="A21" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="87"/>
-      <c r="C21" s="99" t="s">
+      <c r="B21" s="92"/>
+      <c r="C21" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="85"/>
+      <c r="D21" s="90"/>
       <c r="E21" s="12" t="s">
         <v>28</v>
       </c>
@@ -8673,8 +8730,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="88"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="93"/>
+      <c r="B22" s="94"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8699,14 +8756,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="99" t="s">
+      <c r="B23" s="90"/>
+      <c r="C23" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="85"/>
+      <c r="D23" s="90"/>
       <c r="E23" s="12">
         <v>1</v>
       </c>
@@ -8727,14 +8784,14 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="99" t="s">
+      <c r="B24" s="92"/>
+      <c r="C24" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="85"/>
+      <c r="D24" s="90"/>
       <c r="E24" s="12">
         <v>1</v>
       </c>
@@ -8755,12 +8812,12 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="91"/>
-      <c r="B25" s="92"/>
-      <c r="C25" s="104" t="s">
+      <c r="A25" s="96"/>
+      <c r="B25" s="97"/>
+      <c r="C25" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="85"/>
+      <c r="D25" s="90"/>
       <c r="E25" s="12">
         <v>2</v>
       </c>
@@ -8781,12 +8838,12 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91"/>
-      <c r="B26" s="92"/>
-      <c r="C26" s="100" t="s">
+      <c r="A26" s="96"/>
+      <c r="B26" s="97"/>
+      <c r="C26" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="85"/>
+      <c r="D26" s="90"/>
       <c r="E26" s="12">
         <v>2</v>
       </c>
@@ -8807,12 +8864,12 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="91"/>
-      <c r="B27" s="92"/>
-      <c r="C27" s="100" t="s">
+      <c r="A27" s="96"/>
+      <c r="B27" s="97"/>
+      <c r="C27" s="105" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="85"/>
+      <c r="D27" s="90"/>
       <c r="E27" s="12">
         <v>2</v>
       </c>
@@ -8833,12 +8890,12 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
-      <c r="B28" s="89"/>
-      <c r="C28" s="99" t="s">
+      <c r="A28" s="93"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="85"/>
+      <c r="D28" s="90"/>
       <c r="E28" s="12">
         <v>2</v>
       </c>
@@ -18865,10 +18922,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0CDDCDD-446B-FA4F-B242-594ECC6C0CA3}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
+    <col min="14" max="14" width="134.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -18900,7 +18958,8 @@
         <v>128</v>
       </c>
       <c r="B4">
-        <v>0.45</v>
+        <f>0.85</f>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -19006,6 +19065,11 @@
       </c>
       <c r="B17">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="34" spans="14:14" ht="51" x14ac:dyDescent="0.2">
+      <c r="N34" s="112" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -19129,68 +19193,68 @@
       <c r="AG1" s="57" t="s">
         <v>125</v>
       </c>
-      <c r="AH1" s="107">
+      <c r="AH1" s="80">
         <v>2051</v>
       </c>
-      <c r="AI1" s="108">
+      <c r="AI1" s="81">
         <v>2052</v>
       </c>
-      <c r="AJ1" s="108">
+      <c r="AJ1" s="81">
         <v>2053</v>
       </c>
-      <c r="AK1" s="108">
+      <c r="AK1" s="81">
         <v>2054</v>
       </c>
-      <c r="AL1" s="108">
+      <c r="AL1" s="81">
         <v>2055</v>
       </c>
-      <c r="AM1" s="108">
+      <c r="AM1" s="81">
         <v>2056</v>
       </c>
-      <c r="AN1" s="108">
+      <c r="AN1" s="81">
         <v>2057</v>
       </c>
-      <c r="AO1" s="108">
+      <c r="AO1" s="81">
         <v>2058</v>
       </c>
-      <c r="AP1" s="108">
+      <c r="AP1" s="81">
         <v>2059</v>
       </c>
-      <c r="AQ1" s="108">
+      <c r="AQ1" s="81">
         <v>2060</v>
       </c>
-      <c r="AR1" s="108">
+      <c r="AR1" s="81">
         <v>2061</v>
       </c>
-      <c r="AS1" s="108">
+      <c r="AS1" s="81">
         <v>2062</v>
       </c>
-      <c r="AT1" s="108">
+      <c r="AT1" s="81">
         <v>2063</v>
       </c>
-      <c r="AU1" s="108">
+      <c r="AU1" s="81">
         <v>2064</v>
       </c>
-      <c r="AV1" s="108">
+      <c r="AV1" s="81">
         <v>2065</v>
       </c>
-      <c r="AW1" s="108">
+      <c r="AW1" s="81">
         <v>2066</v>
       </c>
-      <c r="AX1" s="108">
+      <c r="AX1" s="81">
         <v>2067</v>
       </c>
-      <c r="AY1" s="108">
+      <c r="AY1" s="81">
         <v>2068</v>
       </c>
-      <c r="AZ1" s="108">
+      <c r="AZ1" s="81">
         <v>2069</v>
       </c>
-      <c r="BA1" s="108">
+      <c r="BA1" s="81">
         <v>2070</v>
       </c>
-      <c r="BB1" s="105"/>
-      <c r="BC1" s="105"/>
+      <c r="BB1" s="70"/>
+      <c r="BC1" s="70"/>
     </row>
     <row r="2" spans="1:55" s="52" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
@@ -19320,87 +19384,87 @@
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
-      <c r="AG2" s="106">
+      <c r="AG2" s="79">
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
-      <c r="AH2" s="109">
+      <c r="AH2" s="82">
         <f>AG2</f>
         <v>0.65</v>
       </c>
-      <c r="AI2" s="109">
+      <c r="AI2" s="82">
         <f t="shared" ref="AI2:BA16" si="1">AH2</f>
         <v>0.65</v>
       </c>
-      <c r="AJ2" s="109">
+      <c r="AJ2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AK2" s="109">
+      <c r="AK2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AL2" s="109">
+      <c r="AL2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AM2" s="109">
+      <c r="AM2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AN2" s="109">
+      <c r="AN2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AO2" s="109">
+      <c r="AO2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AP2" s="109">
+      <c r="AP2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AQ2" s="109">
+      <c r="AQ2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AR2" s="109">
+      <c r="AR2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AS2" s="109">
+      <c r="AS2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AT2" s="109">
+      <c r="AT2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AU2" s="109">
+      <c r="AU2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AV2" s="109">
+      <c r="AV2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AW2" s="109">
+      <c r="AW2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AX2" s="109">
+      <c r="AX2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AY2" s="109">
+      <c r="AY2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AZ2" s="109">
+      <c r="AZ2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="BA2" s="109">
+      <c r="BA2" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
@@ -19533,87 +19597,87 @@
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AG3" s="106">
+      <c r="AG3" s="79">
         <f t="shared" si="0"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AH3" s="109">
+      <c r="AH3" s="82">
         <f t="shared" ref="AH3:AW17" si="3">AG3</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AI3" s="109">
+      <c r="AI3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ3" s="109">
+      <c r="AJ3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AK3" s="109">
+      <c r="AK3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AL3" s="109">
+      <c r="AL3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AM3" s="109">
+      <c r="AM3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AN3" s="109">
+      <c r="AN3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AO3" s="109">
+      <c r="AO3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AP3" s="109">
+      <c r="AP3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AQ3" s="109">
+      <c r="AQ3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AR3" s="109">
+      <c r="AR3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AS3" s="109">
+      <c r="AS3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AT3" s="109">
+      <c r="AT3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AU3" s="109">
+      <c r="AU3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AV3" s="109">
+      <c r="AV3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AW3" s="109">
+      <c r="AW3" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AX3" s="109">
+      <c r="AX3" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AY3" s="109">
+      <c r="AY3" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AZ3" s="109">
+      <c r="AZ3" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="BA3" s="109">
+      <c r="BA3" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
@@ -19624,211 +19688,211 @@
       </c>
       <c r="B4" s="64">
         <f>'Capacity Factor-Reports'!B4</f>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="C4" s="64">
         <f t="shared" si="2"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="E4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="F4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="G4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="I4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="J4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="K4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="L4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="N4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="O4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="P4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Q4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="R4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="S4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="T4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="U4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="V4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="W4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="X4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Y4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Z4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AA4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AB4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AC4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AD4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AE4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AF4" s="64">
         <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-      <c r="AG4" s="106">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-      <c r="AH4" s="109">
+        <v>0.85</v>
+      </c>
+      <c r="AG4" s="79">
+        <f t="shared" si="0"/>
+        <v>0.85</v>
+      </c>
+      <c r="AH4" s="82">
         <f t="shared" si="3"/>
-        <v>0.45</v>
-      </c>
-      <c r="AI4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AJ4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AK4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AL4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AM4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AN4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AO4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AP4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AQ4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AR4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AS4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AT4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AU4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AV4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AW4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AX4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AY4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AZ4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="BA4" s="109">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
+        <v>0.85</v>
+      </c>
+      <c r="AI4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AJ4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AK4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AL4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AM4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AN4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AO4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AP4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AQ4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AR4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AS4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AT4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AU4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AV4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AW4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AX4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AY4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AZ4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="BA4" s="82">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19959,87 +20023,87 @@
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
-      <c r="AG5" s="106">
+      <c r="AG5" s="79">
         <f t="shared" si="0"/>
         <v>0.37</v>
       </c>
-      <c r="AH5" s="109">
+      <c r="AH5" s="82">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="AI5" s="109">
+      <c r="AI5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AJ5" s="109">
+      <c r="AJ5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AK5" s="109">
+      <c r="AK5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AL5" s="109">
+      <c r="AL5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AM5" s="109">
+      <c r="AM5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AN5" s="109">
+      <c r="AN5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AO5" s="109">
+      <c r="AO5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AP5" s="109">
+      <c r="AP5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AQ5" s="109">
+      <c r="AQ5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AR5" s="109">
+      <c r="AR5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AS5" s="109">
+      <c r="AS5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AT5" s="109">
+      <c r="AT5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AU5" s="109">
+      <c r="AU5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AV5" s="109">
+      <c r="AV5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AW5" s="109">
+      <c r="AW5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AX5" s="109">
+      <c r="AX5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AY5" s="109">
+      <c r="AY5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AZ5" s="109">
+      <c r="AZ5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="BA5" s="109">
+      <c r="BA5" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -20172,87 +20236,87 @@
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
-      <c r="AG6" s="106">
+      <c r="AG6" s="79">
         <f t="shared" si="0"/>
         <v>0.35</v>
       </c>
-      <c r="AH6" s="109">
+      <c r="AH6" s="82">
         <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
-      <c r="AI6" s="109">
+      <c r="AI6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AJ6" s="109">
+      <c r="AJ6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AK6" s="109">
+      <c r="AK6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AL6" s="109">
+      <c r="AL6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AM6" s="109">
+      <c r="AM6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AN6" s="109">
+      <c r="AN6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AO6" s="109">
+      <c r="AO6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AP6" s="109">
+      <c r="AP6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AQ6" s="109">
+      <c r="AQ6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AR6" s="109">
+      <c r="AR6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AS6" s="109">
+      <c r="AS6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AT6" s="109">
+      <c r="AT6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AU6" s="109">
+      <c r="AU6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AV6" s="109">
+      <c r="AV6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AW6" s="109">
+      <c r="AW6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AX6" s="109">
+      <c r="AX6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AY6" s="109">
+      <c r="AY6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AZ6" s="109">
+      <c r="AZ6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="BA6" s="109">
+      <c r="BA6" s="82">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
@@ -20385,87 +20449,87 @@
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AG7" s="106">
+      <c r="AG7" s="79">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AH7" s="109">
+      <c r="AH7" s="82">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="AI7" s="109">
+      <c r="AI7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AJ7" s="109">
+      <c r="AJ7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AK7" s="109">
+      <c r="AK7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AL7" s="109">
+      <c r="AL7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AM7" s="109">
+      <c r="AM7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AN7" s="109">
+      <c r="AN7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AO7" s="109">
+      <c r="AO7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AP7" s="109">
+      <c r="AP7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AQ7" s="109">
+      <c r="AQ7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AR7" s="109">
+      <c r="AR7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AS7" s="109">
+      <c r="AS7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AT7" s="109">
+      <c r="AT7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AU7" s="109">
+      <c r="AU7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AV7" s="109">
+      <c r="AV7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AW7" s="109">
+      <c r="AW7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AX7" s="109">
+      <c r="AX7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AY7" s="109">
+      <c r="AY7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AZ7" s="109">
+      <c r="AZ7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="BA7" s="109">
+      <c r="BA7" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
@@ -20598,87 +20662,87 @@
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AG8" s="106">
+      <c r="AG8" s="79">
         <f t="shared" si="0"/>
         <v>0.18</v>
       </c>
-      <c r="AH8" s="109">
+      <c r="AH8" s="82">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="AI8" s="109">
+      <c r="AI8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AJ8" s="109">
+      <c r="AJ8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AK8" s="109">
+      <c r="AK8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AL8" s="109">
+      <c r="AL8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AM8" s="109">
+      <c r="AM8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AN8" s="109">
+      <c r="AN8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AO8" s="109">
+      <c r="AO8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AP8" s="109">
+      <c r="AP8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AQ8" s="109">
+      <c r="AQ8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AR8" s="109">
+      <c r="AR8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AS8" s="109">
+      <c r="AS8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AT8" s="109">
+      <c r="AT8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AU8" s="109">
+      <c r="AU8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AV8" s="109">
+      <c r="AV8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AW8" s="109">
+      <c r="AW8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AX8" s="109">
+      <c r="AX8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AY8" s="109">
+      <c r="AY8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AZ8" s="109">
+      <c r="AZ8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="BA8" s="109">
+      <c r="BA8" s="82">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
@@ -20811,87 +20875,87 @@
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="AG9" s="106">
+      <c r="AG9" s="79">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="AH9" s="109">
+      <c r="AH9" s="82">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="AI9" s="109">
+      <c r="AI9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AJ9" s="109">
+      <c r="AJ9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AK9" s="109">
+      <c r="AK9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AL9" s="109">
+      <c r="AL9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AM9" s="109">
+      <c r="AM9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AN9" s="109">
+      <c r="AN9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AO9" s="109">
+      <c r="AO9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AP9" s="109">
+      <c r="AP9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AQ9" s="109">
+      <c r="AQ9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AR9" s="109">
+      <c r="AR9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AS9" s="109">
+      <c r="AS9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AT9" s="109">
+      <c r="AT9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AU9" s="109">
+      <c r="AU9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AV9" s="109">
+      <c r="AV9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AW9" s="109">
+      <c r="AW9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AX9" s="109">
+      <c r="AX9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AY9" s="109">
+      <c r="AY9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AZ9" s="109">
+      <c r="AZ9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="BA9" s="109">
+      <c r="BA9" s="82">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -21024,87 +21088,87 @@
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
-      <c r="AG10" s="106">
+      <c r="AG10" s="79">
         <f t="shared" si="0"/>
         <v>0.82</v>
       </c>
-      <c r="AH10" s="109">
+      <c r="AH10" s="82">
         <f t="shared" si="3"/>
         <v>0.82</v>
       </c>
-      <c r="AI10" s="109">
+      <c r="AI10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AJ10" s="109">
+      <c r="AJ10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AK10" s="109">
+      <c r="AK10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AL10" s="109">
+      <c r="AL10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AM10" s="109">
+      <c r="AM10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AN10" s="109">
+      <c r="AN10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AO10" s="109">
+      <c r="AO10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AP10" s="109">
+      <c r="AP10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AQ10" s="109">
+      <c r="AQ10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AR10" s="109">
+      <c r="AR10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AS10" s="109">
+      <c r="AS10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AT10" s="109">
+      <c r="AT10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AU10" s="109">
+      <c r="AU10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AV10" s="109">
+      <c r="AV10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AW10" s="109">
+      <c r="AW10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AX10" s="109">
+      <c r="AX10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AY10" s="109">
+      <c r="AY10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AZ10" s="109">
+      <c r="AZ10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="BA10" s="109">
+      <c r="BA10" s="82">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -21237,87 +21301,87 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG11" s="106">
+      <c r="AG11" s="79">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AH11" s="109">
+      <c r="AH11" s="82">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI11" s="109">
+      <c r="AI11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ11" s="109">
+      <c r="AJ11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK11" s="109">
+      <c r="AK11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL11" s="109">
+      <c r="AL11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM11" s="109">
+      <c r="AM11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AN11" s="109">
+      <c r="AN11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AO11" s="109">
+      <c r="AO11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AP11" s="109">
+      <c r="AP11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AQ11" s="109">
+      <c r="AQ11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AR11" s="109">
+      <c r="AR11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AS11" s="109">
+      <c r="AS11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AT11" s="109">
+      <c r="AT11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AU11" s="109">
+      <c r="AU11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AV11" s="109">
+      <c r="AV11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AW11" s="109">
+      <c r="AW11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AX11" s="109">
+      <c r="AX11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AY11" s="109">
+      <c r="AY11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AZ11" s="109">
+      <c r="AZ11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="BA11" s="109">
+      <c r="BA11" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
@@ -21450,87 +21514,87 @@
         <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AG12" s="106">
+      <c r="AG12" s="79">
         <f t="shared" si="4"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AH12" s="109">
+      <c r="AH12" s="82">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AI12" s="109">
+      <c r="AI12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ12" s="109">
+      <c r="AJ12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AK12" s="109">
+      <c r="AK12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AL12" s="109">
+      <c r="AL12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AM12" s="109">
+      <c r="AM12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AN12" s="109">
+      <c r="AN12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AO12" s="109">
+      <c r="AO12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AP12" s="109">
+      <c r="AP12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AQ12" s="109">
+      <c r="AQ12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AR12" s="109">
+      <c r="AR12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AS12" s="109">
+      <c r="AS12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AT12" s="109">
+      <c r="AT12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AU12" s="109">
+      <c r="AU12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AV12" s="109">
+      <c r="AV12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AW12" s="109">
+      <c r="AW12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AX12" s="109">
+      <c r="AX12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AY12" s="109">
+      <c r="AY12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AZ12" s="109">
+      <c r="AZ12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="BA12" s="109">
+      <c r="BA12" s="82">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
@@ -21663,87 +21727,87 @@
         <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
-      <c r="AG13" s="106">
+      <c r="AG13" s="79">
         <f t="shared" si="4"/>
         <v>0.65</v>
       </c>
-      <c r="AH13" s="109">
+      <c r="AH13" s="82">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
-      <c r="AI13" s="109">
+      <c r="AI13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AJ13" s="109">
+      <c r="AJ13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AK13" s="109">
+      <c r="AK13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AL13" s="109">
+      <c r="AL13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AM13" s="109">
+      <c r="AM13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AN13" s="109">
+      <c r="AN13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AO13" s="109">
+      <c r="AO13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AP13" s="109">
+      <c r="AP13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AQ13" s="109">
+      <c r="AQ13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AR13" s="109">
+      <c r="AR13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AS13" s="109">
+      <c r="AS13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AT13" s="109">
+      <c r="AT13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AU13" s="109">
+      <c r="AU13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AV13" s="109">
+      <c r="AV13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AW13" s="109">
+      <c r="AW13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AX13" s="109">
+      <c r="AX13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AY13" s="109">
+      <c r="AY13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AZ13" s="109">
+      <c r="AZ13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="BA13" s="109">
+      <c r="BA13" s="82">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
@@ -21876,87 +21940,87 @@
         <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
-      <c r="AG14" s="106">
+      <c r="AG14" s="79">
         <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
-      <c r="AH14" s="109">
+      <c r="AH14" s="82">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="AI14" s="109">
+      <c r="AI14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AJ14" s="109">
+      <c r="AJ14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AK14" s="109">
+      <c r="AK14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AL14" s="109">
+      <c r="AL14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AM14" s="109">
+      <c r="AM14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AN14" s="109">
+      <c r="AN14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AO14" s="109">
+      <c r="AO14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AP14" s="109">
+      <c r="AP14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AQ14" s="109">
+      <c r="AQ14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AR14" s="109">
+      <c r="AR14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AS14" s="109">
+      <c r="AS14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AT14" s="109">
+      <c r="AT14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AU14" s="109">
+      <c r="AU14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AV14" s="109">
+      <c r="AV14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AW14" s="109">
+      <c r="AW14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AX14" s="109">
+      <c r="AX14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AY14" s="109">
+      <c r="AY14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AZ14" s="109">
+      <c r="AZ14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="BA14" s="109">
+      <c r="BA14" s="82">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -22089,87 +22153,87 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG15" s="106">
+      <c r="AG15" s="79">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AH15" s="109">
+      <c r="AH15" s="82">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI15" s="109">
+      <c r="AI15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ15" s="109">
+      <c r="AJ15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK15" s="109">
+      <c r="AK15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL15" s="109">
+      <c r="AL15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM15" s="109">
+      <c r="AM15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AN15" s="109">
+      <c r="AN15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AO15" s="109">
+      <c r="AO15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AP15" s="109">
+      <c r="AP15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AQ15" s="109">
+      <c r="AQ15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AR15" s="109">
+      <c r="AR15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AS15" s="109">
+      <c r="AS15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AT15" s="109">
+      <c r="AT15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AU15" s="109">
+      <c r="AU15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AV15" s="109">
+      <c r="AV15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AW15" s="109">
+      <c r="AW15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AX15" s="109">
+      <c r="AX15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AY15" s="109">
+      <c r="AY15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AZ15" s="109">
+      <c r="AZ15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="BA15" s="109">
+      <c r="BA15" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
@@ -22302,87 +22366,87 @@
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AG16" s="106">
+      <c r="AG16" s="79">
         <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
-      <c r="AH16" s="109">
+      <c r="AH16" s="82">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI16" s="109">
+      <c r="AI16" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ16" s="109">
+      <c r="AJ16" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK16" s="109">
+      <c r="AK16" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL16" s="109">
+      <c r="AL16" s="82">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM16" s="109">
+      <c r="AM16" s="82">
         <f t="shared" ref="AI16:BA17" si="5">AL16</f>
         <v>0.7</v>
       </c>
-      <c r="AN16" s="109">
+      <c r="AN16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AO16" s="109">
+      <c r="AO16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AP16" s="109">
+      <c r="AP16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AQ16" s="109">
+      <c r="AQ16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AR16" s="109">
+      <c r="AR16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AS16" s="109">
+      <c r="AS16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AT16" s="109">
+      <c r="AT16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AU16" s="109">
+      <c r="AU16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AV16" s="109">
+      <c r="AV16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AW16" s="109">
+      <c r="AW16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AX16" s="109">
+      <c r="AX16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AY16" s="109">
+      <c r="AY16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="AZ16" s="109">
+      <c r="AZ16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
-      <c r="BA16" s="109">
+      <c r="BA16" s="82">
         <f t="shared" si="5"/>
         <v>0.7</v>
       </c>
@@ -22515,87 +22579,87 @@
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="AG17" s="106">
+      <c r="AG17" s="79">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="AH17" s="109">
+      <c r="AH17" s="82">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="AI17" s="109">
+      <c r="AI17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AJ17" s="109">
+      <c r="AJ17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AK17" s="109">
+      <c r="AK17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AL17" s="109">
+      <c r="AL17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AM17" s="109">
+      <c r="AM17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AN17" s="109">
+      <c r="AN17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AO17" s="109">
+      <c r="AO17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AP17" s="109">
+      <c r="AP17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AQ17" s="109">
+      <c r="AQ17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AR17" s="109">
+      <c r="AR17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AS17" s="109">
+      <c r="AS17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AT17" s="109">
+      <c r="AT17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AU17" s="109">
+      <c r="AU17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AV17" s="109">
+      <c r="AV17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AW17" s="109">
+      <c r="AW17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AX17" s="109">
+      <c r="AX17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AY17" s="109">
+      <c r="AY17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="AZ17" s="109">
+      <c r="AZ17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="BA17" s="109">
+      <c r="BA17" s="82">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
@@ -23706,64 +23770,64 @@
       <c r="AG1" s="60">
         <v>2050</v>
       </c>
-      <c r="AH1" s="107">
+      <c r="AH1" s="80">
         <v>2051</v>
       </c>
-      <c r="AI1" s="108">
+      <c r="AI1" s="81">
         <v>2052</v>
       </c>
-      <c r="AJ1" s="108">
+      <c r="AJ1" s="81">
         <v>2053</v>
       </c>
-      <c r="AK1" s="108">
+      <c r="AK1" s="81">
         <v>2054</v>
       </c>
-      <c r="AL1" s="108">
+      <c r="AL1" s="81">
         <v>2055</v>
       </c>
-      <c r="AM1" s="108">
+      <c r="AM1" s="81">
         <v>2056</v>
       </c>
-      <c r="AN1" s="108">
+      <c r="AN1" s="81">
         <v>2057</v>
       </c>
-      <c r="AO1" s="108">
+      <c r="AO1" s="81">
         <v>2058</v>
       </c>
-      <c r="AP1" s="108">
+      <c r="AP1" s="81">
         <v>2059</v>
       </c>
-      <c r="AQ1" s="108">
+      <c r="AQ1" s="81">
         <v>2060</v>
       </c>
-      <c r="AR1" s="108">
+      <c r="AR1" s="81">
         <v>2061</v>
       </c>
-      <c r="AS1" s="108">
+      <c r="AS1" s="81">
         <v>2062</v>
       </c>
-      <c r="AT1" s="108">
+      <c r="AT1" s="81">
         <v>2063</v>
       </c>
-      <c r="AU1" s="108">
+      <c r="AU1" s="81">
         <v>2064</v>
       </c>
-      <c r="AV1" s="108">
+      <c r="AV1" s="81">
         <v>2065</v>
       </c>
-      <c r="AW1" s="108">
+      <c r="AW1" s="81">
         <v>2066</v>
       </c>
-      <c r="AX1" s="108">
+      <c r="AX1" s="81">
         <v>2067</v>
       </c>
-      <c r="AY1" s="108">
+      <c r="AY1" s="81">
         <v>2068</v>
       </c>
-      <c r="AZ1" s="108">
+      <c r="AZ1" s="81">
         <v>2069</v>
       </c>
-      <c r="BA1" s="108">
+      <c r="BA1" s="81">
         <v>2070</v>
       </c>
     </row>
@@ -28261,64 +28325,64 @@
       <c r="AG1" s="62">
         <v>2050</v>
       </c>
-      <c r="AH1" s="107">
+      <c r="AH1" s="80">
         <v>2051</v>
       </c>
-      <c r="AI1" s="108">
+      <c r="AI1" s="81">
         <v>2052</v>
       </c>
-      <c r="AJ1" s="108">
+      <c r="AJ1" s="81">
         <v>2053</v>
       </c>
-      <c r="AK1" s="108">
+      <c r="AK1" s="81">
         <v>2054</v>
       </c>
-      <c r="AL1" s="108">
+      <c r="AL1" s="81">
         <v>2055</v>
       </c>
-      <c r="AM1" s="108">
+      <c r="AM1" s="81">
         <v>2056</v>
       </c>
-      <c r="AN1" s="108">
+      <c r="AN1" s="81">
         <v>2057</v>
       </c>
-      <c r="AO1" s="108">
+      <c r="AO1" s="81">
         <v>2058</v>
       </c>
-      <c r="AP1" s="108">
+      <c r="AP1" s="81">
         <v>2059</v>
       </c>
-      <c r="AQ1" s="108">
+      <c r="AQ1" s="81">
         <v>2060</v>
       </c>
-      <c r="AR1" s="108">
+      <c r="AR1" s="81">
         <v>2061</v>
       </c>
-      <c r="AS1" s="108">
+      <c r="AS1" s="81">
         <v>2062</v>
       </c>
-      <c r="AT1" s="108">
+      <c r="AT1" s="81">
         <v>2063</v>
       </c>
-      <c r="AU1" s="108">
+      <c r="AU1" s="81">
         <v>2064</v>
       </c>
-      <c r="AV1" s="108">
+      <c r="AV1" s="81">
         <v>2065</v>
       </c>
-      <c r="AW1" s="108">
+      <c r="AW1" s="81">
         <v>2066</v>
       </c>
-      <c r="AX1" s="108">
+      <c r="AX1" s="81">
         <v>2067</v>
       </c>
-      <c r="AY1" s="108">
+      <c r="AY1" s="81">
         <v>2068</v>
       </c>
-      <c r="AZ1" s="108">
+      <c r="AZ1" s="81">
         <v>2069</v>
       </c>
-      <c r="BA1" s="108">
+      <c r="BA1" s="81">
         <v>2070</v>
       </c>
     </row>
@@ -28454,83 +28518,83 @@
         <f t="shared" si="0"/>
         <v>0.65</v>
       </c>
-      <c r="AH2" s="110">
+      <c r="AH2" s="83">
         <f>AG2</f>
         <v>0.65</v>
       </c>
-      <c r="AI2" s="110">
+      <c r="AI2" s="83">
         <f t="shared" ref="AI2:BA16" si="1">AH2</f>
         <v>0.65</v>
       </c>
-      <c r="AJ2" s="110">
+      <c r="AJ2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AK2" s="110">
+      <c r="AK2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AL2" s="110">
+      <c r="AL2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AM2" s="110">
+      <c r="AM2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AN2" s="110">
+      <c r="AN2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AO2" s="110">
+      <c r="AO2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AP2" s="110">
+      <c r="AP2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AQ2" s="110">
+      <c r="AQ2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AR2" s="110">
+      <c r="AR2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AS2" s="110">
+      <c r="AS2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AT2" s="110">
+      <c r="AT2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AU2" s="110">
+      <c r="AU2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AV2" s="110">
+      <c r="AV2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AW2" s="110">
+      <c r="AW2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AX2" s="110">
+      <c r="AX2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AY2" s="110">
+      <c r="AY2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AZ2" s="110">
+      <c r="AZ2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="BA2" s="110">
+      <c r="BA2" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
@@ -28667,83 +28731,83 @@
         <f t="shared" si="2"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AH3" s="110">
+      <c r="AH3" s="83">
         <f t="shared" ref="AH3:AW17" si="3">AG3</f>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AI3" s="110">
+      <c r="AI3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ3" s="110">
+      <c r="AJ3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AK3" s="110">
+      <c r="AK3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AL3" s="110">
+      <c r="AL3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AM3" s="110">
+      <c r="AM3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AN3" s="110">
+      <c r="AN3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AO3" s="110">
+      <c r="AO3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AP3" s="110">
+      <c r="AP3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AQ3" s="110">
+      <c r="AQ3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AR3" s="110">
+      <c r="AR3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AS3" s="110">
+      <c r="AS3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AT3" s="110">
+      <c r="AT3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AU3" s="110">
+      <c r="AU3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AV3" s="110">
+      <c r="AV3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AW3" s="110">
+      <c r="AW3" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AX3" s="110">
+      <c r="AX3" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AY3" s="110">
+      <c r="AY3" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AZ3" s="110">
+      <c r="AZ3" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="BA3" s="110">
+      <c r="BA3" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
@@ -28754,211 +28818,211 @@
       </c>
       <c r="B4" s="63">
         <f>'BECF-pre-ret'!B4</f>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="C4" s="63">
         <f>$B$4</f>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="63">
         <f t="shared" ref="D4:AG4" si="4">$B$4</f>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="E4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="F4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="G4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="H4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="I4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="J4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="K4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="L4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="M4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="N4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="O4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="P4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Q4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="R4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="S4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="T4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="U4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="V4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="W4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="X4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Y4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="Z4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AA4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AB4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AC4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AD4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AE4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AF4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AG4" s="63">
         <f t="shared" si="4"/>
-        <v>0.45</v>
-      </c>
-      <c r="AH4" s="110">
+        <v>0.85</v>
+      </c>
+      <c r="AH4" s="83">
         <f t="shared" si="3"/>
-        <v>0.45</v>
-      </c>
-      <c r="AI4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AJ4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AK4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AL4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AM4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AN4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AO4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AP4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AQ4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AR4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AS4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AT4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AU4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AV4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AW4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AX4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AY4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="AZ4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
-      </c>
-      <c r="BA4" s="110">
-        <f t="shared" si="1"/>
-        <v>0.45</v>
+        <v>0.85</v>
+      </c>
+      <c r="AI4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AJ4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AK4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AL4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AM4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AN4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AO4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AP4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AQ4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AR4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AS4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AT4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AU4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AV4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AW4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AX4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AY4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="AZ4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
+      </c>
+      <c r="BA4" s="83">
+        <f t="shared" si="1"/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" spans="1:53" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29093,83 +29157,83 @@
         <f t="shared" si="5"/>
         <v>0.37</v>
       </c>
-      <c r="AH5" s="110">
+      <c r="AH5" s="83">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="AI5" s="110">
+      <c r="AI5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AJ5" s="110">
+      <c r="AJ5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AK5" s="110">
+      <c r="AK5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AL5" s="110">
+      <c r="AL5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AM5" s="110">
+      <c r="AM5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AN5" s="110">
+      <c r="AN5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AO5" s="110">
+      <c r="AO5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AP5" s="110">
+      <c r="AP5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AQ5" s="110">
+      <c r="AQ5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AR5" s="110">
+      <c r="AR5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AS5" s="110">
+      <c r="AS5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AT5" s="110">
+      <c r="AT5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AU5" s="110">
+      <c r="AU5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AV5" s="110">
+      <c r="AV5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AW5" s="110">
+      <c r="AW5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AX5" s="110">
+      <c r="AX5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AY5" s="110">
+      <c r="AY5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AZ5" s="110">
+      <c r="AZ5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="BA5" s="110">
+      <c r="BA5" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -29306,83 +29370,83 @@
         <f t="shared" si="8"/>
         <v>0.35</v>
       </c>
-      <c r="AH6" s="110">
+      <c r="AH6" s="83">
         <f t="shared" si="3"/>
         <v>0.35</v>
       </c>
-      <c r="AI6" s="110">
+      <c r="AI6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AJ6" s="110">
+      <c r="AJ6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AK6" s="110">
+      <c r="AK6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AL6" s="110">
+      <c r="AL6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AM6" s="110">
+      <c r="AM6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AN6" s="110">
+      <c r="AN6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AO6" s="110">
+      <c r="AO6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AP6" s="110">
+      <c r="AP6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AQ6" s="110">
+      <c r="AQ6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AR6" s="110">
+      <c r="AR6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AS6" s="110">
+      <c r="AS6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AT6" s="110">
+      <c r="AT6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AU6" s="110">
+      <c r="AU6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AV6" s="110">
+      <c r="AV6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AW6" s="110">
+      <c r="AW6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AX6" s="110">
+      <c r="AX6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AY6" s="110">
+      <c r="AY6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="AZ6" s="110">
+      <c r="AZ6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
-      <c r="BA6" s="110">
+      <c r="BA6" s="83">
         <f t="shared" si="1"/>
         <v>0.35</v>
       </c>
@@ -29519,83 +29583,83 @@
         <f t="shared" si="9"/>
         <v>0.18</v>
       </c>
-      <c r="AH7" s="110">
+      <c r="AH7" s="83">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="AI7" s="110">
+      <c r="AI7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AJ7" s="110">
+      <c r="AJ7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AK7" s="110">
+      <c r="AK7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AL7" s="110">
+      <c r="AL7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AM7" s="110">
+      <c r="AM7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AN7" s="110">
+      <c r="AN7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AO7" s="110">
+      <c r="AO7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AP7" s="110">
+      <c r="AP7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AQ7" s="110">
+      <c r="AQ7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AR7" s="110">
+      <c r="AR7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AS7" s="110">
+      <c r="AS7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AT7" s="110">
+      <c r="AT7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AU7" s="110">
+      <c r="AU7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AV7" s="110">
+      <c r="AV7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AW7" s="110">
+      <c r="AW7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AX7" s="110">
+      <c r="AX7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AY7" s="110">
+      <c r="AY7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AZ7" s="110">
+      <c r="AZ7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="BA7" s="110">
+      <c r="BA7" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
@@ -29732,83 +29796,83 @@
         <f t="shared" si="10"/>
         <v>0.18</v>
       </c>
-      <c r="AH8" s="110">
+      <c r="AH8" s="83">
         <f t="shared" si="3"/>
         <v>0.18</v>
       </c>
-      <c r="AI8" s="110">
+      <c r="AI8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AJ8" s="110">
+      <c r="AJ8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AK8" s="110">
+      <c r="AK8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AL8" s="110">
+      <c r="AL8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AM8" s="110">
+      <c r="AM8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AN8" s="110">
+      <c r="AN8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AO8" s="110">
+      <c r="AO8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AP8" s="110">
+      <c r="AP8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AQ8" s="110">
+      <c r="AQ8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AR8" s="110">
+      <c r="AR8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AS8" s="110">
+      <c r="AS8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AT8" s="110">
+      <c r="AT8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AU8" s="110">
+      <c r="AU8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AV8" s="110">
+      <c r="AV8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AW8" s="110">
+      <c r="AW8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AX8" s="110">
+      <c r="AX8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AY8" s="110">
+      <c r="AY8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="AZ8" s="110">
+      <c r="AZ8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
-      <c r="BA8" s="110">
+      <c r="BA8" s="83">
         <f t="shared" si="1"/>
         <v>0.18</v>
       </c>
@@ -29945,83 +30009,83 @@
         <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
-      <c r="AH9" s="110">
+      <c r="AH9" s="83">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="AI9" s="110">
+      <c r="AI9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AJ9" s="110">
+      <c r="AJ9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AK9" s="110">
+      <c r="AK9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AL9" s="110">
+      <c r="AL9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AM9" s="110">
+      <c r="AM9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AN9" s="110">
+      <c r="AN9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AO9" s="110">
+      <c r="AO9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AP9" s="110">
+      <c r="AP9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AQ9" s="110">
+      <c r="AQ9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AR9" s="110">
+      <c r="AR9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AS9" s="110">
+      <c r="AS9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AT9" s="110">
+      <c r="AT9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AU9" s="110">
+      <c r="AU9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AV9" s="110">
+      <c r="AV9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AW9" s="110">
+      <c r="AW9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AX9" s="110">
+      <c r="AX9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AY9" s="110">
+      <c r="AY9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="AZ9" s="110">
+      <c r="AZ9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="BA9" s="110">
+      <c r="BA9" s="83">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
@@ -30158,83 +30222,83 @@
         <f t="shared" si="12"/>
         <v>0.82</v>
       </c>
-      <c r="AH10" s="110">
+      <c r="AH10" s="83">
         <f t="shared" si="3"/>
         <v>0.82</v>
       </c>
-      <c r="AI10" s="110">
+      <c r="AI10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AJ10" s="110">
+      <c r="AJ10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AK10" s="110">
+      <c r="AK10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AL10" s="110">
+      <c r="AL10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AM10" s="110">
+      <c r="AM10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AN10" s="110">
+      <c r="AN10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AO10" s="110">
+      <c r="AO10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AP10" s="110">
+      <c r="AP10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AQ10" s="110">
+      <c r="AQ10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AR10" s="110">
+      <c r="AR10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AS10" s="110">
+      <c r="AS10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AT10" s="110">
+      <c r="AT10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AU10" s="110">
+      <c r="AU10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AV10" s="110">
+      <c r="AV10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AW10" s="110">
+      <c r="AW10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AX10" s="110">
+      <c r="AX10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AY10" s="110">
+      <c r="AY10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="AZ10" s="110">
+      <c r="AZ10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
-      <c r="BA10" s="110">
+      <c r="BA10" s="83">
         <f t="shared" si="1"/>
         <v>0.82</v>
       </c>
@@ -30371,83 +30435,83 @@
         <f t="shared" si="13"/>
         <v>0.7</v>
       </c>
-      <c r="AH11" s="110">
+      <c r="AH11" s="83">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI11" s="110">
+      <c r="AI11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ11" s="110">
+      <c r="AJ11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK11" s="110">
+      <c r="AK11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL11" s="110">
+      <c r="AL11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM11" s="110">
+      <c r="AM11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AN11" s="110">
+      <c r="AN11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AO11" s="110">
+      <c r="AO11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AP11" s="110">
+      <c r="AP11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AQ11" s="110">
+      <c r="AQ11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AR11" s="110">
+      <c r="AR11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AS11" s="110">
+      <c r="AS11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AT11" s="110">
+      <c r="AT11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AU11" s="110">
+      <c r="AU11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AV11" s="110">
+      <c r="AV11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AW11" s="110">
+      <c r="AW11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AX11" s="110">
+      <c r="AX11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AY11" s="110">
+      <c r="AY11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AZ11" s="110">
+      <c r="AZ11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="BA11" s="110">
+      <c r="BA11" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
@@ -30584,83 +30648,83 @@
         <f t="shared" si="14"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AH12" s="110">
+      <c r="AH12" s="83">
         <f t="shared" si="3"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AI12" s="110">
+      <c r="AI12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ12" s="110">
+      <c r="AJ12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AK12" s="110">
+      <c r="AK12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AL12" s="110">
+      <c r="AL12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AM12" s="110">
+      <c r="AM12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AN12" s="110">
+      <c r="AN12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AO12" s="110">
+      <c r="AO12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AP12" s="110">
+      <c r="AP12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AQ12" s="110">
+      <c r="AQ12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AR12" s="110">
+      <c r="AR12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AS12" s="110">
+      <c r="AS12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AT12" s="110">
+      <c r="AT12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AU12" s="110">
+      <c r="AU12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AV12" s="110">
+      <c r="AV12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AW12" s="110">
+      <c r="AW12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AX12" s="110">
+      <c r="AX12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AY12" s="110">
+      <c r="AY12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="AZ12" s="110">
+      <c r="AZ12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
-      <c r="BA12" s="110">
+      <c r="BA12" s="83">
         <f t="shared" si="1"/>
         <v>0.28999999999999998</v>
       </c>
@@ -30797,83 +30861,83 @@
         <f t="shared" si="15"/>
         <v>0.65</v>
       </c>
-      <c r="AH13" s="110">
+      <c r="AH13" s="83">
         <f t="shared" si="3"/>
         <v>0.65</v>
       </c>
-      <c r="AI13" s="110">
+      <c r="AI13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AJ13" s="110">
+      <c r="AJ13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AK13" s="110">
+      <c r="AK13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AL13" s="110">
+      <c r="AL13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AM13" s="110">
+      <c r="AM13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AN13" s="110">
+      <c r="AN13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AO13" s="110">
+      <c r="AO13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AP13" s="110">
+      <c r="AP13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AQ13" s="110">
+      <c r="AQ13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AR13" s="110">
+      <c r="AR13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AS13" s="110">
+      <c r="AS13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AT13" s="110">
+      <c r="AT13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AU13" s="110">
+      <c r="AU13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AV13" s="110">
+      <c r="AV13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AW13" s="110">
+      <c r="AW13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AX13" s="110">
+      <c r="AX13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AY13" s="110">
+      <c r="AY13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="AZ13" s="110">
+      <c r="AZ13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
-      <c r="BA13" s="110">
+      <c r="BA13" s="83">
         <f t="shared" si="1"/>
         <v>0.65</v>
       </c>
@@ -31010,83 +31074,83 @@
         <f t="shared" si="16"/>
         <v>0.37</v>
       </c>
-      <c r="AH14" s="110">
+      <c r="AH14" s="83">
         <f t="shared" si="3"/>
         <v>0.37</v>
       </c>
-      <c r="AI14" s="110">
+      <c r="AI14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AJ14" s="110">
+      <c r="AJ14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AK14" s="110">
+      <c r="AK14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AL14" s="110">
+      <c r="AL14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AM14" s="110">
+      <c r="AM14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AN14" s="110">
+      <c r="AN14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AO14" s="110">
+      <c r="AO14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AP14" s="110">
+      <c r="AP14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AQ14" s="110">
+      <c r="AQ14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AR14" s="110">
+      <c r="AR14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AS14" s="110">
+      <c r="AS14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AT14" s="110">
+      <c r="AT14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AU14" s="110">
+      <c r="AU14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AV14" s="110">
+      <c r="AV14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AW14" s="110">
+      <c r="AW14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AX14" s="110">
+      <c r="AX14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AY14" s="110">
+      <c r="AY14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="AZ14" s="110">
+      <c r="AZ14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
-      <c r="BA14" s="110">
+      <c r="BA14" s="83">
         <f t="shared" si="1"/>
         <v>0.37</v>
       </c>
@@ -31223,83 +31287,83 @@
         <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="AH15" s="110">
+      <c r="AH15" s="83">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI15" s="110">
+      <c r="AI15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ15" s="110">
+      <c r="AJ15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK15" s="110">
+      <c r="AK15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL15" s="110">
+      <c r="AL15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM15" s="110">
+      <c r="AM15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AN15" s="110">
+      <c r="AN15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AO15" s="110">
+      <c r="AO15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AP15" s="110">
+      <c r="AP15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AQ15" s="110">
+      <c r="AQ15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AR15" s="110">
+      <c r="AR15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AS15" s="110">
+      <c r="AS15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AT15" s="110">
+      <c r="AT15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AU15" s="110">
+      <c r="AU15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AV15" s="110">
+      <c r="AV15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AW15" s="110">
+      <c r="AW15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AX15" s="110">
+      <c r="AX15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AY15" s="110">
+      <c r="AY15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AZ15" s="110">
+      <c r="AZ15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="BA15" s="110">
+      <c r="BA15" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
@@ -31436,83 +31500,83 @@
         <f t="shared" si="18"/>
         <v>0.7</v>
       </c>
-      <c r="AH16" s="110">
+      <c r="AH16" s="83">
         <f t="shared" si="3"/>
         <v>0.7</v>
       </c>
-      <c r="AI16" s="110">
+      <c r="AI16" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AJ16" s="110">
+      <c r="AJ16" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AK16" s="110">
+      <c r="AK16" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AL16" s="110">
+      <c r="AL16" s="83">
         <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
-      <c r="AM16" s="110">
+      <c r="AM16" s="83">
         <f t="shared" ref="AI16:BA17" si="19">AL16</f>
         <v>0.7</v>
       </c>
-      <c r="AN16" s="110">
+      <c r="AN16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AO16" s="110">
+      <c r="AO16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AP16" s="110">
+      <c r="AP16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AQ16" s="110">
+      <c r="AQ16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AR16" s="110">
+      <c r="AR16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AS16" s="110">
+      <c r="AS16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AT16" s="110">
+      <c r="AT16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AU16" s="110">
+      <c r="AU16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AV16" s="110">
+      <c r="AV16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AW16" s="110">
+      <c r="AW16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AX16" s="110">
+      <c r="AX16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AY16" s="110">
+      <c r="AY16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="AZ16" s="110">
+      <c r="AZ16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
-      <c r="BA16" s="110">
+      <c r="BA16" s="83">
         <f t="shared" si="19"/>
         <v>0.7</v>
       </c>
@@ -31649,83 +31713,83 @@
         <f t="shared" si="20"/>
         <v>0.5</v>
       </c>
-      <c r="AH17" s="110">
+      <c r="AH17" s="83">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="AI17" s="110">
+      <c r="AI17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AJ17" s="110">
+      <c r="AJ17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AK17" s="110">
+      <c r="AK17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AL17" s="110">
+      <c r="AL17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AM17" s="110">
+      <c r="AM17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AN17" s="110">
+      <c r="AN17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AO17" s="110">
+      <c r="AO17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AP17" s="110">
+      <c r="AP17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AQ17" s="110">
+      <c r="AQ17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AR17" s="110">
+      <c r="AR17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AS17" s="110">
+      <c r="AS17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AT17" s="110">
+      <c r="AT17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AU17" s="110">
+      <c r="AU17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AV17" s="110">
+      <c r="AV17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AW17" s="110">
+      <c r="AW17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AX17" s="110">
+      <c r="AX17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AY17" s="110">
+      <c r="AY17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="AZ17" s="110">
+      <c r="AZ17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>
-      <c r="BA17" s="110">
+      <c r="BA17" s="83">
         <f t="shared" si="19"/>
         <v>0.5</v>
       </c>

--- a/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
+++ b/InputData/elec/BECF/BAU Expected Capacity Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-indonesia-cpl/InputData/elec/BECF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85CFDB6A-613F-F74A-AF36-251C24C31E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8940C2D2-088D-7842-BAAF-765B015382C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="177">
   <si>
     <t>BAU Expected Capacity Factors</t>
   </si>
@@ -622,6 +622,9 @@
   </si>
   <si>
     <t> In 2021, the global median capacity factor was 85.6%, in line with recent years. Pressurized water reactors (PWR) and pressurized heavy water moderated, and cooled reactors (PHWR) have been the best performing reactors since 2011, with median capacity factors of 82% and 81%, respectively.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preexisting coal power </t>
   </si>
 </sst>
 </file>
@@ -1220,6 +1223,15 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1230,23 +1242,29 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1263,30 +1281,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1622,16 +1625,16 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
-      <c r="E3" s="85"/>
-      <c r="F3" s="85"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="85"/>
-      <c r="I3" s="86"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="89"/>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -1871,7 +1874,7 @@
     </row>
     <row r="46" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
-      <c r="B46" s="110">
+      <c r="B46" s="84">
         <v>2021</v>
       </c>
     </row>
@@ -1906,141 +1909,141 @@
       <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="87" t="s">
+      <c r="B53" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="88"/>
-      <c r="D53" s="88"/>
-      <c r="E53" s="88"/>
-      <c r="F53" s="88"/>
-      <c r="G53" s="88"/>
-      <c r="H53" s="88"/>
-      <c r="I53" s="88"/>
+      <c r="C53" s="91"/>
+      <c r="D53" s="91"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
     </row>
     <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="88"/>
-      <c r="C54" s="88"/>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
+      <c r="B54" s="91"/>
+      <c r="C54" s="91"/>
+      <c r="D54" s="91"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="91"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="91"/>
+      <c r="I54" s="91"/>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B55" s="88"/>
-      <c r="C55" s="88"/>
-      <c r="D55" s="88"/>
-      <c r="E55" s="88"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88"/>
-      <c r="H55" s="88"/>
-      <c r="I55" s="88"/>
+      <c r="B55" s="91"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="91"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="91"/>
+      <c r="H55" s="91"/>
+      <c r="I55" s="91"/>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B56" s="88"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="88"/>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="88"/>
-      <c r="I56" s="88"/>
+      <c r="B56" s="91"/>
+      <c r="C56" s="91"/>
+      <c r="D56" s="91"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="91"/>
+      <c r="H56" s="91"/>
+      <c r="I56" s="91"/>
     </row>
     <row r="57" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B57" s="88"/>
-      <c r="C57" s="88"/>
-      <c r="D57" s="88"/>
-      <c r="E57" s="88"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="88"/>
-      <c r="H57" s="88"/>
-      <c r="I57" s="88"/>
+      <c r="B57" s="91"/>
+      <c r="C57" s="91"/>
+      <c r="D57" s="91"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="91"/>
+      <c r="H57" s="91"/>
+      <c r="I57" s="91"/>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B58" s="88"/>
-      <c r="C58" s="88"/>
-      <c r="D58" s="88"/>
-      <c r="E58" s="88"/>
-      <c r="F58" s="88"/>
-      <c r="G58" s="88"/>
-      <c r="H58" s="88"/>
-      <c r="I58" s="88"/>
+      <c r="B58" s="91"/>
+      <c r="C58" s="91"/>
+      <c r="D58" s="91"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="91"/>
+      <c r="H58" s="91"/>
+      <c r="I58" s="91"/>
     </row>
     <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B59" s="88"/>
-      <c r="C59" s="88"/>
-      <c r="D59" s="88"/>
-      <c r="E59" s="88"/>
-      <c r="F59" s="88"/>
-      <c r="G59" s="88"/>
-      <c r="H59" s="88"/>
-      <c r="I59" s="88"/>
+      <c r="B59" s="91"/>
+      <c r="C59" s="91"/>
+      <c r="D59" s="91"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="91"/>
+      <c r="H59" s="91"/>
+      <c r="I59" s="91"/>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="88"/>
-      <c r="C60" s="88"/>
-      <c r="D60" s="88"/>
-      <c r="E60" s="88"/>
-      <c r="F60" s="88"/>
-      <c r="G60" s="88"/>
-      <c r="H60" s="88"/>
-      <c r="I60" s="88"/>
+      <c r="B60" s="91"/>
+      <c r="C60" s="91"/>
+      <c r="D60" s="91"/>
+      <c r="E60" s="91"/>
+      <c r="F60" s="91"/>
+      <c r="G60" s="91"/>
+      <c r="H60" s="91"/>
+      <c r="I60" s="91"/>
     </row>
     <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="88"/>
-      <c r="C61" s="88"/>
-      <c r="D61" s="88"/>
-      <c r="E61" s="88"/>
-      <c r="F61" s="88"/>
-      <c r="G61" s="88"/>
-      <c r="H61" s="88"/>
-      <c r="I61" s="88"/>
+      <c r="B61" s="91"/>
+      <c r="C61" s="91"/>
+      <c r="D61" s="91"/>
+      <c r="E61" s="91"/>
+      <c r="F61" s="91"/>
+      <c r="G61" s="91"/>
+      <c r="H61" s="91"/>
+      <c r="I61" s="91"/>
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="88"/>
-      <c r="C62" s="88"/>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
-      <c r="H62" s="88"/>
-      <c r="I62" s="88"/>
+      <c r="B62" s="91"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="91"/>
+      <c r="E62" s="91"/>
+      <c r="F62" s="91"/>
+      <c r="G62" s="91"/>
+      <c r="H62" s="91"/>
+      <c r="I62" s="91"/>
     </row>
     <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="88"/>
-      <c r="C63" s="88"/>
-      <c r="D63" s="88"/>
-      <c r="E63" s="88"/>
-      <c r="F63" s="88"/>
-      <c r="G63" s="88"/>
-      <c r="H63" s="88"/>
-      <c r="I63" s="88"/>
+      <c r="B63" s="91"/>
+      <c r="C63" s="91"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B64" s="88"/>
-      <c r="C64" s="88"/>
-      <c r="D64" s="88"/>
-      <c r="E64" s="88"/>
-      <c r="F64" s="88"/>
-      <c r="G64" s="88"/>
-      <c r="H64" s="88"/>
-      <c r="I64" s="88"/>
+      <c r="B64" s="91"/>
+      <c r="C64" s="91"/>
+      <c r="D64" s="91"/>
+      <c r="E64" s="91"/>
+      <c r="F64" s="91"/>
+      <c r="G64" s="91"/>
+      <c r="H64" s="91"/>
+      <c r="I64" s="91"/>
     </row>
     <row r="65" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B65" s="88"/>
-      <c r="C65" s="88"/>
-      <c r="D65" s="88"/>
-      <c r="E65" s="88"/>
-      <c r="F65" s="88"/>
-      <c r="G65" s="88"/>
-      <c r="H65" s="88"/>
-      <c r="I65" s="88"/>
+      <c r="B65" s="91"/>
+      <c r="C65" s="91"/>
+      <c r="D65" s="91"/>
+      <c r="E65" s="91"/>
+      <c r="F65" s="91"/>
+      <c r="G65" s="91"/>
+      <c r="H65" s="91"/>
+      <c r="I65" s="91"/>
     </row>
     <row r="66" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="68" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B68" s="111" t="s">
+      <c r="B68" s="85" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3051,11 +3054,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
       <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3066,14 +3069,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:30" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="102" t="s">
+      <c r="B3" s="93"/>
+      <c r="C3" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="90"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -3144,14 +3147,14 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="104" t="s">
+      <c r="B4" s="99"/>
+      <c r="C4" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="90"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="12" t="s">
         <v>25</v>
       </c>
@@ -3233,12 +3236,12 @@
       </c>
     </row>
     <row r="5" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="93"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="104" t="s">
+      <c r="A5" s="102"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="90"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="12">
         <v>3</v>
       </c>
@@ -3317,14 +3320,14 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="90"/>
-      <c r="C6" s="104" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="90"/>
+      <c r="D6" s="93"/>
       <c r="E6" s="12" t="s">
         <v>28</v>
       </c>
@@ -3403,14 +3406,14 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="91" t="s">
+      <c r="A7" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="104" t="s">
+      <c r="B7" s="99"/>
+      <c r="C7" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="93"/>
       <c r="E7" s="12" t="s">
         <v>28</v>
       </c>
@@ -3489,12 +3492,12 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="93"/>
-      <c r="B8" s="94"/>
-      <c r="C8" s="104" t="s">
+      <c r="A8" s="102"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="92" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="90"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -3573,14 +3576,14 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="95" t="s">
+      <c r="A9" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="92"/>
-      <c r="C9" s="104" t="s">
+      <c r="B9" s="99"/>
+      <c r="C9" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="90"/>
+      <c r="D9" s="93"/>
       <c r="E9" s="12" t="s">
         <v>32</v>
       </c>
@@ -3659,12 +3662,12 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="96"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="104" t="s">
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="90"/>
+      <c r="D10" s="93"/>
       <c r="E10" s="12" t="s">
         <v>28</v>
       </c>
@@ -3743,12 +3746,12 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="96"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="104" t="s">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="90"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="12" t="s">
         <v>28</v>
       </c>
@@ -3827,12 +3830,12 @@
       </c>
     </row>
     <row r="12" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="93"/>
-      <c r="B12" s="94"/>
-      <c r="C12" s="104" t="s">
+      <c r="A12" s="102"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="12" t="s">
         <v>28</v>
       </c>
@@ -3877,14 +3880,14 @@
       </c>
     </row>
     <row r="13" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="95" t="s">
+      <c r="A13" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="92"/>
-      <c r="C13" s="104" t="s">
+      <c r="B13" s="99"/>
+      <c r="C13" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="90"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="12" t="s">
         <v>37</v>
       </c>
@@ -3962,12 +3965,12 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="104" t="s">
+      <c r="A14" s="102"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="90"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="12">
         <v>3</v>
       </c>
@@ -4206,14 +4209,14 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="104" t="s">
+      <c r="B17" s="99"/>
+      <c r="C17" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="90"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
@@ -4253,12 +4256,12 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="104" t="s">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="90"/>
+      <c r="D18" s="93"/>
       <c r="E18" s="12">
         <v>1</v>
       </c>
@@ -4304,11 +4307,11 @@
       <c r="A19" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="104" t="s">
+      <c r="B19" s="99"/>
+      <c r="C19" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="90"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="12" t="s">
         <v>37</v>
       </c>
@@ -4361,12 +4364,12 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="96"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="104" t="s">
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="90"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="12" t="s">
         <v>37</v>
       </c>
@@ -4425,12 +4428,12 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="93"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="104" t="s">
+      <c r="A21" s="102"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="90"/>
+      <c r="D21" s="93"/>
       <c r="E21" s="12">
         <v>2</v>
       </c>
@@ -4489,14 +4492,14 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="99" t="s">
+      <c r="A22" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="104" t="s">
+      <c r="B22" s="93"/>
+      <c r="C22" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="90"/>
+      <c r="D22" s="93"/>
       <c r="E22" s="12">
         <v>2</v>
       </c>
@@ -4524,11 +4527,11 @@
       <c r="A23" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="104" t="s">
+      <c r="B23" s="99"/>
+      <c r="C23" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="90"/>
+      <c r="D23" s="93"/>
       <c r="E23" s="12" t="s">
         <v>28</v>
       </c>
@@ -4553,12 +4556,12 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="96"/>
-      <c r="B24" s="97"/>
-      <c r="C24" s="105" t="s">
+      <c r="A24" s="100"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="90"/>
+      <c r="D24" s="93"/>
       <c r="E24" s="12">
         <v>3</v>
       </c>
@@ -4616,12 +4619,12 @@
       </c>
     </row>
     <row r="25" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="96"/>
-      <c r="B25" s="97"/>
-      <c r="C25" s="105" t="s">
+      <c r="A25" s="100"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="90"/>
+      <c r="D25" s="93"/>
       <c r="E25" s="12">
         <v>3</v>
       </c>
@@ -4649,12 +4652,12 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="96"/>
-      <c r="B26" s="97"/>
-      <c r="C26" s="105" t="s">
+      <c r="A26" s="100"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="97" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="90"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="12">
         <v>3</v>
       </c>
@@ -4682,12 +4685,12 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="93"/>
-      <c r="B27" s="94"/>
-      <c r="C27" s="104" t="s">
+      <c r="A27" s="102"/>
+      <c r="B27" s="103"/>
+      <c r="C27" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="90"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="12">
         <v>3</v>
       </c>
@@ -4858,12 +4861,12 @@
       </c>
     </row>
     <row r="35" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F35" s="106" t="s">
+      <c r="F35" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="G35" s="88"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="88"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27" t="s">
@@ -5563,12 +5566,12 @@
       <c r="D52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="107" t="s">
+      <c r="A53" s="95" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
+      <c r="B53" s="88"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="89"/>
       <c r="E53" s="26" t="s">
         <v>10</v>
       </c>
@@ -5578,11 +5581,11 @@
       <c r="B54" s="37"/>
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
-      <c r="F54" s="106" t="s">
+      <c r="F54" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="91"/>
     </row>
     <row r="55" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27" t="s">
@@ -6370,12 +6373,12 @@
     </row>
     <row r="69" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="108" t="s">
+      <c r="A70" s="96" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="85"/>
-      <c r="C70" s="85"/>
-      <c r="D70" s="86"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="88"/>
+      <c r="D70" s="89"/>
       <c r="E70" s="26" t="s">
         <v>10</v>
       </c>
@@ -7846,23 +7849,11 @@
     <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F35:I35"/>
-    <mergeCell ref="F54:H54"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B8"/>
+    <mergeCell ref="A9:B12"/>
+    <mergeCell ref="A13:B14"/>
+    <mergeCell ref="A17:B18"/>
     <mergeCell ref="A19:B21"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B27"/>
@@ -7879,11 +7870,23 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B8"/>
-    <mergeCell ref="A9:B12"/>
-    <mergeCell ref="A13:B14"/>
-    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F35:I35"/>
+    <mergeCell ref="F54:H54"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A70:D70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -7905,11 +7908,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="86"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="89"/>
       <c r="D1" s="1" t="s">
         <v>78</v>
       </c>
@@ -7920,14 +7923,14 @@
       <c r="C2" s="5"/>
     </row>
     <row r="3" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="101" t="s">
+      <c r="A3" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="102" t="s">
+      <c r="B3" s="93"/>
+      <c r="C3" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="90"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
@@ -7963,14 +7966,14 @@
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="103" t="s">
+      <c r="A4" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="92"/>
-      <c r="C4" s="99" t="s">
+      <c r="B4" s="99"/>
+      <c r="C4" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="90"/>
+      <c r="D4" s="93"/>
       <c r="E4" s="12" t="s">
         <v>28</v>
       </c>
@@ -8015,12 +8018,12 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="96"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="104" t="s">
+      <c r="A5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="90"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="12" t="s">
         <v>28</v>
       </c>
@@ -8065,12 +8068,12 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="93"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="104" t="s">
+      <c r="A6" s="102"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="D6" s="90"/>
+      <c r="D6" s="93"/>
       <c r="E6" s="12">
         <v>1</v>
       </c>
@@ -8115,14 +8118,14 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="109" t="s">
+      <c r="B7" s="93"/>
+      <c r="C7" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="90"/>
+      <c r="D7" s="93"/>
       <c r="E7" s="12">
         <v>1</v>
       </c>
@@ -8167,14 +8170,14 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="91" t="s">
+      <c r="A8" s="110" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="92"/>
-      <c r="C8" s="109" t="s">
+      <c r="B8" s="99"/>
+      <c r="C8" s="112" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="90"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="12">
         <v>1</v>
       </c>
@@ -8219,12 +8222,12 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="96"/>
-      <c r="B9" s="97"/>
-      <c r="C9" s="109" t="s">
+      <c r="A9" s="100"/>
+      <c r="B9" s="101"/>
+      <c r="C9" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="90"/>
+      <c r="D9" s="93"/>
       <c r="E9" s="12">
         <v>1</v>
       </c>
@@ -8269,12 +8272,12 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="93"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="104" t="s">
+      <c r="A10" s="102"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="90"/>
+      <c r="D10" s="93"/>
       <c r="E10" s="12">
         <v>1</v>
       </c>
@@ -8330,14 +8333,14 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="111" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="109" t="s">
+      <c r="B11" s="99"/>
+      <c r="C11" s="112" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="90"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="12">
         <v>1</v>
       </c>
@@ -8382,12 +8385,12 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="96"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="109" t="s">
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="93"/>
       <c r="E12" s="12">
         <v>1</v>
       </c>
@@ -8432,12 +8435,12 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="96"/>
-      <c r="B13" s="97"/>
-      <c r="C13" s="109" t="s">
+      <c r="A13" s="100"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="90"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="12">
         <v>1</v>
       </c>
@@ -8482,12 +8485,12 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="93"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="109" t="s">
+      <c r="A14" s="102"/>
+      <c r="B14" s="103"/>
+      <c r="C14" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="90"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="12">
         <v>1</v>
       </c>
@@ -8624,25 +8627,25 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="95" t="s">
+      <c r="A17" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="109" t="s">
+      <c r="B17" s="99"/>
+      <c r="C17" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="90"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="93"/>
-      <c r="B18" s="94"/>
-      <c r="C18" s="109" t="s">
+      <c r="A18" s="102"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="90"/>
+      <c r="D18" s="93"/>
       <c r="E18" s="12">
         <v>2</v>
       </c>
@@ -8651,14 +8654,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="109" t="s">
+      <c r="B19" s="99"/>
+      <c r="C19" s="112" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="90"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="12">
         <v>1</v>
       </c>
@@ -8676,12 +8679,12 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="93"/>
-      <c r="B20" s="94"/>
-      <c r="C20" s="104" t="s">
+      <c r="A20" s="102"/>
+      <c r="B20" s="103"/>
+      <c r="C20" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="D20" s="90"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="12">
         <v>1</v>
       </c>
@@ -8705,11 +8708,11 @@
       <c r="A21" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="104" t="s">
+      <c r="B21" s="99"/>
+      <c r="C21" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="90"/>
+      <c r="D21" s="93"/>
       <c r="E21" s="12" t="s">
         <v>28</v>
       </c>
@@ -8730,8 +8733,8 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93"/>
-      <c r="B22" s="94"/>
+      <c r="A22" s="102"/>
+      <c r="B22" s="103"/>
       <c r="C22" s="21" t="s">
         <v>42</v>
       </c>
@@ -8756,14 +8759,14 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="99" t="s">
+      <c r="A23" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="104" t="s">
+      <c r="B23" s="93"/>
+      <c r="C23" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="90"/>
+      <c r="D23" s="93"/>
       <c r="E23" s="12">
         <v>1</v>
       </c>
@@ -8787,11 +8790,11 @@
       <c r="A24" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="104" t="s">
+      <c r="B24" s="99"/>
+      <c r="C24" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="90"/>
+      <c r="D24" s="93"/>
       <c r="E24" s="12">
         <v>1</v>
       </c>
@@ -8812,12 +8815,12 @@
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="96"/>
-      <c r="B25" s="97"/>
-      <c r="C25" s="109" t="s">
+      <c r="A25" s="100"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="90"/>
+      <c r="D25" s="93"/>
       <c r="E25" s="12">
         <v>2</v>
       </c>
@@ -8838,12 +8841,12 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="96"/>
-      <c r="B26" s="97"/>
-      <c r="C26" s="105" t="s">
+      <c r="A26" s="100"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="90"/>
+      <c r="D26" s="93"/>
       <c r="E26" s="12">
         <v>2</v>
       </c>
@@ -8864,12 +8867,12 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="96"/>
-      <c r="B27" s="97"/>
-      <c r="C27" s="105" t="s">
+      <c r="A27" s="100"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="97" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="90"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="12">
         <v>2</v>
       </c>
@@ -8890,12 +8893,12 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="93"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="104" t="s">
+      <c r="A28" s="102"/>
+      <c r="B28" s="103"/>
+      <c r="C28" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="90"/>
+      <c r="D28" s="93"/>
       <c r="E28" s="12">
         <v>2</v>
       </c>
@@ -10940,22 +10943,13 @@
     <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A24:B28"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
@@ -10967,13 +10961,22 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A11:B14"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A24:B28"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -18929,23 +18932,29 @@
     <col min="14" max="14" width="134.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="65" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="65" t="s">
         <v>151</v>
       </c>
+      <c r="C1" s="65" t="s">
+        <v>176</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="55" t="s">
         <v>126</v>
       </c>
       <c r="B2">
         <v>0.65</v>
       </c>
+      <c r="C2">
+        <v>0.49</v>
+      </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="54" t="s">
         <v>127</v>
       </c>
@@ -18953,7 +18962,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>128</v>
       </c>
@@ -18962,7 +18971,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="54" t="s">
         <v>15</v>
       </c>
@@ -18970,7 +18979,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="54" t="s">
         <v>129</v>
       </c>
@@ -18978,7 +18987,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="54" t="s">
         <v>23</v>
       </c>
@@ -18986,7 +18995,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="54" t="s">
         <v>130</v>
       </c>
@@ -18995,7 +19004,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="54" t="s">
         <v>21</v>
       </c>
@@ -19003,7 +19012,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="54" t="s">
         <v>16</v>
       </c>
@@ -19011,7 +19020,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="54" t="s">
         <v>131</v>
       </c>
@@ -19019,7 +19028,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="54" t="s">
         <v>132</v>
       </c>
@@ -19027,7 +19036,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="54" t="s">
         <v>65</v>
       </c>
@@ -19035,7 +19044,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="54" t="s">
         <v>133</v>
       </c>
@@ -19043,7 +19052,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="54" t="s">
         <v>134</v>
       </c>
@@ -19051,7 +19060,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="54" t="s">
         <v>135</v>
       </c>
@@ -19068,7 +19077,7 @@
       </c>
     </row>
     <row r="34" spans="14:14" ht="51" x14ac:dyDescent="0.2">
-      <c r="N34" s="112" t="s">
+      <c r="N34" s="86" t="s">
         <v>175</v>
       </c>
     </row>
@@ -19261,212 +19270,212 @@
         <v>126</v>
       </c>
       <c r="B2" s="64">
-        <f>'Capacity Factor-Reports'!B2</f>
-        <v>0.65</v>
+        <f>'Capacity Factor-Reports'!C2</f>
+        <v>0.49</v>
       </c>
       <c r="C2" s="64">
         <f>B2</f>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="D2" s="64">
         <f t="shared" ref="D2:AG10" si="0">C2</f>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="E2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="F2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="G2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="I2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="J2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="K2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="L2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="M2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="N2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="O2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="P2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="Q2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="R2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="S2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="T2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="U2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="V2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="W2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="X2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="Y2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="Z2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AA2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AB2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AC2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AD2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AE2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AF2" s="64">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AG2" s="79">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AH2" s="82">
         <f>AG2</f>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AI2" s="82">
         <f t="shared" ref="AI2:BA16" si="1">AH2</f>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AJ2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AK2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AL2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AM2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AN2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AO2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AP2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AQ2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AR2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AS2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AT2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AU2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AV2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AW2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AX2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AY2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="AZ2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="BA2" s="82">
         <f t="shared" si="1"/>
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="3" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28391,7 +28400,7 @@
         <v>126</v>
       </c>
       <c r="B2" s="63">
-        <f>'BECF-pre-ret'!B2</f>
+        <f>'Capacity Factor-Reports'!B2</f>
         <v>0.65</v>
       </c>
       <c r="C2" s="63">
